--- a/data/rateBuildUp/File1/RPT_RPT5219538410918ZM_rateBuildUp.xlsx
+++ b/data/rateBuildUp/File1/RPT_RPT5219538410918ZM_rateBuildUp.xlsx
@@ -2958,37 +2958,37 @@
         <v>46576674.63854355</v>
       </c>
       <c r="D11" s="368" t="n">
-        <v>53430343.59559113</v>
+        <v>53430343.59559114</v>
       </c>
       <c r="E11" s="368" t="n">
-        <v>60385901.22126445</v>
+        <v>60385901.22126446</v>
       </c>
       <c r="F11" s="368" t="n">
         <v>67888460.72936952</v>
       </c>
       <c r="G11" s="370" t="n">
-        <v>77027357.5318035</v>
+        <v>77027357.53180349</v>
       </c>
       <c r="H11" s="371" t="n">
         <v>297.2181477908225</v>
       </c>
       <c r="I11" s="372" t="n">
-        <v>325.0610632735838</v>
+        <v>325.0610632735839</v>
       </c>
       <c r="J11" s="372" t="n">
-        <v>349.5382246116499</v>
+        <v>349.53822461165</v>
       </c>
       <c r="K11" s="372" t="n">
         <v>370.339099584712</v>
       </c>
       <c r="L11" s="373" t="n">
-        <v>391.0995684445464</v>
+        <v>391.0995684445463</v>
       </c>
       <c r="M11" s="371" t="n">
-        <v>36.83999773386718</v>
+        <v>36.83999773386717</v>
       </c>
       <c r="N11" s="372" t="n">
-        <v>41.57241017461948</v>
+        <v>41.57241017461949</v>
       </c>
       <c r="O11" s="372" t="n">
         <v>46.2794485051866</v>
@@ -2997,7 +2997,7 @@
         <v>51.2827090282068</v>
       </c>
       <c r="Q11" s="373" t="n">
-        <v>57.14382652496204</v>
+        <v>57.14382652496202</v>
       </c>
       <c r="S11" s="72" t="inlineStr">
         <is>
@@ -3008,37 +3008,37 @@
         <v>46576674.63854355</v>
       </c>
       <c r="U11" s="375" t="n">
-        <v>53430343.59559113</v>
+        <v>53430343.59559114</v>
       </c>
       <c r="V11" s="375" t="n">
-        <v>60385901.22126445</v>
+        <v>60385901.22126446</v>
       </c>
       <c r="W11" s="375" t="n">
         <v>67888460.72936952</v>
       </c>
       <c r="X11" s="376" t="n">
-        <v>77027357.5318035</v>
+        <v>77027357.53180349</v>
       </c>
       <c r="Y11" s="377" t="n">
         <v>297.2181477908225</v>
       </c>
       <c r="Z11" s="372" t="n">
-        <v>325.0610632735838</v>
+        <v>325.0610632735839</v>
       </c>
       <c r="AA11" s="372" t="n">
-        <v>349.5382246116499</v>
+        <v>349.53822461165</v>
       </c>
       <c r="AB11" s="372" t="n">
         <v>370.339099584712</v>
       </c>
       <c r="AC11" s="378" t="n">
-        <v>391.0995684445464</v>
+        <v>391.0995684445463</v>
       </c>
       <c r="AD11" s="377" t="n">
-        <v>36.83999773386718</v>
+        <v>36.83999773386717</v>
       </c>
       <c r="AE11" s="372" t="n">
-        <v>41.57241017461948</v>
+        <v>41.57241017461949</v>
       </c>
       <c r="AF11" s="372" t="n">
         <v>46.2794485051866</v>
@@ -3047,7 +3047,7 @@
         <v>51.2827090282068</v>
       </c>
       <c r="AH11" s="378" t="n">
-        <v>57.14382652496204</v>
+        <v>57.14382652496202</v>
       </c>
       <c r="AJ11" s="78" t="inlineStr">
         <is>
@@ -3058,46 +3058,46 @@
         <v>46576674.63854355</v>
       </c>
       <c r="AL11" s="368" t="n">
-        <v>53430343.59559113</v>
+        <v>53430343.59559114</v>
       </c>
       <c r="AM11" s="368" t="n">
-        <v>60385901.22126445</v>
+        <v>60385901.22126446</v>
       </c>
       <c r="AN11" s="368" t="n">
         <v>67888460.72936952</v>
       </c>
       <c r="AO11" s="380" t="n">
-        <v>77027357.5318035</v>
+        <v>77027357.53180349</v>
       </c>
       <c r="AP11" s="381" t="n">
         <v>297.2366573077144</v>
       </c>
       <c r="AQ11" s="372" t="n">
-        <v>325.0851884256384</v>
+        <v>325.0851884256385</v>
       </c>
       <c r="AR11" s="372" t="n">
-        <v>349.5678434310158</v>
+        <v>349.5678434310159</v>
       </c>
       <c r="AS11" s="372" t="n">
         <v>370.3745893541272</v>
       </c>
       <c r="AT11" s="382" t="n">
-        <v>391.141430041976</v>
+        <v>391.1414300419759</v>
       </c>
       <c r="AU11" s="372" t="n">
         <v>36.84028208826756</v>
       </c>
       <c r="AV11" s="372" t="n">
-        <v>41.57280474314858</v>
+        <v>41.57280474314859</v>
       </c>
       <c r="AW11" s="372" t="n">
-        <v>46.27996769100663</v>
+        <v>46.27996769100664</v>
       </c>
       <c r="AX11" s="372" t="n">
         <v>51.28338949998517</v>
       </c>
       <c r="AY11" s="382" t="n">
-        <v>57.14472011859631</v>
+        <v>57.1447201185963</v>
       </c>
       <c r="BA11" s="83" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>57940652.86013988</v>
       </c>
       <c r="BD11" s="384" t="n">
-        <v>67404504.66779351</v>
+        <v>67404504.6677935</v>
       </c>
       <c r="BE11" s="384" t="n">
         <v>77991280.33764645</v>
@@ -3126,7 +3126,7 @@
         <v>352.5271743544865</v>
       </c>
       <c r="BI11" s="372" t="n">
-        <v>390.19782528242</v>
+        <v>390.1978252824199</v>
       </c>
       <c r="BJ11" s="372" t="n">
         <v>425.491874729779</v>
@@ -3141,7 +3141,7 @@
         <v>45.08216279267779</v>
       </c>
       <c r="BN11" s="389" t="n">
-        <v>51.65905012866295</v>
+        <v>51.65905012866294</v>
       </c>
       <c r="BO11" s="389" t="n">
         <v>58.91512584299542</v>
@@ -3161,7 +3161,7 @@
         <v>58312864.66497567</v>
       </c>
       <c r="BU11" s="375" t="n">
-        <v>68266434.39100206</v>
+        <v>68266434.39100204</v>
       </c>
       <c r="BV11" s="375" t="n">
         <v>79412930.37978922</v>
@@ -3176,7 +3176,7 @@
         <v>350.2537801471804</v>
       </c>
       <c r="BZ11" s="372" t="n">
-        <v>387.8149181787845</v>
+        <v>387.8149181787844</v>
       </c>
       <c r="CA11" s="372" t="n">
         <v>422.970205261525</v>
@@ -3212,16 +3212,16 @@
         <v>2.521669468254004</v>
       </c>
       <c r="DA11" s="93" t="n">
-        <v>2.636263747678015</v>
+        <v>2.636263747678072</v>
       </c>
       <c r="DC11" s="393" t="n">
         <v>0.01509919443924005</v>
       </c>
       <c r="DD11" s="394" t="n">
-        <v>0.01518172965937269</v>
+        <v>0.01518172965937268</v>
       </c>
       <c r="DE11" s="394" t="n">
-        <v>0.01534942786781859</v>
+        <v>0.0153494278678186</v>
       </c>
       <c r="DF11" s="394" t="n">
         <v>0.01557349634666996</v>
@@ -3411,7 +3411,7 @@
         <v>709.9350070881704</v>
       </c>
       <c r="BJ12" s="372" t="n">
-        <v>765.5314427408264</v>
+        <v>765.5314427408265</v>
       </c>
       <c r="BK12" s="387" t="n">
         <v>822.3432742273291</v>
@@ -3426,7 +3426,7 @@
         <v>82.50071570226636</v>
       </c>
       <c r="BO12" s="372" t="n">
-        <v>93.26595055882055</v>
+        <v>93.26595055882056</v>
       </c>
       <c r="BP12" s="387" t="n">
         <v>106.2320297817867</v>
@@ -3440,7 +3440,7 @@
         <v>18191941.16370313</v>
       </c>
       <c r="BT12" s="375" t="n">
-        <v>21058880.08272808</v>
+        <v>21058880.08272809</v>
       </c>
       <c r="BU12" s="375" t="n">
         <v>24238389.22827421</v>
@@ -3455,7 +3455,7 @@
         <v>565.9086046083704</v>
       </c>
       <c r="BY12" s="372" t="n">
-        <v>638.8115762007227</v>
+        <v>638.8115762007228</v>
       </c>
       <c r="BZ12" s="372" t="n">
         <v>705.4030879692489</v>
@@ -3470,7 +3470,7 @@
         <v>64.2268940149862</v>
       </c>
       <c r="CD12" s="372" t="n">
-        <v>73.73722693051934</v>
+        <v>73.73722693051936</v>
       </c>
       <c r="CE12" s="372" t="n">
         <v>84.15733049819283</v>
@@ -3485,19 +3485,19 @@
         <v>4.139547601566619</v>
       </c>
       <c r="CX12" s="103" t="n">
-        <v>4.332453120688115</v>
+        <v>4.332453120688001</v>
       </c>
       <c r="CY12" s="103" t="n">
         <v>4.531919118921564</v>
       </c>
       <c r="CZ12" s="103" t="n">
-        <v>4.772232663181853</v>
+        <v>4.772232663181967</v>
       </c>
       <c r="DA12" s="104" t="n">
         <v>4.91704419064672</v>
       </c>
       <c r="DC12" s="396" t="n">
-        <v>0.01565152476890455</v>
+        <v>0.01565152476890456</v>
       </c>
       <c r="DD12" s="397" t="n">
         <v>0.01558388449696707</v>
@@ -3509,7 +3509,7 @@
         <v>0.01599766935119004</v>
       </c>
       <c r="DG12" s="398" t="n">
-        <v>0.0159762087404998</v>
+        <v>0.01597620874049981</v>
       </c>
     </row>
     <row r="13">
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="C13" s="369" t="n">
-        <v>8050790.236236954</v>
+        <v>8050790.236236955</v>
       </c>
       <c r="D13" s="368" t="n">
         <v>9114259.644327773</v>
@@ -3531,10 +3531,10 @@
         <v>11623184.18433255</v>
       </c>
       <c r="G13" s="370" t="n">
-        <v>13221332.43027924</v>
+        <v>13221332.43027923</v>
       </c>
       <c r="H13" s="371" t="n">
-        <v>688.9527768236626</v>
+        <v>688.9527768236627</v>
       </c>
       <c r="I13" s="372" t="n">
         <v>740.1454183530594</v>
@@ -3546,7 +3546,7 @@
         <v>816.2714790591486</v>
       </c>
       <c r="L13" s="373" t="n">
-        <v>845.0312067744577</v>
+        <v>845.0312067744575</v>
       </c>
       <c r="M13" s="371" t="n">
         <v>117.4941092693843</v>
@@ -3561,7 +3561,7 @@
         <v>160.1083938410563</v>
       </c>
       <c r="Q13" s="373" t="n">
-        <v>177.3697971666426</v>
+        <v>177.3697971666425</v>
       </c>
       <c r="S13" s="109" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="T13" s="374" t="n">
-        <v>8050790.236236954</v>
+        <v>8050790.236236955</v>
       </c>
       <c r="U13" s="375" t="n">
         <v>9114259.644327773</v>
@@ -3581,10 +3581,10 @@
         <v>11623184.18433255</v>
       </c>
       <c r="X13" s="376" t="n">
-        <v>13221332.43027924</v>
+        <v>13221332.43027923</v>
       </c>
       <c r="Y13" s="377" t="n">
-        <v>688.9527768236626</v>
+        <v>688.9527768236627</v>
       </c>
       <c r="Z13" s="372" t="n">
         <v>740.1454183530594</v>
@@ -3596,7 +3596,7 @@
         <v>816.2714790591486</v>
       </c>
       <c r="AC13" s="378" t="n">
-        <v>845.0312067744577</v>
+        <v>845.0312067744575</v>
       </c>
       <c r="AD13" s="377" t="n">
         <v>117.4941092693843</v>
@@ -3611,7 +3611,7 @@
         <v>160.1083938410563</v>
       </c>
       <c r="AH13" s="378" t="n">
-        <v>177.3697971666426</v>
+        <v>177.3697971666425</v>
       </c>
       <c r="AJ13" s="110" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="AK13" s="379" t="n">
-        <v>8050790.236236954</v>
+        <v>8050790.236236955</v>
       </c>
       <c r="AL13" s="368" t="n">
         <v>9114259.644327773</v>
@@ -3631,10 +3631,10 @@
         <v>11623184.18433255</v>
       </c>
       <c r="AO13" s="380" t="n">
-        <v>13221332.43027924</v>
+        <v>13221332.43027923</v>
       </c>
       <c r="AP13" s="381" t="n">
-        <v>688.9527768236626</v>
+        <v>688.9527768236627</v>
       </c>
       <c r="AQ13" s="372" t="n">
         <v>740.1454183530594</v>
@@ -3646,7 +3646,7 @@
         <v>816.2714790591486</v>
       </c>
       <c r="AT13" s="382" t="n">
-        <v>845.0312067744577</v>
+        <v>845.0312067744575</v>
       </c>
       <c r="AU13" s="372" t="n">
         <v>117.4941092696929</v>
@@ -3661,7 +3661,7 @@
         <v>160.1083938414533</v>
       </c>
       <c r="AY13" s="382" t="n">
-        <v>177.3697971675706</v>
+        <v>177.3697971675705</v>
       </c>
       <c r="BA13" s="111" t="inlineStr">
         <is>
@@ -3740,13 +3740,13 @@
         <v>802.3898184552372</v>
       </c>
       <c r="BZ13" s="372" t="n">
-        <v>873.7820185630105</v>
+        <v>873.7820185630106</v>
       </c>
       <c r="CA13" s="372" t="n">
-        <v>937.8388397236423</v>
+        <v>937.8388397236424</v>
       </c>
       <c r="CB13" s="387" t="n">
-        <v>998.5916384034792</v>
+        <v>998.5916384034794</v>
       </c>
       <c r="CC13" s="386" t="n">
         <v>123.6967833481126</v>
@@ -3755,7 +3755,7 @@
         <v>142.9612665200117</v>
       </c>
       <c r="CE13" s="372" t="n">
-        <v>163.5829476219391</v>
+        <v>163.5829476219392</v>
       </c>
       <c r="CF13" s="372" t="n">
         <v>187.1594979275484</v>
@@ -3770,16 +3770,16 @@
         <v>1.416031513925077</v>
       </c>
       <c r="CY13" s="103" t="n">
-        <v>1.262268921135615</v>
+        <v>1.262268921135501</v>
       </c>
       <c r="CZ13" s="103" t="n">
-        <v>1.195333547514224</v>
+        <v>1.19533354751411</v>
       </c>
       <c r="DA13" s="104" t="n">
-        <v>1.153911241974924</v>
+        <v>1.153911241974811</v>
       </c>
       <c r="DC13" s="396" t="n">
-        <v>0.01255052524219419</v>
+        <v>0.01255052524219418</v>
       </c>
       <c r="DD13" s="397" t="n">
         <v>0.01250671103088637</v>
@@ -3788,7 +3788,7 @@
         <v>0.01253173068945308</v>
       </c>
       <c r="DF13" s="397" t="n">
-        <v>0.0125379336023419</v>
+        <v>0.01253793360234189</v>
       </c>
       <c r="DG13" s="398" t="n">
         <v>0.01247566905431304</v>
@@ -3807,7 +3807,7 @@
         <v>79803883.49063842</v>
       </c>
       <c r="E14" s="368" t="n">
-        <v>91622541.55629718</v>
+        <v>91622541.5562972</v>
       </c>
       <c r="F14" s="368" t="n">
         <v>104824680.999119</v>
@@ -3822,7 +3822,7 @@
         <v>3266.727771821991</v>
       </c>
       <c r="J14" s="372" t="n">
-        <v>3389.394385753167</v>
+        <v>3389.394385753168</v>
       </c>
       <c r="K14" s="372" t="n">
         <v>3503.631779582348</v>
@@ -3857,7 +3857,7 @@
         <v>79803883.49063842</v>
       </c>
       <c r="V14" s="402" t="n">
-        <v>91622541.55629718</v>
+        <v>91622541.5562972</v>
       </c>
       <c r="W14" s="402" t="n">
         <v>104824680.999119</v>
@@ -3872,7 +3872,7 @@
         <v>3266.727771821991</v>
       </c>
       <c r="AA14" s="405" t="n">
-        <v>3389.394385753167</v>
+        <v>3389.394385753168</v>
       </c>
       <c r="AB14" s="405" t="n">
         <v>3503.631779582348</v>
@@ -3904,7 +3904,7 @@
         <v>71146187.32989207</v>
       </c>
       <c r="AL14" s="408" t="n">
-        <v>79803883.49063841</v>
+        <v>79803883.49063842</v>
       </c>
       <c r="AM14" s="408" t="n">
         <v>91622541.55629718</v>
@@ -3919,28 +3919,28 @@
         <v>3210.84112247966</v>
       </c>
       <c r="AQ14" s="411" t="n">
-        <v>3266.72777182199</v>
+        <v>3266.727771821991</v>
       </c>
       <c r="AR14" s="411" t="n">
         <v>3389.394385627783</v>
       </c>
       <c r="AS14" s="411" t="n">
-        <v>3503.631779582348</v>
+        <v>3503.631779582347</v>
       </c>
       <c r="AT14" s="412" t="n">
-        <v>3639.570859167151</v>
+        <v>3639.57085916715</v>
       </c>
       <c r="AU14" s="411" t="n">
         <v>2823.987813284443</v>
       </c>
       <c r="AV14" s="411" t="n">
-        <v>2869.321462784831</v>
+        <v>2869.321462784832</v>
       </c>
       <c r="AW14" s="411" t="n">
         <v>2976.398170657375</v>
       </c>
       <c r="AX14" s="411" t="n">
-        <v>3073.152424049543</v>
+        <v>3073.152424049542</v>
       </c>
       <c r="AY14" s="412" t="n">
         <v>3200.681242612935</v>
@@ -4001,79 +4001,79 @@
         </is>
       </c>
       <c r="BS14" s="419" t="n">
-        <v>71159770.3910052</v>
+        <v>71159770.39100517</v>
       </c>
       <c r="BT14" s="420" t="n">
-        <v>82721160.47969423</v>
+        <v>82721160.4796942</v>
       </c>
       <c r="BU14" s="420" t="n">
-        <v>97003937.42761643</v>
+        <v>97003937.4276164</v>
       </c>
       <c r="BV14" s="420" t="n">
-        <v>113407926.4288038</v>
+        <v>113407926.4288037</v>
       </c>
       <c r="BW14" s="421" t="n">
-        <v>134573833.4912403</v>
+        <v>134573833.4912402</v>
       </c>
       <c r="BX14" s="416" t="n">
-        <v>3301.597169367807</v>
+        <v>3301.597169367805</v>
       </c>
       <c r="BY14" s="417" t="n">
-        <v>3480.273585109801</v>
+        <v>3480.2735851098</v>
       </c>
       <c r="BZ14" s="417" t="n">
-        <v>3686.742635471711</v>
+        <v>3686.74263547171</v>
       </c>
       <c r="CA14" s="417" t="n">
-        <v>3890.434507683264</v>
+        <v>3890.434507683263</v>
       </c>
       <c r="CB14" s="418" t="n">
-        <v>4130.885314437096</v>
+        <v>4130.885314437093</v>
       </c>
       <c r="CC14" s="417" t="n">
-        <v>2900.977332425374</v>
+        <v>2900.977332425372</v>
       </c>
       <c r="CD14" s="417" t="n">
-        <v>3057.045126093473</v>
+        <v>3057.045126093472</v>
       </c>
       <c r="CE14" s="417" t="n">
-        <v>3241.150819879243</v>
+        <v>3241.150819879242</v>
       </c>
       <c r="CF14" s="417" t="n">
-        <v>3420.097797411757</v>
+        <v>3420.097797411756</v>
       </c>
       <c r="CG14" s="418" t="n">
-        <v>3644.962699007892</v>
+        <v>3644.96269900789</v>
       </c>
       <c r="CW14" s="132" t="n">
-        <v>67.81229001315205</v>
+        <v>67.81229001315342</v>
       </c>
       <c r="CX14" s="133" t="n">
-        <v>71.20819560781501</v>
+        <v>71.20819560781592</v>
       </c>
       <c r="CY14" s="133" t="n">
-        <v>73.37099834241462</v>
+        <v>73.37099834241599</v>
       </c>
       <c r="CZ14" s="133" t="n">
-        <v>78.47102417561155</v>
+        <v>78.47102417561291</v>
       </c>
       <c r="DA14" s="134" t="n">
-        <v>80.37337236889744</v>
+        <v>80.37337236889925</v>
       </c>
       <c r="DC14" s="422" t="n">
         <v>0.04866627713558654</v>
       </c>
       <c r="DD14" s="423" t="n">
-        <v>0.04942471132771884</v>
+        <v>0.04942471132771883</v>
       </c>
       <c r="DE14" s="423" t="n">
-        <v>0.04960100930908168</v>
+        <v>0.04960100930908167</v>
       </c>
       <c r="DF14" s="423" t="n">
-        <v>0.04998498574654767</v>
+        <v>0.04998498574654768</v>
       </c>
       <c r="DG14" s="424" t="n">
-        <v>0.05019646764910229</v>
+        <v>0.0501964676491023</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
@@ -4095,13 +4095,13 @@
         <v>207923974.6524976</v>
       </c>
       <c r="G15" s="426" t="n">
-        <v>238354658.0410134</v>
+        <v>238354658.0410133</v>
       </c>
       <c r="H15" s="427" t="n">
         <v>643.3438188355617</v>
       </c>
       <c r="I15" s="427" t="n">
-        <v>691.7972564127135</v>
+        <v>691.7972564127136</v>
       </c>
       <c r="J15" s="427" t="n">
         <v>744.9252828782172</v>
@@ -4110,7 +4110,7 @@
         <v>790.847943618515</v>
       </c>
       <c r="L15" s="428" t="n">
-        <v>839.1266863494591</v>
+        <v>839.126686349459</v>
       </c>
       <c r="M15" s="427" t="n">
         <v>87.1518501311496</v>
@@ -4145,13 +4145,13 @@
         <v>207923974.6524976</v>
       </c>
       <c r="X15" s="431" t="n">
-        <v>238354658.0410134</v>
+        <v>238354658.0410133</v>
       </c>
       <c r="Y15" s="432" t="n">
         <v>643.3438188355617</v>
       </c>
       <c r="Z15" s="433" t="n">
-        <v>691.7972564127135</v>
+        <v>691.7972564127136</v>
       </c>
       <c r="AA15" s="433" t="n">
         <v>744.9252828782172</v>
@@ -4160,7 +4160,7 @@
         <v>790.847943618515</v>
       </c>
       <c r="AC15" s="434" t="n">
-        <v>839.1266863494591</v>
+        <v>839.126686349459</v>
       </c>
       <c r="AD15" s="433" t="n">
         <v>87.1518501311496</v>
@@ -4189,34 +4189,34 @@
         <v>161532099.6256683</v>
       </c>
       <c r="AM15" s="408" t="n">
-        <v>183579080.9847428</v>
+        <v>183579080.9847429</v>
       </c>
       <c r="AN15" s="408" t="n">
         <v>207923974.6524976</v>
       </c>
       <c r="AO15" s="409" t="n">
-        <v>238354658.0410134</v>
+        <v>238354658.0410133</v>
       </c>
       <c r="AP15" s="436" t="n">
-        <v>643.3720511397373</v>
+        <v>643.3720511397372</v>
       </c>
       <c r="AQ15" s="437" t="n">
-        <v>691.8333988481107</v>
+        <v>691.8333988481108</v>
       </c>
       <c r="AR15" s="437" t="n">
-        <v>744.9695320502485</v>
+        <v>744.9695320502486</v>
       </c>
       <c r="AS15" s="437" t="n">
-        <v>790.9007843495842</v>
+        <v>790.9007843495839</v>
       </c>
       <c r="AT15" s="438" t="n">
-        <v>839.1889598517764</v>
+        <v>839.1889598517763</v>
       </c>
       <c r="AU15" s="437" t="n">
-        <v>87.15236821113017</v>
+        <v>87.15236821113018</v>
       </c>
       <c r="AV15" s="437" t="n">
-        <v>96.79739763240832</v>
+        <v>96.79739763240835</v>
       </c>
       <c r="AW15" s="437" t="n">
         <v>108.2995898725064</v>
@@ -4248,7 +4248,7 @@
         <v>278690895.7052011</v>
       </c>
       <c r="BG15" s="442" t="n">
-        <v>674.7756382273338</v>
+        <v>674.7756382273337</v>
       </c>
       <c r="BH15" s="443" t="n">
         <v>751.3393199094292</v>
@@ -4257,13 +4257,13 @@
         <v>829.1928544556764</v>
       </c>
       <c r="BJ15" s="443" t="n">
-        <v>902.4062819970376</v>
+        <v>902.4062819970374</v>
       </c>
       <c r="BK15" s="444" t="n">
         <v>981.2030728040784</v>
       </c>
       <c r="BL15" s="443" t="n">
-        <v>91.4063562110131</v>
+        <v>91.40635621101312</v>
       </c>
       <c r="BM15" s="443" t="n">
         <v>105.1231279484721</v>
@@ -4283,19 +4283,19 @@
         </is>
       </c>
       <c r="BS15" s="439" t="n">
-        <v>146573182.8131705</v>
+        <v>146573182.8131704</v>
       </c>
       <c r="BT15" s="440" t="n">
-        <v>172045860.0076335</v>
+        <v>172045860.0076334</v>
       </c>
       <c r="BU15" s="440" t="n">
-        <v>201114502.5764503</v>
+        <v>201114502.5764502</v>
       </c>
       <c r="BV15" s="440" t="n">
-        <v>234178526.107541</v>
+        <v>234178526.1075409</v>
       </c>
       <c r="BW15" s="441" t="n">
-        <v>275765716.3780742</v>
+        <v>275765716.3780741</v>
       </c>
       <c r="BX15" s="442" t="n">
         <v>656.9627481758935</v>
@@ -4304,16 +4304,16 @@
         <v>730.1653162186612</v>
       </c>
       <c r="BZ15" s="443" t="n">
-        <v>804.5121242644021</v>
+        <v>804.512124264402</v>
       </c>
       <c r="CA15" s="443" t="n">
-        <v>874.124505895719</v>
+        <v>874.1245058957189</v>
       </c>
       <c r="CB15" s="444" t="n">
-        <v>949.2839689357266</v>
+        <v>949.283968935726</v>
       </c>
       <c r="CC15" s="443" t="n">
-        <v>89.45645662511875</v>
+        <v>89.45645662511873</v>
       </c>
       <c r="CD15" s="443" t="n">
         <v>103.3101833037134</v>
@@ -4325,7 +4325,7 @@
         <v>136.3720025714879</v>
       </c>
       <c r="CG15" s="444" t="n">
-        <v>157.5642466267241</v>
+        <v>157.564246626724</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
@@ -5079,7 +5079,7 @@
         <v>0.01267173069085671</v>
       </c>
       <c r="N20" s="372" t="n">
-        <v>0.01496336219370705</v>
+        <v>0.01496336219370706</v>
       </c>
       <c r="O20" s="372" t="n">
         <v>0.01772122650145935</v>
@@ -5129,7 +5129,7 @@
         <v>0.01267173069085671</v>
       </c>
       <c r="AE20" s="372" t="n">
-        <v>0.01496336219370705</v>
+        <v>0.01496336219370706</v>
       </c>
       <c r="AF20" s="372" t="n">
         <v>0.01772122650145935</v>
@@ -5179,7 +5179,7 @@
         <v>0.01267182849928787</v>
       </c>
       <c r="AV20" s="372" t="n">
-        <v>0.01496350421269961</v>
+        <v>0.01496350421269962</v>
       </c>
       <c r="AW20" s="372" t="n">
         <v>0.01772142530697261</v>
@@ -5229,7 +5229,7 @@
         <v>0.01267182849928787</v>
       </c>
       <c r="BM20" s="389" t="n">
-        <v>0.01496350421269961</v>
+        <v>0.01496350421269962</v>
       </c>
       <c r="BN20" s="389" t="n">
         <v>0.01772142530697261</v>
@@ -5249,7 +5249,7 @@
         <v>16233.04970876887</v>
       </c>
       <c r="BT20" s="375" t="n">
-        <v>19628.59781623222</v>
+        <v>19628.59781623223</v>
       </c>
       <c r="BU20" s="375" t="n">
         <v>23757.72589699713</v>
@@ -5294,7 +5294,7 @@
         <v>-0.000701658151545118</v>
       </c>
       <c r="CX20" s="92" t="n">
-        <v>-0.0008888391821984391</v>
+        <v>-0.000888839182198425</v>
       </c>
       <c r="CY20" s="92" t="n">
         <v>-0.001109546786169202</v>
@@ -5303,13 +5303,13 @@
         <v>-0.001342965810719049</v>
       </c>
       <c r="DA20" s="93" t="n">
-        <v>-0.001577712896554062</v>
+        <v>-0.001577712896554034</v>
       </c>
       <c r="DC20" s="393" t="n">
         <v>0.001461865594343583</v>
       </c>
       <c r="DD20" s="394" t="n">
-        <v>0.001260033722669668</v>
+        <v>0.001260033722669667</v>
       </c>
       <c r="DE20" s="394" t="n">
         <v>0.001087258220052518</v>
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="BS22" s="391" t="n">
-        <v>645.7249921338652</v>
+        <v>645.7249921338653</v>
       </c>
       <c r="BT22" s="375" t="n">
-        <v>744.5914070340302</v>
+        <v>744.5914070340303</v>
       </c>
       <c r="BU22" s="375" t="n">
         <v>863.5965974050199</v>
@@ -5825,10 +5825,10 @@
         <v>1176.931500651294</v>
       </c>
       <c r="BX22" s="386" t="n">
-        <v>0.05511847987654938</v>
+        <v>0.05511847987654939</v>
       </c>
       <c r="BY22" s="372" t="n">
-        <v>0.06002765782677747</v>
+        <v>0.06002765782677748</v>
       </c>
       <c r="BZ22" s="372" t="n">
         <v>0.06501912662649774</v>
@@ -5840,7 +5840,7 @@
         <v>0.07390165411824727</v>
       </c>
       <c r="CC22" s="386" t="n">
-        <v>0.009441786196499305</v>
+        <v>0.009441786196499307</v>
       </c>
       <c r="CD22" s="372" t="n">
         <v>0.01069508833707209</v>
@@ -5855,10 +5855,10 @@
         <v>0.01583000519619676</v>
       </c>
       <c r="CW22" s="102" t="n">
-        <v>-0.000573019225692403</v>
+        <v>-0.000573019225692417</v>
       </c>
       <c r="CX22" s="103" t="n">
-        <v>-0.000646138604390285</v>
+        <v>-0.000646138604390292</v>
       </c>
       <c r="CY22" s="103" t="n">
         <v>-0.000722052366372558</v>
@@ -6192,7 +6192,7 @@
         <v>0.07641852628351198</v>
       </c>
       <c r="I24" s="427" t="n">
-        <v>0.08698338292420588</v>
+        <v>0.0869833829242059</v>
       </c>
       <c r="J24" s="427" t="n">
         <v>0.09871707464059969</v>
@@ -6216,7 +6216,7 @@
         <v>0.01694302130542042</v>
       </c>
       <c r="Q24" s="428" t="n">
-        <v>0.01998258260730822</v>
+        <v>0.01998258260730821</v>
       </c>
       <c r="S24" s="143" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>0.07641852628351198</v>
       </c>
       <c r="Z24" s="433" t="n">
-        <v>0.08698338292420588</v>
+        <v>0.0869833829242059</v>
       </c>
       <c r="AA24" s="433" t="n">
         <v>0.09871707464059969</v>
@@ -6266,7 +6266,7 @@
         <v>0.01694302130542042</v>
       </c>
       <c r="AH24" s="434" t="n">
-        <v>0.01998258260730822</v>
+        <v>0.01998258260730821</v>
       </c>
       <c r="AJ24" s="150" t="inlineStr">
         <is>
@@ -6289,10 +6289,10 @@
         <v>35066.58257983708</v>
       </c>
       <c r="AP24" s="436" t="n">
-        <v>0.07642187981084141</v>
+        <v>0.07642187981084139</v>
       </c>
       <c r="AQ24" s="437" t="n">
-        <v>0.08698792730663704</v>
+        <v>0.08698792730663706</v>
       </c>
       <c r="AR24" s="437" t="n">
         <v>0.09872293851570045</v>
@@ -6313,7 +6313,7 @@
         <v>0.01435180002977338</v>
       </c>
       <c r="AX24" s="437" t="n">
-        <v>0.01694319419540831</v>
+        <v>0.01694319419540832</v>
       </c>
       <c r="AY24" s="438" t="n">
         <v>0.0199828226312997</v>
@@ -6339,10 +6339,10 @@
         <v>35066.58257983708</v>
       </c>
       <c r="BG24" s="442" t="n">
-        <v>0.07642187981084141</v>
+        <v>0.07642187981084139</v>
       </c>
       <c r="BH24" s="443" t="n">
-        <v>0.08698792730663704</v>
+        <v>0.08698792730663706</v>
       </c>
       <c r="BI24" s="443" t="n">
         <v>0.09872293851570045</v>
@@ -6363,7 +6363,7 @@
         <v>0.01435180002977338</v>
       </c>
       <c r="BO24" s="443" t="n">
-        <v>0.01694319419540831</v>
+        <v>0.01694319419540832</v>
       </c>
       <c r="BP24" s="444" t="n">
         <v>0.0199828226312997</v>
@@ -6392,7 +6392,7 @@
         <v>0.07718104575580055</v>
       </c>
       <c r="BY24" s="443" t="n">
-        <v>0.08797366820908514</v>
+        <v>0.08797366820908517</v>
       </c>
       <c r="BZ24" s="443" t="n">
         <v>0.09997933894145931</v>
@@ -6401,7 +6401,7 @@
         <v>0.1124814121024787</v>
       </c>
       <c r="CB24" s="444" t="n">
-        <v>0.1253069545890618</v>
+        <v>0.1253069545890617</v>
       </c>
       <c r="CC24" s="443" t="n">
         <v>0.01050948914699579</v>
@@ -6413,7 +6413,7 @@
         <v>0.01477743200122038</v>
       </c>
       <c r="CF24" s="443" t="n">
-        <v>0.01754820430845324</v>
+        <v>0.01754820430845323</v>
       </c>
       <c r="CG24" s="444" t="n">
         <v>0.02079872466302172</v>
@@ -7295,19 +7295,19 @@
         <v>1047.177933892141</v>
       </c>
       <c r="BE29" s="375" t="n">
-        <v>40.99114946186235</v>
+        <v>40.99114946186234</v>
       </c>
       <c r="BF29" s="392" t="n">
         <v>0</v>
       </c>
       <c r="BG29" s="386" t="n">
-        <v>0.006909841051221675</v>
+        <v>0.006909841051221674</v>
       </c>
       <c r="BH29" s="372" t="n">
         <v>0.006474500763672487</v>
       </c>
       <c r="BI29" s="372" t="n">
-        <v>0.006062006604785378</v>
+        <v>0.006062006604785379</v>
       </c>
       <c r="BJ29" s="372" t="n">
         <v>0.0002236327055582059</v>
@@ -7316,16 +7316,16 @@
         <v>0</v>
       </c>
       <c r="BL29" s="388" t="n">
-        <v>0.0008564236181964726</v>
+        <v>0.0008564236181964725</v>
       </c>
       <c r="BM29" s="389" t="n">
         <v>0.0008279772983846429</v>
       </c>
       <c r="BN29" s="389" t="n">
-        <v>0.0008025608621735257</v>
+        <v>0.0008025608621735258</v>
       </c>
       <c r="BO29" s="389" t="n">
-        <v>3.096498375894635e-05</v>
+        <v>3.096498375894634e-05</v>
       </c>
       <c r="BP29" s="390" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
         <v>1040.945851984663</v>
       </c>
       <c r="BV29" s="375" t="n">
-        <v>40.97542503859011</v>
+        <v>40.9754250385901</v>
       </c>
       <c r="BW29" s="392" t="n">
         <v>0</v>
@@ -7357,7 +7357,7 @@
         <v>0.006312652989907676</v>
       </c>
       <c r="BZ29" s="372" t="n">
-        <v>0.0059135112887804</v>
+        <v>0.005913511288780401</v>
       </c>
       <c r="CA29" s="372" t="n">
         <v>0.0002182438534425569</v>
@@ -7375,13 +7375,13 @@
         <v>0.0007992417272445699</v>
       </c>
       <c r="CF29" s="389" t="n">
-        <v>3.101437433010594e-05</v>
+        <v>3.101437433010593e-05</v>
       </c>
       <c r="CG29" s="390" t="n">
         <v>0</v>
       </c>
       <c r="CW29" s="91" t="n">
-        <v>0.000176273348129297</v>
+        <v>0.000176273348129296</v>
       </c>
       <c r="CX29" s="92" t="n">
         <v>0.000161847773764811</v>
@@ -8297,7 +8297,7 @@
         <v>0.0006940130281475309</v>
       </c>
       <c r="N33" s="427" t="n">
-        <v>0.0006998071303654664</v>
+        <v>0.0006998071303654662</v>
       </c>
       <c r="O33" s="427" t="n">
         <v>0.0007061831938429285</v>
@@ -8347,7 +8347,7 @@
         <v>0.0006940130281475309</v>
       </c>
       <c r="AE33" s="433" t="n">
-        <v>0.0006998071303654664</v>
+        <v>0.0006998071303654662</v>
       </c>
       <c r="AF33" s="433" t="n">
         <v>0.0007061831938429285</v>
@@ -8388,22 +8388,22 @@
         <v>0.004857723902874456</v>
       </c>
       <c r="AS33" s="437" t="n">
-        <v>0.0001866963165992431</v>
+        <v>0.000186696316599243</v>
       </c>
       <c r="AT33" s="438" t="n">
         <v>0</v>
       </c>
       <c r="AU33" s="437" t="n">
-        <v>0.000694017153754223</v>
+        <v>0.0006940171537542231</v>
       </c>
       <c r="AV33" s="437" t="n">
         <v>0.0006998122457593086</v>
       </c>
       <c r="AW33" s="437" t="n">
-        <v>0.0007061892919933395</v>
+        <v>0.0007061892919933396</v>
       </c>
       <c r="AX33" s="437" t="n">
-        <v>2.851273625649545e-05</v>
+        <v>2.851273625649546e-05</v>
       </c>
       <c r="AY33" s="438" t="n">
         <v>0</v>
@@ -8423,37 +8423,37 @@
         <v>1047.177933892141</v>
       </c>
       <c r="BE33" s="440" t="n">
-        <v>40.99114946186235</v>
+        <v>40.99114946186234</v>
       </c>
       <c r="BF33" s="441" t="n">
         <v>0</v>
       </c>
       <c r="BG33" s="442" t="n">
-        <v>0.004869131335124141</v>
+        <v>0.004869131335124139</v>
       </c>
       <c r="BH33" s="443" t="n">
         <v>0.004557637259016115</v>
       </c>
       <c r="BI33" s="443" t="n">
-        <v>0.00424948012159299</v>
+        <v>0.004249480121592991</v>
       </c>
       <c r="BJ33" s="443" t="n">
-        <v>0.0001559220494652493</v>
+        <v>0.0001559220494652492</v>
       </c>
       <c r="BK33" s="444" t="n">
         <v>0</v>
       </c>
       <c r="BL33" s="443" t="n">
-        <v>0.0006595815379846565</v>
+        <v>0.0006595815379846564</v>
       </c>
       <c r="BM33" s="443" t="n">
         <v>0.000637678705248688</v>
       </c>
       <c r="BN33" s="443" t="n">
-        <v>0.0006177661428291101</v>
+        <v>0.0006177661428291104</v>
       </c>
       <c r="BO33" s="443" t="n">
-        <v>2.381281191807357e-05</v>
+        <v>2.381281191807356e-05</v>
       </c>
       <c r="BP33" s="444" t="n">
         <v>0</v>
@@ -8473,22 +8473,22 @@
         <v>1040.945851984663</v>
       </c>
       <c r="BV33" s="440" t="n">
-        <v>40.97542503859011</v>
+        <v>40.9754250385901</v>
       </c>
       <c r="BW33" s="441" t="n">
         <v>0</v>
       </c>
       <c r="BX33" s="442" t="n">
-        <v>0.004759294004793454</v>
+        <v>0.004759294004793455</v>
       </c>
       <c r="BY33" s="443" t="n">
-        <v>0.004460365371489598</v>
+        <v>0.004460365371489599</v>
       </c>
       <c r="BZ33" s="443" t="n">
         <v>0.004164063495649975</v>
       </c>
       <c r="CA33" s="443" t="n">
-        <v>0.0001529500751459861</v>
+        <v>0.000152950075145986</v>
       </c>
       <c r="CB33" s="444" t="n">
         <v>0</v>
@@ -8500,7 +8500,7 @@
         <v>0.0006310915540558638</v>
       </c>
       <c r="CE33" s="443" t="n">
-        <v>0.0006154688139292611</v>
+        <v>0.0006154688139292612</v>
       </c>
       <c r="CF33" s="443" t="n">
         <v>2.386171294871122e-05</v>
@@ -9376,16 +9376,16 @@
         </is>
       </c>
       <c r="BB38" s="391" t="n">
-        <v>444.1441328636855</v>
+        <v>444.1441328636854</v>
       </c>
       <c r="BC38" s="375" t="n">
         <v>689.3364752758301</v>
       </c>
       <c r="BD38" s="375" t="n">
-        <v>969.3457246219494</v>
+        <v>969.3457246219497</v>
       </c>
       <c r="BE38" s="375" t="n">
-        <v>1274.632341559144</v>
+        <v>1274.632341559143</v>
       </c>
       <c r="BF38" s="392" t="n">
         <v>1624.657186703561</v>
@@ -9397,25 +9397,25 @@
         <v>0.004194116355489805</v>
       </c>
       <c r="BI38" s="372" t="n">
-        <v>0.005611443857624268</v>
+        <v>0.005611443857624269</v>
       </c>
       <c r="BJ38" s="372" t="n">
-        <v>0.006953927442314565</v>
+        <v>0.006953927442314564</v>
       </c>
       <c r="BK38" s="387" t="n">
         <v>0.008249935551441287</v>
       </c>
       <c r="BL38" s="388" t="n">
-        <v>0.0003513002005730741</v>
+        <v>0.000351300200573074</v>
       </c>
       <c r="BM38" s="389" t="n">
         <v>0.00053635535091968</v>
       </c>
       <c r="BN38" s="389" t="n">
-        <v>0.0007429099824566609</v>
+        <v>0.0007429099824566611</v>
       </c>
       <c r="BO38" s="389" t="n">
-        <v>0.000962865649613658</v>
+        <v>0.0009628656496136579</v>
       </c>
       <c r="BP38" s="390" t="n">
         <v>0.001205293589157703</v>
@@ -9432,7 +9432,7 @@
         <v>704.4597020478225</v>
       </c>
       <c r="BU38" s="375" t="n">
-        <v>997.0452295340143</v>
+        <v>997.0452295340147</v>
       </c>
       <c r="BV38" s="375" t="n">
         <v>1318.398827527651</v>
@@ -9447,13 +9447,13 @@
         <v>0.00423130770579009</v>
       </c>
       <c r="BZ38" s="372" t="n">
-        <v>0.005664116158427142</v>
+        <v>0.005664116158427144</v>
       </c>
       <c r="CA38" s="372" t="n">
-        <v>0.007022073357940787</v>
+        <v>0.007022073357940786</v>
       </c>
       <c r="CB38" s="387" t="n">
-        <v>0.00833311895691425</v>
+        <v>0.008333118956914248</v>
       </c>
       <c r="CC38" s="388" t="n">
         <v>0.0003570298447330324</v>
@@ -9462,13 +9462,13 @@
         <v>0.0005490464510592812</v>
       </c>
       <c r="CE38" s="389" t="n">
-        <v>0.0007655346816305533</v>
+        <v>0.0007655346816305535</v>
       </c>
       <c r="CF38" s="389" t="n">
-        <v>0.0009978984895167367</v>
+        <v>0.0009978984895167365</v>
       </c>
       <c r="CG38" s="390" t="n">
-        <v>0.00125515799160005</v>
+        <v>0.001255157991600049</v>
       </c>
       <c r="CW38" s="91" t="n">
         <v>-2.363004316375e-05</v>
@@ -9477,13 +9477,13 @@
         <v>-3.7191350300285e-05</v>
       </c>
       <c r="CY38" s="92" t="n">
-        <v>-5.2672300802874e-05</v>
+        <v>-5.2672300802875e-05</v>
       </c>
       <c r="CZ38" s="92" t="n">
         <v>-6.8145915626222e-05</v>
       </c>
       <c r="DA38" s="93" t="n">
-        <v>-8.318340547296301e-05</v>
+        <v>-8.3183405472961e-05</v>
       </c>
       <c r="DC38" s="393" t="n">
         <v>0</v>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="BB40" s="391" t="n">
-        <v>74.97592112721193</v>
+        <v>74.97592112721192</v>
       </c>
       <c r="BC40" s="375" t="n">
         <v>118.1051228030125</v>
@@ -9952,10 +9952,10 @@
         <v>226.764681219807</v>
       </c>
       <c r="BF40" s="392" t="n">
-        <v>294.2621680813407</v>
+        <v>294.2621680813406</v>
       </c>
       <c r="BG40" s="386" t="n">
-        <v>0.006416124074752784</v>
+        <v>0.006416124074752783</v>
       </c>
       <c r="BH40" s="372" t="n">
         <v>0.009591011112030095</v>
@@ -9982,7 +9982,7 @@
         <v>0.003123664592617599</v>
       </c>
       <c r="BP40" s="387" t="n">
-        <v>0.003947652125223406</v>
+        <v>0.003947652125223405</v>
       </c>
       <c r="BR40" s="111" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         </is>
       </c>
       <c r="BS40" s="391" t="n">
-        <v>75.95593873923131</v>
+        <v>75.9559387392313</v>
       </c>
       <c r="BT40" s="375" t="n">
         <v>120.2627442393418</v>
@@ -9999,16 +9999,16 @@
         <v>172.6544121934863</v>
       </c>
       <c r="BV40" s="375" t="n">
-        <v>232.7888997678468</v>
+        <v>232.7888997678469</v>
       </c>
       <c r="BW40" s="392" t="n">
-        <v>302.9560444208731</v>
+        <v>302.956044420873</v>
       </c>
       <c r="BX40" s="386" t="n">
-        <v>0.006483527712111258</v>
+        <v>0.006483527712111256</v>
       </c>
       <c r="BY40" s="372" t="n">
-        <v>0.009695372243502838</v>
+        <v>0.00969537224350284</v>
       </c>
       <c r="BZ40" s="372" t="n">
         <v>0.01299893853538077</v>
@@ -10023,13 +10023,13 @@
         <v>0.001110627190625366</v>
       </c>
       <c r="CD40" s="372" t="n">
-        <v>0.001727418099574823</v>
+        <v>0.001727418099574824</v>
       </c>
       <c r="CE40" s="372" t="n">
         <v>0.002433564248748223</v>
       </c>
       <c r="CF40" s="372" t="n">
-        <v>0.003214363362248185</v>
+        <v>0.003214363362248186</v>
       </c>
       <c r="CG40" s="387" t="n">
         <v>0.004074829975022104</v>
@@ -10038,13 +10038,13 @@
         <v>-6.7403637358474e-05</v>
       </c>
       <c r="CX40" s="103" t="n">
-        <v>-0.000104361131472743</v>
+        <v>-0.000104361131472745</v>
       </c>
       <c r="CY40" s="103" t="n">
-        <v>-0.00014435620434769</v>
+        <v>-0.000144356204347692</v>
       </c>
       <c r="CZ40" s="103" t="n">
-        <v>-0.000181675125866487</v>
+        <v>-0.00018167512586649</v>
       </c>
       <c r="DA40" s="104" t="n">
         <v>-0.000215618858751286</v>
@@ -10387,7 +10387,7 @@
         <v>0.0003321269940986058</v>
       </c>
       <c r="N42" s="427" t="n">
-        <v>0.0005288826754889807</v>
+        <v>0.0005288826754889806</v>
       </c>
       <c r="O42" s="427" t="n">
         <v>0.0007626449245434798</v>
@@ -10396,7 +10396,7 @@
         <v>0.00103437041833548</v>
       </c>
       <c r="Q42" s="428" t="n">
-        <v>0.001348685021355276</v>
+        <v>0.001348685021355275</v>
       </c>
       <c r="S42" s="143" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>0.0003321269940986058</v>
       </c>
       <c r="AE42" s="433" t="n">
-        <v>0.0005288826754889807</v>
+        <v>0.0005288826754889806</v>
       </c>
       <c r="AF42" s="433" t="n">
         <v>0.0007626449245434798</v>
@@ -10446,7 +10446,7 @@
         <v>0.00103437041833548</v>
       </c>
       <c r="AH42" s="434" t="n">
-        <v>0.001348685021355276</v>
+        <v>0.001348685021355275</v>
       </c>
       <c r="AJ42" s="150" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>0.005246115330499869</v>
       </c>
       <c r="AS42" s="437" t="n">
-        <v>0.006772942306571762</v>
+        <v>0.00677294230657176</v>
       </c>
       <c r="AT42" s="438" t="n">
         <v>0.008332752433835432</v>
@@ -10493,7 +10493,7 @@
         <v>0.000762651510261606</v>
       </c>
       <c r="AX42" s="437" t="n">
-        <v>0.001034380973258706</v>
+        <v>0.001034380973258707</v>
       </c>
       <c r="AY42" s="438" t="n">
         <v>0.001348701221301421</v>
@@ -10504,7 +10504,7 @@
         </is>
       </c>
       <c r="BB42" s="439" t="n">
-        <v>519.1200539908974</v>
+        <v>519.1200539908973</v>
       </c>
       <c r="BC42" s="440" t="n">
         <v>807.4415980788426</v>
@@ -10513,22 +10513,22 @@
         <v>1138.144052207517</v>
       </c>
       <c r="BE42" s="440" t="n">
-        <v>1501.397022778951</v>
+        <v>1501.39702277895</v>
       </c>
       <c r="BF42" s="441" t="n">
         <v>1918.919354784902</v>
       </c>
       <c r="BG42" s="442" t="n">
-        <v>0.00233445296394002</v>
+        <v>0.002334452963940019</v>
       </c>
       <c r="BH42" s="443" t="n">
         <v>0.003458229456960944</v>
       </c>
       <c r="BI42" s="443" t="n">
-        <v>0.00461862341520968</v>
+        <v>0.004618623415209681</v>
       </c>
       <c r="BJ42" s="443" t="n">
-        <v>0.005711010887131186</v>
+        <v>0.005711010887131183</v>
       </c>
       <c r="BK42" s="444" t="n">
         <v>0.00675604978990717</v>
@@ -10540,7 +10540,7 @@
         <v>0.0004838558132736932</v>
       </c>
       <c r="BN42" s="443" t="n">
-        <v>0.000671430172810107</v>
+        <v>0.0006714301728101072</v>
       </c>
       <c r="BO42" s="443" t="n">
         <v>0.0008722001062950048</v>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="BS42" s="439" t="n">
-        <v>526.642464841529</v>
+        <v>526.6424648415289</v>
       </c>
       <c r="BT42" s="440" t="n">
         <v>824.7224462871643</v>
@@ -10575,25 +10575,25 @@
         <v>0.003500134939365452</v>
       </c>
       <c r="BZ42" s="443" t="n">
-        <v>0.004679113298454358</v>
+        <v>0.004679113298454359</v>
       </c>
       <c r="CA42" s="443" t="n">
         <v>0.005790160302960489</v>
       </c>
       <c r="CB42" s="444" t="n">
-        <v>0.006854465118683072</v>
+        <v>0.00685446511868307</v>
       </c>
       <c r="CC42" s="443" t="n">
-        <v>0.0003214201118433284</v>
+        <v>0.0003214201118433283</v>
       </c>
       <c r="CD42" s="443" t="n">
         <v>0.0004952297433767576</v>
       </c>
       <c r="CE42" s="443" t="n">
-        <v>0.0006915956769268277</v>
+        <v>0.0006915956769268279</v>
       </c>
       <c r="CF42" s="443" t="n">
-        <v>0.0009033218384782982</v>
+        <v>0.0009033218384782981</v>
       </c>
       <c r="CG42" s="444" t="n">
         <v>0.001137719236600299</v>
@@ -11237,7 +11237,7 @@
         <v>46594302.08771282</v>
       </c>
       <c r="D47" s="375" t="n">
-        <v>53451499.36762998</v>
+        <v>53451499.36762999</v>
       </c>
       <c r="E47" s="375" t="n">
         <v>60411329.21631917</v>
@@ -11246,16 +11246,16 @@
         <v>67917847.50485983</v>
       </c>
       <c r="G47" s="455" t="n">
-        <v>77062920.15333697</v>
+        <v>77062920.15333696</v>
       </c>
       <c r="H47" s="371" t="n">
-        <v>297.3306332319371</v>
+        <v>297.330633231937</v>
       </c>
       <c r="I47" s="372" t="n">
-        <v>325.1897713688446</v>
+        <v>325.1897713688447</v>
       </c>
       <c r="J47" s="372" t="n">
-        <v>349.6854122178147</v>
+        <v>349.6854122178148</v>
       </c>
       <c r="K47" s="372" t="n">
         <v>370.4994077115697</v>
@@ -11267,7 +11267,7 @@
         <v>36.85394023174813</v>
       </c>
       <c r="N47" s="372" t="n">
-        <v>41.58887079181888</v>
+        <v>41.58887079181889</v>
       </c>
       <c r="O47" s="372" t="n">
         <v>46.29893639166217</v>
@@ -11276,7 +11276,7 @@
         <v>51.30490769703145</v>
       </c>
       <c r="Q47" s="373" t="n">
-        <v>57.17020915498855</v>
+        <v>57.17020915498854</v>
       </c>
       <c r="S47" s="72" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>46594302.08771282</v>
       </c>
       <c r="U47" s="375" t="n">
-        <v>53451499.36762998</v>
+        <v>53451499.36762999</v>
       </c>
       <c r="V47" s="375" t="n">
         <v>60411329.21631917</v>
@@ -11296,16 +11296,16 @@
         <v>67917847.50485983</v>
       </c>
       <c r="X47" s="376" t="n">
-        <v>77062920.15333697</v>
+        <v>77062920.15333696</v>
       </c>
       <c r="Y47" s="377" t="n">
-        <v>297.3306332319371</v>
+        <v>297.330633231937</v>
       </c>
       <c r="Z47" s="372" t="n">
-        <v>325.1897713688446</v>
+        <v>325.1897713688447</v>
       </c>
       <c r="AA47" s="372" t="n">
-        <v>349.6854122178147</v>
+        <v>349.6854122178148</v>
       </c>
       <c r="AB47" s="372" t="n">
         <v>370.4994077115697</v>
@@ -11317,7 +11317,7 @@
         <v>36.85394023174813</v>
       </c>
       <c r="AE47" s="372" t="n">
-        <v>41.58887079181888</v>
+        <v>41.58887079181889</v>
       </c>
       <c r="AF47" s="372" t="n">
         <v>46.29893639166217</v>
@@ -11326,7 +11326,7 @@
         <v>51.30490769703145</v>
       </c>
       <c r="AH47" s="378" t="n">
-        <v>57.17020915498855</v>
+        <v>57.17020915498854</v>
       </c>
       <c r="AJ47" s="78" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>46594302.08771282</v>
       </c>
       <c r="AL47" s="375" t="n">
-        <v>53451499.36762998</v>
+        <v>53451499.36762999</v>
       </c>
       <c r="AM47" s="375" t="n">
         <v>60411329.21631917</v>
@@ -11346,28 +11346,28 @@
         <v>67917847.50485983</v>
       </c>
       <c r="AO47" s="456" t="n">
-        <v>77062920.15333697</v>
+        <v>77062920.15333696</v>
       </c>
       <c r="AP47" s="381" t="n">
         <v>297.349149753957</v>
       </c>
       <c r="AQ47" s="372" t="n">
-        <v>325.2139060732657</v>
+        <v>325.2139060732658</v>
       </c>
       <c r="AR47" s="372" t="n">
-        <v>349.7150435094162</v>
+        <v>349.7150435094163</v>
       </c>
       <c r="AS47" s="372" t="n">
         <v>370.5349128433877</v>
       </c>
       <c r="AT47" s="382" t="n">
-        <v>391.3220154221365</v>
+        <v>391.3220154221364</v>
       </c>
       <c r="AU47" s="372" t="n">
-        <v>36.85422469376553</v>
+        <v>36.85422469376552</v>
       </c>
       <c r="AV47" s="372" t="n">
-        <v>41.5892655165776</v>
+        <v>41.58926551657762</v>
       </c>
       <c r="AW47" s="372" t="n">
         <v>46.29945579610698</v>
@@ -11376,7 +11376,7 @@
         <v>51.30558846336461</v>
       </c>
       <c r="AY47" s="382" t="n">
-        <v>57.17110316118445</v>
+        <v>57.17110316118443</v>
       </c>
       <c r="BA47" s="83" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>57961637.77898525</v>
       </c>
       <c r="BD47" s="375" t="n">
-        <v>67429644.03037083</v>
+        <v>67429644.03037082</v>
       </c>
       <c r="BE47" s="375" t="n">
         <v>78020407.44910015</v>
@@ -11405,7 +11405,7 @@
         <v>352.6548524833898</v>
       </c>
       <c r="BI47" s="372" t="n">
-        <v>390.3433544967507</v>
+        <v>390.3433544967506</v>
       </c>
       <c r="BJ47" s="372" t="n">
         <v>425.6507815871128</v>
@@ -11440,7 +11440,7 @@
         <v>58334248.7001003</v>
       </c>
       <c r="BU47" s="375" t="n">
-        <v>68292230.10798058</v>
+        <v>68292230.10798056</v>
       </c>
       <c r="BV47" s="375" t="n">
         <v>79443029.17070332</v>
@@ -11455,7 +11455,7 @@
         <v>350.3822224588424</v>
       </c>
       <c r="BZ47" s="372" t="n">
-        <v>387.9614611168862</v>
+        <v>387.9614611168861</v>
       </c>
       <c r="CA47" s="372" t="n">
         <v>423.130517841733</v>
@@ -11470,7 +11470,7 @@
         <v>45.46493167869708</v>
       </c>
       <c r="CE47" s="389" t="n">
-        <v>52.43500403485944</v>
+        <v>52.43500403485943</v>
       </c>
       <c r="CF47" s="389" t="n">
         <v>60.13057441862465</v>
@@ -11660,7 +11660,7 @@
         <v>709.9457672218626</v>
       </c>
       <c r="BJ48" s="372" t="n">
-        <v>765.5420174799297</v>
+        <v>765.5420174799298</v>
       </c>
       <c r="BK48" s="387" t="n">
         <v>822.3535162668516</v>
@@ -11675,7 +11675,7 @@
         <v>82.50196612480053</v>
       </c>
       <c r="BO48" s="372" t="n">
-        <v>93.26723889662003</v>
+        <v>93.26723889662004</v>
       </c>
       <c r="BP48" s="387" t="n">
         <v>106.2333528699443</v>
@@ -11689,7 +11689,7 @@
         <v>18192282.0434814</v>
       </c>
       <c r="BT48" s="375" t="n">
-        <v>21059235.76827997</v>
+        <v>21059235.76827998</v>
       </c>
       <c r="BU48" s="375" t="n">
         <v>24238761.05928575</v>
@@ -11704,7 +11704,7 @@
         <v>565.9192085784429</v>
       </c>
       <c r="BY48" s="372" t="n">
-        <v>638.8223657606205</v>
+        <v>638.8223657606206</v>
       </c>
       <c r="BZ48" s="372" t="n">
         <v>705.4139092635714</v>
@@ -11719,7 +11719,7 @@
         <v>64.22809749564799</v>
       </c>
       <c r="CD48" s="372" t="n">
-        <v>73.73847235601929</v>
+        <v>73.7384723560193</v>
       </c>
       <c r="CE48" s="372" t="n">
         <v>84.15862152067099</v>
@@ -11738,7 +11738,7 @@
         </is>
       </c>
       <c r="C49" s="454" t="n">
-        <v>8051505.518484238</v>
+        <v>8051505.518484239</v>
       </c>
       <c r="D49" s="375" t="n">
         <v>9115116.960997041</v>
@@ -11750,7 +11750,7 @@
         <v>11624418.14797619</v>
       </c>
       <c r="G49" s="455" t="n">
-        <v>13222813.69470703</v>
+        <v>13222813.69470702</v>
       </c>
       <c r="H49" s="371" t="n">
         <v>689.0139876707992</v>
@@ -11765,10 +11765,10 @@
         <v>816.3581376986849</v>
       </c>
       <c r="L49" s="373" t="n">
-        <v>845.1258806413747</v>
+        <v>845.1258806413745</v>
       </c>
       <c r="M49" s="371" t="n">
-        <v>117.5045481763803</v>
+        <v>117.5045481763804</v>
       </c>
       <c r="N49" s="372" t="n">
         <v>130.6584099244982</v>
@@ -11788,7 +11788,7 @@
         </is>
       </c>
       <c r="T49" s="374" t="n">
-        <v>8051505.518484238</v>
+        <v>8051505.518484239</v>
       </c>
       <c r="U49" s="375" t="n">
         <v>9115116.960997041</v>
@@ -11800,7 +11800,7 @@
         <v>11624418.14797619</v>
       </c>
       <c r="X49" s="376" t="n">
-        <v>13222813.69470703</v>
+        <v>13222813.69470702</v>
       </c>
       <c r="Y49" s="377" t="n">
         <v>689.0139876707992</v>
@@ -11815,10 +11815,10 @@
         <v>816.3581376986849</v>
       </c>
       <c r="AC49" s="378" t="n">
-        <v>845.1258806413747</v>
+        <v>845.1258806413745</v>
       </c>
       <c r="AD49" s="377" t="n">
-        <v>117.5045481763803</v>
+        <v>117.5045481763804</v>
       </c>
       <c r="AE49" s="372" t="n">
         <v>130.6584099244982</v>
@@ -11838,7 +11838,7 @@
         </is>
       </c>
       <c r="AK49" s="379" t="n">
-        <v>8051505.518484238</v>
+        <v>8051505.518484239</v>
       </c>
       <c r="AL49" s="375" t="n">
         <v>9115116.960997041</v>
@@ -11850,10 +11850,10 @@
         <v>11624418.14797619</v>
       </c>
       <c r="AO49" s="456" t="n">
-        <v>13222813.69470703</v>
+        <v>13222813.69470702</v>
       </c>
       <c r="AP49" s="381" t="n">
-        <v>689.0139876707991</v>
+        <v>689.0139876707992</v>
       </c>
       <c r="AQ49" s="372" t="n">
         <v>740.2150388191859</v>
@@ -11865,7 +11865,7 @@
         <v>816.3581376986849</v>
       </c>
       <c r="AT49" s="382" t="n">
-        <v>845.1258806413746</v>
+        <v>845.1258806413744</v>
       </c>
       <c r="AU49" s="372" t="n">
         <v>117.504548176689</v>
@@ -11959,13 +11959,13 @@
         <v>802.4595414853076</v>
       </c>
       <c r="BZ49" s="372" t="n">
-        <v>873.8600366281723</v>
+        <v>873.8600366281725</v>
       </c>
       <c r="CA49" s="372" t="n">
-        <v>937.9245263542813</v>
+        <v>937.9245263542814</v>
       </c>
       <c r="CB49" s="387" t="n">
-        <v>998.6845632146762</v>
+        <v>998.6845632146764</v>
       </c>
       <c r="CC49" s="386" t="n">
         <v>123.7073357614998</v>
@@ -11977,7 +11977,7 @@
         <v>163.5975535817733</v>
       </c>
       <c r="CF49" s="372" t="n">
-        <v>187.1765979516572</v>
+        <v>187.1765979516573</v>
       </c>
       <c r="CG49" s="387" t="n">
         <v>213.9218940858095</v>
@@ -11996,7 +11996,7 @@
         <v>79803883.49063842</v>
       </c>
       <c r="E50" s="375" t="n">
-        <v>91622541.55629718</v>
+        <v>91622541.5562972</v>
       </c>
       <c r="F50" s="375" t="n">
         <v>104824680.999119</v>
@@ -12011,7 +12011,7 @@
         <v>3266.727771821991</v>
       </c>
       <c r="J50" s="372" t="n">
-        <v>3389.394385753167</v>
+        <v>3389.394385753168</v>
       </c>
       <c r="K50" s="372" t="n">
         <v>3503.631779582348</v>
@@ -12046,7 +12046,7 @@
         <v>79803883.49063842</v>
       </c>
       <c r="V50" s="402" t="n">
-        <v>91622541.55629718</v>
+        <v>91622541.5562972</v>
       </c>
       <c r="W50" s="402" t="n">
         <v>104824680.999119</v>
@@ -12061,7 +12061,7 @@
         <v>3266.727771821991</v>
       </c>
       <c r="AA50" s="405" t="n">
-        <v>3389.394385753167</v>
+        <v>3389.394385753168</v>
       </c>
       <c r="AB50" s="405" t="n">
         <v>3503.631779582348</v>
@@ -12093,7 +12093,7 @@
         <v>71146187.32989207</v>
       </c>
       <c r="AL50" s="458" t="n">
-        <v>79803883.49063841</v>
+        <v>79803883.49063842</v>
       </c>
       <c r="AM50" s="458" t="n">
         <v>91622541.55629718</v>
@@ -12108,28 +12108,28 @@
         <v>3210.84112247966</v>
       </c>
       <c r="AQ50" s="411" t="n">
-        <v>3266.72777182199</v>
+        <v>3266.727771821991</v>
       </c>
       <c r="AR50" s="411" t="n">
         <v>3389.394385627783</v>
       </c>
       <c r="AS50" s="411" t="n">
-        <v>3503.631779582348</v>
+        <v>3503.631779582347</v>
       </c>
       <c r="AT50" s="412" t="n">
-        <v>3639.570859167151</v>
+        <v>3639.57085916715</v>
       </c>
       <c r="AU50" s="411" t="n">
         <v>2823.987813284443</v>
       </c>
       <c r="AV50" s="411" t="n">
-        <v>2869.321462784831</v>
+        <v>2869.321462784832</v>
       </c>
       <c r="AW50" s="411" t="n">
         <v>2976.398170657375</v>
       </c>
       <c r="AX50" s="411" t="n">
-        <v>3073.152424049543</v>
+        <v>3073.152424049542</v>
       </c>
       <c r="AY50" s="412" t="n">
         <v>3200.681242612935</v>
@@ -12190,49 +12190,49 @@
         </is>
       </c>
       <c r="BS50" s="419" t="n">
-        <v>71159770.3910052</v>
+        <v>71159770.39100517</v>
       </c>
       <c r="BT50" s="420" t="n">
-        <v>82721160.47969423</v>
+        <v>82721160.4796942</v>
       </c>
       <c r="BU50" s="420" t="n">
-        <v>97003937.42761643</v>
+        <v>97003937.4276164</v>
       </c>
       <c r="BV50" s="420" t="n">
-        <v>113407926.4288038</v>
+        <v>113407926.4288037</v>
       </c>
       <c r="BW50" s="421" t="n">
-        <v>134573833.4912403</v>
+        <v>134573833.4912402</v>
       </c>
       <c r="BX50" s="416" t="n">
-        <v>3301.597169367807</v>
+        <v>3301.597169367805</v>
       </c>
       <c r="BY50" s="417" t="n">
-        <v>3480.273585109801</v>
+        <v>3480.2735851098</v>
       </c>
       <c r="BZ50" s="417" t="n">
-        <v>3686.742635471711</v>
+        <v>3686.74263547171</v>
       </c>
       <c r="CA50" s="417" t="n">
-        <v>3890.434507683264</v>
+        <v>3890.434507683263</v>
       </c>
       <c r="CB50" s="418" t="n">
-        <v>4130.885314437096</v>
+        <v>4130.885314437093</v>
       </c>
       <c r="CC50" s="417" t="n">
-        <v>2900.977332425374</v>
+        <v>2900.977332425372</v>
       </c>
       <c r="CD50" s="417" t="n">
-        <v>3057.045126093473</v>
+        <v>3057.045126093472</v>
       </c>
       <c r="CE50" s="417" t="n">
-        <v>3241.150819879243</v>
+        <v>3241.150819879242</v>
       </c>
       <c r="CF50" s="417" t="n">
-        <v>3420.097797411757</v>
+        <v>3420.097797411756</v>
       </c>
       <c r="CG50" s="418" t="n">
-        <v>3644.962699007892</v>
+        <v>3644.96269900789</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" thickBot="1">
@@ -12260,7 +12260,7 @@
         <v>643.4278121963389</v>
       </c>
       <c r="I51" s="427" t="n">
-        <v>691.8930211314047</v>
+        <v>691.8930211314048</v>
       </c>
       <c r="J51" s="427" t="n">
         <v>745.0341031919506</v>
@@ -12269,7 +12269,7 @@
         <v>790.9658363967465</v>
       </c>
       <c r="L51" s="428" t="n">
-        <v>839.2584702569819</v>
+        <v>839.2584702569818</v>
       </c>
       <c r="M51" s="427" t="n">
         <v>87.16322845884336</v>
@@ -12325,7 +12325,7 @@
         <v>87.16322845884338</v>
       </c>
       <c r="AE51" s="433" t="n">
-        <v>96.81008953305005</v>
+        <v>96.81008953305003</v>
       </c>
       <c r="AF51" s="433" t="n">
         <v>108.3144751781915</v>
@@ -12357,7 +12357,7 @@
         <v>238392091.3734576</v>
       </c>
       <c r="AP51" s="436" t="n">
-        <v>643.4560481864537</v>
+        <v>643.4560481864536</v>
       </c>
       <c r="AQ51" s="437" t="n">
         <v>691.9291685699586</v>
@@ -12366,13 +12366,13 @@
         <v>745.0783588279978</v>
       </c>
       <c r="AS51" s="437" t="n">
-        <v>791.0186850048552</v>
+        <v>791.018685004855</v>
       </c>
       <c r="AT51" s="438" t="n">
-        <v>839.3207535392833</v>
+        <v>839.3207535392831</v>
       </c>
       <c r="AU51" s="437" t="n">
-        <v>87.16374660646318</v>
+        <v>87.16374660646319</v>
       </c>
       <c r="AV51" s="437" t="n">
         <v>96.81079718765139</v>
@@ -12404,10 +12404,10 @@
         <v>237268936.6235472</v>
       </c>
       <c r="BF51" s="441" t="n">
-        <v>278727881.2071358</v>
+        <v>278727881.2071357</v>
       </c>
       <c r="BG51" s="442" t="n">
-        <v>674.8592636914437</v>
+        <v>674.8592636914436</v>
       </c>
       <c r="BH51" s="443" t="n">
         <v>751.4343237034519</v>
@@ -12416,13 +12416,13 @@
         <v>829.3004454977289</v>
       </c>
       <c r="BJ51" s="443" t="n">
-        <v>902.523089946622</v>
+        <v>902.5230899466218</v>
       </c>
       <c r="BK51" s="444" t="n">
-        <v>981.3332897889413</v>
+        <v>981.3332897889409</v>
       </c>
       <c r="BL51" s="443" t="n">
-        <v>91.41768427107884</v>
+        <v>91.41768427107885</v>
       </c>
       <c r="BM51" s="443" t="n">
         <v>105.1364203394464</v>
@@ -12457,22 +12457,22 @@
         <v>275804109.0927685</v>
       </c>
       <c r="BX51" s="416" t="n">
-        <v>657.0470490053042</v>
+        <v>657.047049005304</v>
       </c>
       <c r="BY51" s="417" t="n">
-        <v>730.261250387181</v>
+        <v>730.2612503871811</v>
       </c>
       <c r="BZ51" s="417" t="n">
-        <v>804.6209467801377</v>
+        <v>804.6209467801376</v>
       </c>
       <c r="CA51" s="417" t="n">
-        <v>874.2429304181996</v>
+        <v>874.2429304181995</v>
       </c>
       <c r="CB51" s="418" t="n">
-        <v>949.4161303554343</v>
+        <v>949.4161303554339</v>
       </c>
       <c r="CC51" s="417" t="n">
-        <v>89.46793559178859</v>
+        <v>89.46793559178856</v>
       </c>
       <c r="CD51" s="417" t="n">
         <v>103.3237569100115</v>
@@ -12481,7 +12481,7 @@
         <v>118.9268848313061</v>
       </c>
       <c r="CF51" s="417" t="n">
-        <v>136.3904779593478</v>
+        <v>136.3904779593477</v>
       </c>
       <c r="CG51" s="418" t="n">
         <v>157.5861830706237</v>
@@ -13653,22 +13653,22 @@
         <v>29501926</v>
       </c>
       <c r="CW58" s="91" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="CX58" s="92" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="CY58" s="92" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="CZ58" s="92" t="n">
-        <v>2615.14832817374</v>
+        <v>2615.148328173735</v>
       </c>
       <c r="DA58" s="93" t="n">
-        <v>2879.554573333055</v>
+        <v>2879.554573333049</v>
       </c>
       <c r="DC58" s="393" t="n">
-        <v>0.00984816114216361</v>
+        <v>0.009848161142163608</v>
       </c>
       <c r="DD58" s="394" t="n">
         <v>0.01024095992489387</v>
@@ -13962,25 +13962,25 @@
         <v>24983100</v>
       </c>
       <c r="CW59" s="102" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="CX59" s="103" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="CY59" s="103" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="CZ59" s="103" t="n">
-        <v>446.752825629441</v>
+        <v>446.7528256294406</v>
       </c>
       <c r="DA59" s="104" t="n">
-        <v>490.9710966469161</v>
+        <v>490.9710966469158</v>
       </c>
       <c r="DC59" s="396" t="n">
         <v>0.009375041997651625</v>
       </c>
       <c r="DD59" s="397" t="n">
-        <v>0.00975735308650902</v>
+        <v>0.009757353086509022</v>
       </c>
       <c r="DE59" s="397" t="n">
         <v>0.01026840829288288</v>
@@ -13989,7 +13989,7 @@
         <v>0.01058323089473216</v>
       </c>
       <c r="DG59" s="398" t="n">
-        <v>0.01076943133572349</v>
+        <v>0.0107694313357235</v>
       </c>
     </row>
     <row r="60">
@@ -14274,7 +14274,7 @@
         <v>130.6682137649017</v>
       </c>
       <c r="CX60" s="103" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="CY60" s="103" t="n">
         <v>157.7761316534635</v>
@@ -14292,7 +14292,7 @@
         <v>0.01115257791951863</v>
       </c>
       <c r="DE60" s="397" t="n">
-        <v>0.01148428654108853</v>
+        <v>0.01148428654108854</v>
       </c>
       <c r="DF60" s="397" t="n">
         <v>0.01164983319294991</v>
@@ -14526,7 +14526,7 @@
         <v>21553.13526775011</v>
       </c>
       <c r="BY61" s="212" t="n">
-        <v>23768.57981326903</v>
+        <v>23768.57981326902</v>
       </c>
       <c r="BZ61" s="212" t="n">
         <v>26311.55657416943</v>
@@ -14580,34 +14580,34 @@
         <v>837210</v>
       </c>
       <c r="CW61" s="132" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="CX61" s="133" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="CY61" s="133" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="CZ61" s="133" t="n">
-        <v>950.5574286398319</v>
+        <v>950.5574286398321</v>
       </c>
       <c r="DA61" s="134" t="n">
-        <v>1093.34929571737</v>
+        <v>1093.349295717371</v>
       </c>
       <c r="DC61" s="422" t="n">
-        <v>0.0294741231667958</v>
+        <v>0.02947412316679581</v>
       </c>
       <c r="DD61" s="423" t="n">
         <v>0.03031253335912444</v>
       </c>
       <c r="DE61" s="423" t="n">
-        <v>0.03101698224883411</v>
+        <v>0.0310169822488341</v>
       </c>
       <c r="DF61" s="423" t="n">
         <v>0.0311467331423472</v>
       </c>
       <c r="DG61" s="424" t="n">
-        <v>0.03202818225091575</v>
+        <v>0.03202818225091576</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" thickBot="1">
@@ -14832,7 +14832,7 @@
         <v>1459680.857487836</v>
       </c>
       <c r="BX62" s="221" t="n">
-        <v>223107.2967533425</v>
+        <v>223107.2967533424</v>
       </c>
       <c r="BY62" s="222" t="n">
         <v>235625.9003079122</v>
@@ -14844,7 +14844,7 @@
         <v>267900.6531999435</v>
       </c>
       <c r="CB62" s="214" t="n">
-        <v>290498.6551992911</v>
+        <v>290498.6551992912</v>
       </c>
       <c r="CC62" s="222" t="n">
         <v>1638486.346797842</v>
@@ -14889,19 +14889,19 @@
         <v>60466650</v>
       </c>
       <c r="CW62" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="CX62" s="133" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="CY62" s="133" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
       <c r="CZ62" s="133" t="n">
-        <v>4186.715162875309</v>
+        <v>4186.715162875304</v>
       </c>
       <c r="DA62" s="134" t="n">
-        <v>4656.789813563187</v>
+        <v>4656.78981356318</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" thickBot="1">
@@ -15772,16 +15772,16 @@
         <v>0.6466114449742995</v>
       </c>
       <c r="BY67" s="463" t="n">
-        <v>0.6803881747826381</v>
+        <v>0.6803881747826384</v>
       </c>
       <c r="BZ67" s="463" t="n">
-        <v>0.7041227667525718</v>
+        <v>0.7041227667525719</v>
       </c>
       <c r="CA67" s="463" t="n">
         <v>0.721646058437451</v>
       </c>
       <c r="CB67" s="464" t="n">
-        <v>0.7433596047961799</v>
+        <v>0.74335960479618</v>
       </c>
       <c r="CC67" s="199" t="n">
         <v>101965.7843942914</v>
@@ -15796,7 +15796,7 @@
         <v>135489.5155371729</v>
       </c>
       <c r="CG67" s="201" t="n">
-        <v>150601.7080481506</v>
+        <v>150601.7080481507</v>
       </c>
       <c r="CW67" s="465" t="n"/>
       <c r="CX67" s="465" t="n"/>
@@ -16017,7 +16017,7 @@
         </is>
       </c>
       <c r="BS68" s="236" t="n">
-        <v>19760.61072108875</v>
+        <v>19760.61072108874</v>
       </c>
       <c r="BT68" s="237" t="n">
         <v>21206.57507523217</v>
@@ -16032,22 +16032,22 @@
         <v>27292.71916327555</v>
       </c>
       <c r="BX68" s="462" t="n">
-        <v>0.6167000484410815</v>
+        <v>0.6167000484410814</v>
       </c>
       <c r="BY68" s="463" t="n">
-        <v>0.6509786380086138</v>
+        <v>0.6509786380086139</v>
       </c>
       <c r="BZ68" s="463" t="n">
-        <v>0.6763319833499947</v>
+        <v>0.6763319833499948</v>
       </c>
       <c r="CA68" s="463" t="n">
-        <v>0.6929421555022223</v>
+        <v>0.6929421555022224</v>
       </c>
       <c r="CB68" s="464" t="n">
         <v>0.714253308151782</v>
       </c>
       <c r="CC68" s="197" t="n">
-        <v>19824.70474124875</v>
+        <v>19824.70474124874</v>
       </c>
       <c r="CD68" s="190" t="n">
         <v>21459.97596939845</v>
@@ -16280,7 +16280,7 @@
         </is>
       </c>
       <c r="BS69" s="236" t="n">
-        <v>7709.422594120959</v>
+        <v>7709.422594120958</v>
       </c>
       <c r="BT69" s="237" t="n">
         <v>8517.104467793557</v>
@@ -16307,7 +16307,7 @@
         <v>0.73849796762568</v>
       </c>
       <c r="CB69" s="464" t="n">
-        <v>0.7670945895092585</v>
+        <v>0.7670945895092586</v>
       </c>
       <c r="CC69" s="197" t="n">
         <v>7684.536209253197</v>
@@ -16322,7 +16322,7 @@
         <v>10673.33792484693</v>
       </c>
       <c r="CG69" s="198" t="n">
-        <v>12216.47603351414</v>
+        <v>12216.47603351415</v>
       </c>
       <c r="CW69" s="465" t="n"/>
       <c r="CX69" s="465" t="n"/>
@@ -16546,7 +16546,7 @@
         <v>15709.70744138703</v>
       </c>
       <c r="BT70" s="255" t="n">
-        <v>17732.88691759676</v>
+        <v>17732.88691759677</v>
       </c>
       <c r="BU70" s="255" t="n">
         <v>19920.31722773356</v>
@@ -16555,22 +16555,22 @@
         <v>22371.86578071988</v>
       </c>
       <c r="BW70" s="256" t="n">
-        <v>25652.86382685494</v>
+        <v>25652.86382685493</v>
       </c>
       <c r="BX70" s="466" t="n">
         <v>0.7000174703382455</v>
       </c>
       <c r="BY70" s="467" t="n">
-        <v>0.7171947087988735</v>
+        <v>0.7171947087988736</v>
       </c>
       <c r="BZ70" s="467" t="n">
-        <v>0.7283718889056493</v>
+        <v>0.7283718889056494</v>
       </c>
       <c r="CA70" s="467" t="n">
-        <v>0.7395256919006067</v>
+        <v>0.7395256919006068</v>
       </c>
       <c r="CB70" s="468" t="n">
-        <v>0.7595570753160314</v>
+        <v>0.7595570753160313</v>
       </c>
       <c r="CC70" s="212" t="n">
         <v>15087.57122798845</v>
@@ -16579,7 +16579,7 @@
         <v>17046.69967774026</v>
       </c>
       <c r="CE70" s="212" t="n">
-        <v>19164.59816197564</v>
+        <v>19164.59816197565</v>
       </c>
       <c r="CF70" s="212" t="n">
         <v>21557.50857484997</v>
@@ -16630,7 +16630,7 @@
         <v>7356.815408947481</v>
       </c>
       <c r="K71" s="215" t="n">
-        <v>9192.319349132102</v>
+        <v>9192.3193491321</v>
       </c>
       <c r="L71" s="216" t="n">
         <v>11125.79579552732</v>
@@ -16680,7 +16680,7 @@
         <v>7356.815408947481</v>
       </c>
       <c r="AB71" s="218" t="n">
-        <v>9192.319349132102</v>
+        <v>9192.3193491321</v>
       </c>
       <c r="AC71" s="219" t="n">
         <v>11125.79579552732</v>
@@ -16824,16 +16824,16 @@
         <v>0.64795100239417</v>
       </c>
       <c r="BY71" s="467" t="n">
-        <v>0.6803922139883307</v>
+        <v>0.6803922139883309</v>
       </c>
       <c r="BZ71" s="467" t="n">
-        <v>0.703403312819713</v>
+        <v>0.7034033128197131</v>
       </c>
       <c r="CA71" s="467" t="n">
         <v>0.7205849213555849</v>
       </c>
       <c r="CB71" s="468" t="n">
-        <v>0.7425296329386262</v>
+        <v>0.7425296329386263</v>
       </c>
       <c r="CC71" s="212" t="n">
         <v>144562.5965727818</v>
@@ -18560,13 +18560,13 @@
         <v>0.864533010841866</v>
       </c>
       <c r="I80" s="495" t="n">
-        <v>0.8600793958367392</v>
+        <v>0.8600793958367391</v>
       </c>
       <c r="J80" s="495" t="n">
         <v>0.8546180977298358</v>
       </c>
       <c r="K80" s="495" t="n">
-        <v>0.8472688112097916</v>
+        <v>0.8472688112097914</v>
       </c>
       <c r="L80" s="496" t="n">
         <v>0.8381345034486744</v>
@@ -18575,7 +18575,7 @@
         <v>0.8621930108418661</v>
       </c>
       <c r="N80" s="495" t="n">
-        <v>0.8567393958367391</v>
+        <v>0.8567393958367389</v>
       </c>
       <c r="O80" s="495" t="n">
         <v>0.8502780977298359</v>
@@ -18584,7 +18584,7 @@
         <v>0.8419288112097915</v>
       </c>
       <c r="Q80" s="496" t="n">
-        <v>0.8317945034486744</v>
+        <v>0.8317945034486743</v>
       </c>
       <c r="S80" s="143" t="inlineStr">
         <is>
@@ -18610,13 +18610,13 @@
         <v>0.864533010841866</v>
       </c>
       <c r="Z80" s="498" t="n">
-        <v>0.8600793958367392</v>
+        <v>0.8600793958367391</v>
       </c>
       <c r="AA80" s="498" t="n">
         <v>0.8546180977298358</v>
       </c>
       <c r="AB80" s="498" t="n">
-        <v>0.8472688112097916</v>
+        <v>0.8472688112097914</v>
       </c>
       <c r="AC80" s="499" t="n">
         <v>0.8381345034486744</v>
@@ -18625,7 +18625,7 @@
         <v>0.8621930108418661</v>
       </c>
       <c r="AE80" s="498" t="n">
-        <v>0.8567393958367391</v>
+        <v>0.8567393958367389</v>
       </c>
       <c r="AF80" s="498" t="n">
         <v>0.8502780977298359</v>
@@ -18634,7 +18634,7 @@
         <v>0.8419288112097915</v>
       </c>
       <c r="AH80" s="499" t="n">
-        <v>0.8317945034486744</v>
+        <v>0.8317945034486743</v>
       </c>
       <c r="AJ80" s="150" t="inlineStr">
         <is>
@@ -18657,31 +18657,31 @@
         <v>1459680.857487836</v>
       </c>
       <c r="AP80" s="500" t="n">
-        <v>0.8645381501158789</v>
+        <v>0.864538150115879</v>
       </c>
       <c r="AQ80" s="501" t="n">
         <v>0.8600856827762666</v>
       </c>
       <c r="AR80" s="501" t="n">
-        <v>0.8546254776696</v>
+        <v>0.8546254776696002</v>
       </c>
       <c r="AS80" s="501" t="n">
-        <v>0.8472774569104109</v>
+        <v>0.847277456910411</v>
       </c>
       <c r="AT80" s="502" t="n">
-        <v>0.8381445708353253</v>
+        <v>0.8381445708353255</v>
       </c>
       <c r="AU80" s="501" t="n">
-        <v>0.862198150115879</v>
+        <v>0.8621981501158791</v>
       </c>
       <c r="AV80" s="501" t="n">
         <v>0.8567456827762665</v>
       </c>
       <c r="AW80" s="501" t="n">
-        <v>0.8502854776696002</v>
+        <v>0.8502854776696003</v>
       </c>
       <c r="AX80" s="501" t="n">
-        <v>0.8419374569104108</v>
+        <v>0.841937456910411</v>
       </c>
       <c r="AY80" s="502" t="n">
         <v>0.8318045708353253</v>
@@ -18707,31 +18707,31 @@
         <v>1459680.857487836</v>
       </c>
       <c r="BG80" s="503" t="n">
-        <v>0.8645381501158789</v>
+        <v>0.864538150115879</v>
       </c>
       <c r="BH80" s="504" t="n">
         <v>0.8600856827762666</v>
       </c>
       <c r="BI80" s="504" t="n">
-        <v>0.8546254776696</v>
+        <v>0.8546254776696002</v>
       </c>
       <c r="BJ80" s="504" t="n">
-        <v>0.8472774569104109</v>
+        <v>0.847277456910411</v>
       </c>
       <c r="BK80" s="505" t="n">
-        <v>0.8381445708353253</v>
+        <v>0.8381445708353255</v>
       </c>
       <c r="BL80" s="504" t="n">
-        <v>0.862198150115879</v>
+        <v>0.8621981501158791</v>
       </c>
       <c r="BM80" s="504" t="n">
         <v>0.8567456827762665</v>
       </c>
       <c r="BN80" s="504" t="n">
-        <v>0.8502854776696002</v>
+        <v>0.8502854776696003</v>
       </c>
       <c r="BO80" s="504" t="n">
-        <v>0.8419374569104108</v>
+        <v>0.841937456910411</v>
       </c>
       <c r="BP80" s="505" t="n">
         <v>0.8318045708353253</v>
@@ -18763,13 +18763,13 @@
         <v>0.8585112425789678</v>
       </c>
       <c r="BZ80" s="504" t="n">
-        <v>0.8521951419395463</v>
+        <v>0.8521951419395464</v>
       </c>
       <c r="CA80" s="504" t="n">
         <v>0.8439901848630282</v>
       </c>
       <c r="CB80" s="505" t="n">
-        <v>0.8340177946927991</v>
+        <v>0.8340177946927992</v>
       </c>
       <c r="CC80" s="492" t="n">
         <v>0</v>
@@ -19452,7 +19452,7 @@
         <v>142.5496348122926</v>
       </c>
       <c r="AR87" s="372" t="n">
-        <v>146.6709237723741</v>
+        <v>146.6709237723742</v>
       </c>
       <c r="AS87" s="372" t="n">
         <v>152.4634568955537</v>
@@ -19487,7 +19487,7 @@
         <v>142.5496348122926</v>
       </c>
       <c r="BI87" s="372" t="n">
-        <v>146.6709237723741</v>
+        <v>146.6709237723742</v>
       </c>
       <c r="BJ87" s="372" t="n">
         <v>152.4634568955537</v>
@@ -19507,10 +19507,10 @@
         <v>159167049.023647</v>
       </c>
       <c r="BU87" s="375" t="n">
-        <v>165208428.9489246</v>
+        <v>165208428.9489247</v>
       </c>
       <c r="BV87" s="375" t="n">
-        <v>172805839.1481514</v>
+        <v>172805839.1481515</v>
       </c>
       <c r="BW87" s="392" t="n">
         <v>179867333.877422</v>
@@ -19522,7 +19522,7 @@
         <v>142.5496348122926</v>
       </c>
       <c r="BZ87" s="372" t="n">
-        <v>146.6709237723741</v>
+        <v>146.6709237723742</v>
       </c>
       <c r="CA87" s="372" t="n">
         <v>152.4634568955537</v>
@@ -19540,13 +19540,13 @@
         <v>241872927.186839</v>
       </c>
       <c r="CL87" s="388" t="n">
-        <v>130.7920126950558</v>
+        <v>130.7920126950557</v>
       </c>
       <c r="CM87" s="390" t="n">
-        <v>721.1982665064118</v>
+        <v>721.1982665064115</v>
       </c>
       <c r="CN87" s="507" t="n">
-        <v>199.6089300018313</v>
+        <v>199.6089300018312</v>
       </c>
     </row>
     <row r="88">
@@ -19629,7 +19629,7 @@
         <v>99621263.56557636</v>
       </c>
       <c r="AL88" s="368" t="n">
-        <v>102867455.424678</v>
+        <v>102867455.4246781</v>
       </c>
       <c r="AM88" s="368" t="n">
         <v>105943211.5840001</v>
@@ -19644,7 +19644,7 @@
         <v>395.6960415492913</v>
       </c>
       <c r="AQ88" s="372" t="n">
-        <v>405.6559433826561</v>
+        <v>405.6559433826562</v>
       </c>
       <c r="AR88" s="372" t="n">
         <v>415.6208472109502</v>
@@ -19653,7 +19653,7 @@
         <v>427.160169283209</v>
       </c>
       <c r="AT88" s="382" t="n">
-        <v>437.5536311497633</v>
+        <v>437.5536311497634</v>
       </c>
       <c r="BA88" s="101" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>99621263.56557636</v>
       </c>
       <c r="BC88" s="375" t="n">
-        <v>102867455.424678</v>
+        <v>102867455.4246781</v>
       </c>
       <c r="BD88" s="375" t="n">
         <v>105943211.5840001</v>
@@ -19679,7 +19679,7 @@
         <v>395.6960415492913</v>
       </c>
       <c r="BH88" s="372" t="n">
-        <v>405.6559433826561</v>
+        <v>405.6559433826562</v>
       </c>
       <c r="BI88" s="372" t="n">
         <v>415.6208472109502</v>
@@ -19688,7 +19688,7 @@
         <v>427.160169283209</v>
       </c>
       <c r="BK88" s="387" t="n">
-        <v>437.5536311497633</v>
+        <v>437.5536311497634</v>
       </c>
       <c r="BR88" s="101" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>395.6960415492913</v>
       </c>
       <c r="BY88" s="372" t="n">
-        <v>405.6559433826561</v>
+        <v>405.6559433826562</v>
       </c>
       <c r="BZ88" s="372" t="n">
         <v>415.6208472109502</v>
@@ -19723,10 +19723,10 @@
         <v>427.160169283209</v>
       </c>
       <c r="CB88" s="387" t="n">
-        <v>437.5536311497633</v>
+        <v>437.5536311497634</v>
       </c>
       <c r="CI88" s="197" t="n">
-        <v>92468586.62020525</v>
+        <v>92468586.62020524</v>
       </c>
       <c r="CJ88" s="198" t="n">
         <v>50146632.66768061</v>
@@ -19824,7 +19824,7 @@
         <v>24428704.35144113</v>
       </c>
       <c r="AL89" s="368" t="n">
-        <v>25266859.46546124</v>
+        <v>25266859.46546125</v>
       </c>
       <c r="AM89" s="368" t="n">
         <v>26068955.30914956</v>
@@ -19839,7 +19839,7 @@
         <v>429.8160672674827</v>
       </c>
       <c r="AQ89" s="372" t="n">
-        <v>439.8151990364772</v>
+        <v>439.8151990364773</v>
       </c>
       <c r="AR89" s="372" t="n">
         <v>449.6699082011643</v>
@@ -19859,7 +19859,7 @@
         <v>24428704.35144113</v>
       </c>
       <c r="BC89" s="375" t="n">
-        <v>25266859.46546124</v>
+        <v>25266859.46546125</v>
       </c>
       <c r="BD89" s="375" t="n">
         <v>26068955.30914956</v>
@@ -19874,7 +19874,7 @@
         <v>429.8160672674827</v>
       </c>
       <c r="BH89" s="372" t="n">
-        <v>439.8151990364772</v>
+        <v>439.8151990364773</v>
       </c>
       <c r="BI89" s="372" t="n">
         <v>449.6699082011643</v>
@@ -19894,7 +19894,7 @@
         <v>24359788.21509158</v>
       </c>
       <c r="BT89" s="375" t="n">
-        <v>25164378.88482037</v>
+        <v>25164378.88482038</v>
       </c>
       <c r="BU89" s="375" t="n">
         <v>25930189.281765</v>
@@ -19909,7 +19909,7 @@
         <v>429.8160672674827</v>
       </c>
       <c r="BY89" s="372" t="n">
-        <v>439.8151990364772</v>
+        <v>439.8151990364773</v>
       </c>
       <c r="BZ89" s="372" t="n">
         <v>449.6699082011643</v>
@@ -19924,10 +19924,10 @@
         <v>22520192.04029759</v>
       </c>
       <c r="CJ89" s="198" t="n">
-        <v>23188084.77820081</v>
+        <v>23188084.77820082</v>
       </c>
       <c r="CK89" s="346" t="n">
-        <v>45708276.8184984</v>
+        <v>45708276.81849842</v>
       </c>
       <c r="CL89" s="386" t="n">
         <v>408.0188433579301</v>
@@ -19936,7 +19936,7 @@
         <v>2158.838541867686</v>
       </c>
       <c r="CN89" s="508" t="n">
-        <v>693.2323776218761</v>
+        <v>693.2323776218764</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1" thickBot="1">
@@ -20016,7 +20016,7 @@
         </is>
       </c>
       <c r="AK90" s="435" t="n">
-        <v>24369432.40270781</v>
+        <v>24369432.4027078</v>
       </c>
       <c r="AL90" s="408" t="n">
         <v>28456663.68210901</v>
@@ -20028,10 +20028,10 @@
         <v>40344383.15839814</v>
       </c>
       <c r="AO90" s="409" t="n">
-        <v>46075816.37371124</v>
+        <v>46075816.37371123</v>
       </c>
       <c r="AP90" s="410" t="n">
-        <v>8028.4018247064</v>
+        <v>8028.401824706396</v>
       </c>
       <c r="AQ90" s="411" t="n">
         <v>8410.41351574498</v>
@@ -20051,7 +20051,7 @@
         </is>
       </c>
       <c r="BB90" s="419" t="n">
-        <v>24369432.40270781</v>
+        <v>24369432.4027078</v>
       </c>
       <c r="BC90" s="420" t="n">
         <v>28456663.68210901</v>
@@ -20063,10 +20063,10 @@
         <v>40344383.15839814</v>
       </c>
       <c r="BF90" s="421" t="n">
-        <v>46075816.37371124</v>
+        <v>46075816.37371123</v>
       </c>
       <c r="BG90" s="416" t="n">
-        <v>8028.4018247064</v>
+        <v>8028.401824706396</v>
       </c>
       <c r="BH90" s="417" t="n">
         <v>8410.41351574498</v>
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="BS90" s="419" t="n">
-        <v>23896135.3809097</v>
+        <v>23896135.38090969</v>
       </c>
       <c r="BT90" s="420" t="n">
         <v>27675380.21333782</v>
@@ -20098,10 +20098,10 @@
         <v>38590944.95395812</v>
       </c>
       <c r="BW90" s="421" t="n">
-        <v>43653353.27835909</v>
+        <v>43653353.27835907</v>
       </c>
       <c r="BX90" s="416" t="n">
-        <v>8028.4018247064</v>
+        <v>8028.401824706396</v>
       </c>
       <c r="BY90" s="417" t="n">
         <v>8410.41351574498</v>
@@ -20116,7 +20116,7 @@
         <v>10051.38944352971</v>
       </c>
       <c r="CI90" s="211" t="n">
-        <v>17230897.74462212</v>
+        <v>17230897.74462213</v>
       </c>
       <c r="CJ90" s="213" t="n">
         <v>211983483.7044855</v>
@@ -20125,7 +20125,7 @@
         <v>229214381.4491076</v>
       </c>
       <c r="CL90" s="416" t="n">
-        <v>6864.899499849451</v>
+        <v>6864.899499849453</v>
       </c>
       <c r="CM90" s="418" t="n">
         <v>11988.65986339133</v>
@@ -20141,10 +20141,10 @@
         </is>
       </c>
       <c r="C91" s="425" t="n">
-        <v>301977441.5881631</v>
+        <v>301977441.588163</v>
       </c>
       <c r="D91" s="425" t="n">
-        <v>316369942.7622761</v>
+        <v>316369942.762276</v>
       </c>
       <c r="E91" s="425" t="n">
         <v>331898217.337541</v>
@@ -20159,13 +20159,13 @@
         <v>212.7769907992159</v>
       </c>
       <c r="I91" s="427" t="n">
-        <v>220.4237268582841</v>
+        <v>220.423726858284</v>
       </c>
       <c r="J91" s="427" t="n">
         <v>229.10401737997</v>
       </c>
       <c r="K91" s="427" t="n">
-        <v>240.154187953093</v>
+        <v>240.1541879530931</v>
       </c>
       <c r="L91" s="428" t="n">
         <v>249.7553771891122</v>
@@ -20176,10 +20176,10 @@
         </is>
       </c>
       <c r="T91" s="429" t="n">
-        <v>301977441.5881631</v>
+        <v>301977441.588163</v>
       </c>
       <c r="U91" s="430" t="n">
-        <v>316369942.7622761</v>
+        <v>316369942.762276</v>
       </c>
       <c r="V91" s="430" t="n">
         <v>331898217.337541</v>
@@ -20194,13 +20194,13 @@
         <v>212.7769907992159</v>
       </c>
       <c r="Z91" s="433" t="n">
-        <v>220.4237268582841</v>
+        <v>220.423726858284</v>
       </c>
       <c r="AA91" s="433" t="n">
         <v>229.10401737997</v>
       </c>
       <c r="AB91" s="433" t="n">
-        <v>240.154187953093</v>
+        <v>240.1541879530931</v>
       </c>
       <c r="AC91" s="434" t="n">
         <v>249.7553771891122</v>
@@ -20223,7 +20223,7 @@
         <v>350263780.7229205</v>
       </c>
       <c r="AO91" s="409" t="n">
-        <v>367341837.0863926</v>
+        <v>367341837.0863928</v>
       </c>
       <c r="AP91" s="436" t="n">
         <v>212.7769907992355</v>
@@ -20258,7 +20258,7 @@
         <v>350263780.7229205</v>
       </c>
       <c r="BF91" s="441" t="n">
-        <v>367341837.0863926</v>
+        <v>367341837.0863928</v>
       </c>
       <c r="BG91" s="442" t="n">
         <v>212.7769907992355</v>
@@ -20287,7 +20287,7 @@
         <v>314486811.255067</v>
       </c>
       <c r="BU91" s="440" t="n">
-        <v>329203076.1069097</v>
+        <v>329203076.1069098</v>
       </c>
       <c r="BV91" s="440" t="n">
         <v>346590229.4588977</v>
@@ -20311,7 +20311,7 @@
         <v>248.3649123529707</v>
       </c>
       <c r="CI91" s="349" t="n">
-        <v>272232002.8271314</v>
+        <v>272232002.8271313</v>
       </c>
       <c r="CJ91" s="350" t="n">
         <v>387178801.9151995</v>
@@ -20996,7 +20996,7 @@
         <v>139869021.2694384</v>
       </c>
       <c r="AX96" s="375" t="n">
-        <v>155296042.6431743</v>
+        <v>155296042.6431742</v>
       </c>
       <c r="AY96" s="456" t="n">
         <v>177112421.3247131</v>
@@ -21087,7 +21087,7 @@
         <v>0</v>
       </c>
       <c r="DC96" s="391" t="n">
-        <v>91214772.24990708</v>
+        <v>91214772.24990706</v>
       </c>
       <c r="DD96" s="375" t="n">
         <v>104988005.1745432</v>
@@ -21099,7 +21099,7 @@
         <v>131624915.6046411</v>
       </c>
       <c r="DG96" s="392" t="n">
-        <v>150667262.2450605</v>
+        <v>150667262.2450604</v>
       </c>
       <c r="DI96" s="368" t="n"/>
       <c r="DJ96" s="368" t="n"/>
@@ -21217,13 +21217,13 @@
         <v>41689376.3923699</v>
       </c>
       <c r="AV97" s="375" t="n">
-        <v>46504050.28654233</v>
+        <v>46504050.28654231</v>
       </c>
       <c r="AW97" s="375" t="n">
         <v>51437235.63014472</v>
       </c>
       <c r="AX97" s="375" t="n">
-        <v>56974314.50595678</v>
+        <v>56974314.50595677</v>
       </c>
       <c r="AY97" s="456" t="n">
         <v>65212950.89794064</v>
@@ -21314,19 +21314,19 @@
         <v>0</v>
       </c>
       <c r="DC97" s="391" t="n">
-        <v>34750578.12386221</v>
+        <v>34750578.1238622</v>
       </c>
       <c r="DD97" s="375" t="n">
-        <v>39059424.72252001</v>
+        <v>39059424.72251999</v>
       </c>
       <c r="DE97" s="375" t="n">
-        <v>43435991.25102001</v>
+        <v>43435991.25102002</v>
       </c>
       <c r="DF97" s="375" t="n">
-        <v>48299721.45663889</v>
+        <v>48299721.45663888</v>
       </c>
       <c r="DG97" s="392" t="n">
-        <v>55445858.27455463</v>
+        <v>55445858.27455464</v>
       </c>
       <c r="DI97" s="368" t="n"/>
       <c r="DJ97" s="368" t="n"/>
@@ -21453,7 +21453,7 @@
         <v>32731840.56260733</v>
       </c>
       <c r="AY98" s="456" t="n">
-        <v>37735006.45384409</v>
+        <v>37735006.45384408</v>
       </c>
       <c r="BA98" s="111" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>0</v>
       </c>
       <c r="DC98" s="391" t="n">
-        <v>18936636.22699493</v>
+        <v>18936636.22699492</v>
       </c>
       <c r="DD98" s="375" t="n">
         <v>21655757.83449386</v>
@@ -21550,7 +21550,7 @@
         <v>24654357.0821007</v>
       </c>
       <c r="DF98" s="375" t="n">
-        <v>28165319.75427984</v>
+        <v>28165319.75427985</v>
       </c>
       <c r="DG98" s="392" t="n">
         <v>32487496.48841152</v>
@@ -21768,19 +21768,19 @@
         <v>0</v>
       </c>
       <c r="DC99" s="419" t="n">
-        <v>163797061.6705361</v>
+        <v>163797061.670536</v>
       </c>
       <c r="DD99" s="420" t="n">
         <v>188089957.4893994</v>
       </c>
       <c r="DE99" s="420" t="n">
-        <v>215978942.3423741</v>
+        <v>215978942.3423739</v>
       </c>
       <c r="DF99" s="420" t="n">
         <v>246346883.7616733</v>
       </c>
       <c r="DG99" s="421" t="n">
-        <v>286688358.6587337</v>
+        <v>286688358.6587336</v>
       </c>
       <c r="DI99" s="368" t="n"/>
       <c r="DJ99" s="368" t="n"/>
@@ -21865,10 +21865,10 @@
         </is>
       </c>
       <c r="AK100" s="435" t="n">
-        <v>481161614.8533111</v>
+        <v>481161614.853311</v>
       </c>
       <c r="AL100" s="408" t="n">
-        <v>538476579.7954479</v>
+        <v>538476579.7954481</v>
       </c>
       <c r="AM100" s="408" t="n">
         <v>602828595.0017819</v>
@@ -21883,13 +21883,13 @@
         <v>2163.756050827067</v>
       </c>
       <c r="AQ100" s="437" t="n">
-        <v>2306.266576508938</v>
+        <v>2306.266576508939</v>
       </c>
       <c r="AR100" s="437" t="n">
         <v>2446.29689786011</v>
       </c>
       <c r="AS100" s="437" t="n">
-        <v>2570.842398783472</v>
+        <v>2570.842398783471</v>
       </c>
       <c r="AT100" s="438" t="n">
         <v>2709.041941860333</v>
@@ -21898,13 +21898,13 @@
         <v>379489526.4173334</v>
       </c>
       <c r="AV100" s="408" t="n">
-        <v>433432828.6743559</v>
+        <v>433432828.674356</v>
       </c>
       <c r="AW100" s="408" t="n">
         <v>491407974.4457932</v>
       </c>
       <c r="AX100" s="408" t="n">
-        <v>554204976.4714398</v>
+        <v>554204976.4714397</v>
       </c>
       <c r="AY100" s="409" t="n">
         <v>639528011.3196728</v>
@@ -21915,10 +21915,10 @@
         </is>
       </c>
       <c r="BB100" s="439" t="n">
-        <v>481161614.8533111</v>
+        <v>481161614.853311</v>
       </c>
       <c r="BC100" s="440" t="n">
-        <v>538476579.7954479</v>
+        <v>538476579.7954481</v>
       </c>
       <c r="BD100" s="440" t="n">
         <v>602828595.0017819</v>
@@ -21933,13 +21933,13 @@
         <v>2163.756050827067</v>
       </c>
       <c r="BH100" s="443" t="n">
-        <v>2306.266576508938</v>
+        <v>2306.266576508939</v>
       </c>
       <c r="BI100" s="443" t="n">
         <v>2446.29689786011</v>
       </c>
       <c r="BJ100" s="443" t="n">
-        <v>2570.842398783472</v>
+        <v>2570.842398783471</v>
       </c>
       <c r="BK100" s="444" t="n">
         <v>2709.041941860333</v>
@@ -21956,7 +21956,7 @@
         <v>533029484.8637558</v>
       </c>
       <c r="BU100" s="440" t="n">
-        <v>598231970.56968</v>
+        <v>598231970.5696801</v>
       </c>
       <c r="BV100" s="440" t="n">
         <v>672371281.2531219</v>
@@ -21971,13 +21971,13 @@
         <v>2262.185456552957</v>
       </c>
       <c r="BZ100" s="443" t="n">
-        <v>2393.088848791202</v>
+        <v>2393.088848791203</v>
       </c>
       <c r="CA100" s="443" t="n">
         <v>2509.778431750624</v>
       </c>
       <c r="CB100" s="444" t="n">
-        <v>2639.541171381976</v>
+        <v>2639.541171381975</v>
       </c>
       <c r="CC100" s="368" t="n"/>
       <c r="CD100" s="368" t="n"/>
@@ -21997,19 +21997,19 @@
         <v>0</v>
       </c>
       <c r="DC100" s="439" t="n">
-        <v>308699048.2713003</v>
+        <v>308699048.2713002</v>
       </c>
       <c r="DD100" s="440" t="n">
-        <v>353793145.2209566</v>
+        <v>353793145.2209565</v>
       </c>
       <c r="DE100" s="440" t="n">
-        <v>402085870.8964268</v>
+        <v>402085870.8964267</v>
       </c>
       <c r="DF100" s="440" t="n">
         <v>454436840.5772331</v>
       </c>
       <c r="DG100" s="441" t="n">
-        <v>525288975.6667603</v>
+        <v>525288975.6667602</v>
       </c>
       <c r="DI100" s="368" t="n"/>
       <c r="DJ100" s="368" t="n"/>
@@ -23081,34 +23081,34 @@
         <v>0</v>
       </c>
       <c r="BX108" s="197" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="BY108" s="190" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="BZ108" s="190" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="CA108" s="190" t="n">
-        <v>2615.14832817374</v>
+        <v>2615.148328173735</v>
       </c>
       <c r="CB108" s="198" t="n">
-        <v>2879.554573333055</v>
+        <v>2879.554573333049</v>
       </c>
       <c r="CC108" s="199" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="CD108" s="200" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="CE108" s="200" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="CF108" s="200" t="n">
-        <v>2615.14832817374</v>
+        <v>2615.148328173735</v>
       </c>
       <c r="CG108" s="201" t="n">
-        <v>2879.554573333055</v>
+        <v>2879.554573333049</v>
       </c>
       <c r="CI108" s="199" t="n">
         <v>0</v>
@@ -23138,19 +23138,19 @@
         <v>0</v>
       </c>
       <c r="CW108" s="199" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784404</v>
       </c>
       <c r="CX108" s="200" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.15531948237</v>
       </c>
       <c r="CY108" s="200" t="n">
-        <v>2378.866087308555</v>
+        <v>2378.86608730855</v>
       </c>
       <c r="CZ108" s="200" t="n">
-        <v>2615.14832817374</v>
+        <v>2615.148328173735</v>
       </c>
       <c r="DA108" s="201" t="n">
-        <v>2879.554573333055</v>
+        <v>2879.554573333049</v>
       </c>
     </row>
     <row r="109">
@@ -23376,34 +23376,34 @@
         <v>0</v>
       </c>
       <c r="BX109" s="197" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="BY109" s="190" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="BZ109" s="190" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="CA109" s="190" t="n">
-        <v>446.752825629441</v>
+        <v>446.7528256294406</v>
       </c>
       <c r="CB109" s="198" t="n">
-        <v>490.9710966469161</v>
+        <v>490.9710966469158</v>
       </c>
       <c r="CC109" s="197" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="CD109" s="190" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="CE109" s="190" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="CF109" s="190" t="n">
-        <v>446.752825629441</v>
+        <v>446.7528256294406</v>
       </c>
       <c r="CG109" s="198" t="n">
-        <v>490.9710966469161</v>
+        <v>490.9710966469158</v>
       </c>
       <c r="CI109" s="197" t="n">
         <v>0</v>
@@ -23433,19 +23433,19 @@
         <v>0</v>
       </c>
       <c r="CW109" s="197" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030452</v>
       </c>
       <c r="CX109" s="190" t="n">
-        <v>372.0859813343213</v>
+        <v>372.085981334321</v>
       </c>
       <c r="CY109" s="190" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315899</v>
       </c>
       <c r="CZ109" s="190" t="n">
-        <v>446.752825629441</v>
+        <v>446.7528256294406</v>
       </c>
       <c r="DA109" s="198" t="n">
-        <v>490.9710966469161</v>
+        <v>490.9710966469158</v>
       </c>
     </row>
     <row r="110">
@@ -23674,7 +23674,7 @@
         <v>130.6682137649017</v>
       </c>
       <c r="BY110" s="190" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="BZ110" s="190" t="n">
         <v>157.7761316534635</v>
@@ -23689,7 +23689,7 @@
         <v>130.6682137649017</v>
       </c>
       <c r="CD110" s="190" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="CE110" s="190" t="n">
         <v>157.7761316534635</v>
@@ -23731,7 +23731,7 @@
         <v>130.6682137649017</v>
       </c>
       <c r="CX110" s="190" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943963</v>
       </c>
       <c r="CY110" s="190" t="n">
         <v>157.7761316534635</v>
@@ -23966,34 +23966,34 @@
         <v>0</v>
       </c>
       <c r="BX111" s="211" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="BY111" s="212" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="BZ111" s="212" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="CA111" s="212" t="n">
-        <v>950.5574286398319</v>
+        <v>950.5574286398321</v>
       </c>
       <c r="CB111" s="213" t="n">
-        <v>1093.34929571737</v>
+        <v>1093.349295717371</v>
       </c>
       <c r="CC111" s="212" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="CD111" s="212" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="CE111" s="212" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="CF111" s="212" t="n">
-        <v>950.5574286398319</v>
+        <v>950.5574286398321</v>
       </c>
       <c r="CG111" s="213" t="n">
-        <v>1093.34929571737</v>
+        <v>1093.349295717371</v>
       </c>
       <c r="CI111" s="211" t="n">
         <v>0</v>
@@ -24023,19 +24023,19 @@
         <v>0</v>
       </c>
       <c r="CW111" s="211" t="n">
-        <v>663.9327169755762</v>
+        <v>663.9327169755763</v>
       </c>
       <c r="CX111" s="212" t="n">
-        <v>753.6182474419384</v>
+        <v>753.6182474419385</v>
       </c>
       <c r="CY111" s="212" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244978</v>
       </c>
       <c r="CZ111" s="212" t="n">
-        <v>950.5574286398319</v>
+        <v>950.5574286398321</v>
       </c>
       <c r="DA111" s="213" t="n">
-        <v>1093.34929571737</v>
+        <v>1093.349295717371</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" thickBot="1">
@@ -24261,34 +24261,34 @@
         <v>0</v>
       </c>
       <c r="BX112" s="221" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="BY112" s="222" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="BZ112" s="222" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
       <c r="CA112" s="222" t="n">
-        <v>4186.715162875308</v>
+        <v>4186.715162875304</v>
       </c>
       <c r="CB112" s="214" t="n">
-        <v>4656.789813563186</v>
+        <v>4656.78981356318</v>
       </c>
       <c r="CC112" s="222" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="CD112" s="222" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="CE112" s="222" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
       <c r="CF112" s="222" t="n">
-        <v>4186.715162875308</v>
+        <v>4186.715162875304</v>
       </c>
       <c r="CG112" s="214" t="n">
-        <v>4656.789813563186</v>
+        <v>4656.78981356318</v>
       </c>
       <c r="CI112" s="349" t="n">
         <v>0</v>
@@ -24318,19 +24318,19 @@
         <v>0</v>
       </c>
       <c r="CW112" s="211" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027927</v>
       </c>
       <c r="CX112" s="212" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653025</v>
       </c>
       <c r="CY112" s="212" t="n">
-        <v>3798.519391218107</v>
+        <v>3798.519391218101</v>
       </c>
       <c r="CZ112" s="212" t="n">
-        <v>4186.715162875309</v>
+        <v>4186.715162875304</v>
       </c>
       <c r="DA112" s="213" t="n">
-        <v>4656.789813563187</v>
+        <v>4656.78981356318</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" thickBot="1">
@@ -30296,19 +30296,19 @@
         </is>
       </c>
       <c r="BS146" s="391" t="n">
-        <v>1587676.557721971</v>
+        <v>1587676.557721967</v>
       </c>
       <c r="BT146" s="375" t="n">
-        <v>1859004.22412202</v>
+        <v>1859004.224122016</v>
       </c>
       <c r="BU146" s="375" t="n">
-        <v>2152911.242960695</v>
+        <v>2152911.242960691</v>
       </c>
       <c r="BV146" s="375" t="n">
-        <v>2465352.406803231</v>
+        <v>2465352.406803226</v>
       </c>
       <c r="BW146" s="392" t="n">
-        <v>2848333.991969491</v>
+        <v>2848333.991969484</v>
       </c>
       <c r="BX146" s="386" t="n">
         <v>808.0292638046026</v>
@@ -30317,28 +30317,28 @@
         <v>859.3947033664067</v>
       </c>
       <c r="BZ146" s="372" t="n">
-        <v>905.0157360461154</v>
+        <v>905.0157360461156</v>
       </c>
       <c r="CA146" s="372" t="n">
         <v>942.7199139120659</v>
       </c>
       <c r="CB146" s="387" t="n">
-        <v>989.1578434898606</v>
+        <v>989.1578434898605</v>
       </c>
       <c r="CW146" s="511" t="n">
-        <v>1587676.557721971</v>
+        <v>1587676.557721967</v>
       </c>
       <c r="CX146" s="512" t="n">
-        <v>1859004.22412202</v>
+        <v>1859004.224122016</v>
       </c>
       <c r="CY146" s="512" t="n">
-        <v>2152911.242960695</v>
+        <v>2152911.242960691</v>
       </c>
       <c r="CZ146" s="512" t="n">
-        <v>2465352.406803231</v>
+        <v>2465352.406803226</v>
       </c>
       <c r="DA146" s="513" t="n">
-        <v>2848333.991969491</v>
+        <v>2848333.991969484</v>
       </c>
     </row>
     <row r="147">
@@ -30488,19 +30488,19 @@
         </is>
       </c>
       <c r="BS147" s="391" t="n">
-        <v>542516.2970588928</v>
+        <v>542516.2970588924</v>
       </c>
       <c r="BT147" s="375" t="n">
-        <v>615908.7206401867</v>
+        <v>615908.7206401862</v>
       </c>
       <c r="BU147" s="375" t="n">
-        <v>709964.9410228858</v>
+        <v>709964.941022885</v>
       </c>
       <c r="BV147" s="375" t="n">
-        <v>811268.0615034173</v>
+        <v>811268.0615034166</v>
       </c>
       <c r="BW147" s="392" t="n">
-        <v>938677.3753287443</v>
+        <v>938677.3753287438</v>
       </c>
       <c r="BX147" s="386" t="n">
         <v>1559.512140023056</v>
@@ -30518,19 +30518,19 @@
         <v>1911.879093778504</v>
       </c>
       <c r="CW147" s="391" t="n">
-        <v>542516.2970588928</v>
+        <v>542516.2970588924</v>
       </c>
       <c r="CX147" s="375" t="n">
-        <v>615908.7206401867</v>
+        <v>615908.7206401862</v>
       </c>
       <c r="CY147" s="375" t="n">
-        <v>709964.9410228858</v>
+        <v>709964.941022885</v>
       </c>
       <c r="CZ147" s="375" t="n">
-        <v>811268.0615034173</v>
+        <v>811268.0615034166</v>
       </c>
       <c r="DA147" s="392" t="n">
-        <v>938677.3753287443</v>
+        <v>938677.3753287438</v>
       </c>
     </row>
     <row r="148">
@@ -30689,10 +30689,10 @@
         <v>411894.9442355949</v>
       </c>
       <c r="BV148" s="375" t="n">
-        <v>471930.3932149258</v>
+        <v>471930.3932149257</v>
       </c>
       <c r="BW148" s="392" t="n">
-        <v>539734.7192076781</v>
+        <v>539734.719207678</v>
       </c>
       <c r="BX148" s="386" t="n">
         <v>2349.470593410198</v>
@@ -30719,10 +30719,10 @@
         <v>411894.9442355949</v>
       </c>
       <c r="CZ148" s="375" t="n">
-        <v>471930.3932149258</v>
+        <v>471930.3932149257</v>
       </c>
       <c r="DA148" s="392" t="n">
-        <v>539734.7192076781</v>
+        <v>539734.719207678</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1" thickBot="1">
@@ -30872,10 +30872,10 @@
         </is>
       </c>
       <c r="BS149" s="419" t="n">
-        <v>8313320.311779679</v>
+        <v>8313320.31177968</v>
       </c>
       <c r="BT149" s="420" t="n">
-        <v>9656231.481041212</v>
+        <v>9656231.481041213</v>
       </c>
       <c r="BU149" s="420" t="n">
         <v>11180930.84122668</v>
@@ -30902,10 +30902,10 @@
         <v>13705.78892383383</v>
       </c>
       <c r="CW149" s="419" t="n">
-        <v>8313320.311779679</v>
+        <v>8313320.31177968</v>
       </c>
       <c r="CX149" s="420" t="n">
-        <v>9656231.481041212</v>
+        <v>9656231.481041213</v>
       </c>
       <c r="CY149" s="420" t="n">
         <v>11180930.84122668</v>
@@ -31064,46 +31064,46 @@
         </is>
       </c>
       <c r="BS150" s="439" t="n">
-        <v>10750514.29229462</v>
+        <v>10750514.29229461</v>
       </c>
       <c r="BT150" s="440" t="n">
         <v>12486637.91338247</v>
       </c>
       <c r="BU150" s="440" t="n">
-        <v>14455701.96944586</v>
+        <v>14455701.96944585</v>
       </c>
       <c r="BV150" s="440" t="n">
-        <v>16461601.19830941</v>
+        <v>16461601.1983094</v>
       </c>
       <c r="BW150" s="441" t="n">
         <v>19311960.75363057</v>
       </c>
       <c r="BX150" s="442" t="n">
-        <v>3459.703149058872</v>
+        <v>3459.703149058875</v>
       </c>
       <c r="BY150" s="443" t="n">
-        <v>3638.429096094123</v>
+        <v>3638.429096094129</v>
       </c>
       <c r="BZ150" s="443" t="n">
-        <v>3805.614893757384</v>
+        <v>3805.614893757388</v>
       </c>
       <c r="CA150" s="443" t="n">
-        <v>3931.865569523025</v>
+        <v>3931.865569523028</v>
       </c>
       <c r="CB150" s="444" t="n">
-        <v>4147.054414477394</v>
+        <v>4147.054414477399</v>
       </c>
       <c r="CW150" s="419" t="n">
-        <v>10750514.29229462</v>
+        <v>10750514.29229461</v>
       </c>
       <c r="CX150" s="420" t="n">
         <v>12486637.91338247</v>
       </c>
       <c r="CY150" s="420" t="n">
-        <v>14455701.96944586</v>
+        <v>14455701.96944585</v>
       </c>
       <c r="CZ150" s="420" t="n">
-        <v>16461601.19830941</v>
+        <v>16461601.1983094</v>
       </c>
       <c r="DA150" s="421" t="n">
         <v>19311960.75363057</v>
@@ -34183,7 +34183,7 @@
         <v>1132051.225420706</v>
       </c>
       <c r="AN172" s="179" t="n">
-        <v>1140493.683591618</v>
+        <v>1140493.683591617</v>
       </c>
       <c r="AO172" s="195" t="n">
         <v>1151005.129087162</v>
@@ -34204,19 +34204,19 @@
         <v>196929.682247454</v>
       </c>
       <c r="AU172" s="190" t="n">
-        <v>1264286.590611396</v>
+        <v>1264286.590611395</v>
       </c>
       <c r="AV172" s="190" t="n">
         <v>1285223.451381556</v>
       </c>
       <c r="AW172" s="190" t="n">
-        <v>1304795.66503686</v>
+        <v>1304795.665036861</v>
       </c>
       <c r="AX172" s="190" t="n">
-        <v>1323790.439580505</v>
+        <v>1323790.439580504</v>
       </c>
       <c r="AY172" s="196" t="n">
-        <v>1347934.811334616</v>
+        <v>1347934.811334617</v>
       </c>
       <c r="BA172" s="83" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>1132051.225420706</v>
       </c>
       <c r="BE172" s="190" t="n">
-        <v>1140493.683591618</v>
+        <v>1140493.683591617</v>
       </c>
       <c r="BF172" s="198" t="n">
         <v>1151005.129087162</v>
@@ -34263,7 +34263,7 @@
         <v>1304795.665036861</v>
       </c>
       <c r="BO172" s="200" t="n">
-        <v>1323790.439580505</v>
+        <v>1323790.439580504</v>
       </c>
       <c r="BP172" s="201" t="n">
         <v>1347934.811334616</v>
@@ -34283,7 +34283,7 @@
         <v>1126388.412234446</v>
       </c>
       <c r="BV172" s="190" t="n">
-        <v>1133424.642644258</v>
+        <v>1133424.642644257</v>
       </c>
       <c r="BW172" s="198" t="n">
         <v>1142459.222383301</v>
@@ -34301,7 +34301,7 @@
         <v>187750.6486080731</v>
       </c>
       <c r="CB172" s="198" t="n">
-        <v>202596.0343779826</v>
+        <v>202596.0343779827</v>
       </c>
       <c r="CC172" s="199" t="n">
         <v>1262321.715539611</v>
@@ -34313,7 +34313,7 @@
         <v>1302416.798949552</v>
       </c>
       <c r="CF172" s="200" t="n">
-        <v>1321175.291252331</v>
+        <v>1321175.29125233</v>
       </c>
       <c r="CG172" s="201" t="n">
         <v>1345055.256761284</v>
@@ -34453,7 +34453,7 @@
         </is>
       </c>
       <c r="AK173" s="194" t="n">
-        <v>251762.092882014</v>
+        <v>251762.092882013</v>
       </c>
       <c r="AL173" s="179" t="n">
         <v>253583.010683622</v>
@@ -34483,7 +34483,7 @@
         <v>38024.309718277</v>
       </c>
       <c r="AU173" s="190" t="n">
-        <v>283592.7910795145</v>
+        <v>283592.7910795144</v>
       </c>
       <c r="AV173" s="190" t="n">
         <v>285965.6858407336</v>
@@ -34492,7 +34492,7 @@
         <v>288420.5176779932</v>
       </c>
       <c r="AX173" s="190" t="n">
-        <v>290894.5708527533</v>
+        <v>290894.5708527532</v>
       </c>
       <c r="AY173" s="196" t="n">
         <v>294346.5865991116</v>
@@ -34503,7 +34503,7 @@
         </is>
       </c>
       <c r="BB173" s="197" t="n">
-        <v>251762.092882014</v>
+        <v>251762.092882013</v>
       </c>
       <c r="BC173" s="190" t="n">
         <v>253583.010683622</v>
@@ -34533,7 +34533,7 @@
         <v>38024.309718277</v>
       </c>
       <c r="BL173" s="197" t="n">
-        <v>283592.791079515</v>
+        <v>283592.791079514</v>
       </c>
       <c r="BM173" s="190" t="n">
         <v>285965.685840734</v>
@@ -34553,7 +34553,7 @@
         </is>
       </c>
       <c r="BS173" s="197" t="n">
-        <v>251098.485750888</v>
+        <v>251098.485750887</v>
       </c>
       <c r="BT173" s="190" t="n">
         <v>252627.885292914</v>
@@ -34583,7 +34583,7 @@
         <v>39399.4959806686</v>
       </c>
       <c r="CC173" s="197" t="n">
-        <v>283244.9154310119</v>
+        <v>283244.9154310109</v>
       </c>
       <c r="CD173" s="190" t="n">
         <v>285593.5998593998</v>
@@ -34762,13 +34762,13 @@
         <v>15645.969431663</v>
       </c>
       <c r="AU174" s="190" t="n">
-        <v>68520.79892571829</v>
+        <v>68520.79892571821</v>
       </c>
       <c r="AV174" s="190" t="n">
-        <v>69762.95644698211</v>
+        <v>69762.95644698199</v>
       </c>
       <c r="AW174" s="190" t="n">
-        <v>71104.91150434389</v>
+        <v>71104.911504344</v>
       </c>
       <c r="AX174" s="190" t="n">
         <v>72595.7203454608</v>
@@ -35290,7 +35290,7 @@
         </is>
       </c>
       <c r="AK176" s="206" t="n">
-        <v>1419220.379298875</v>
+        <v>1419220.379298874</v>
       </c>
       <c r="AL176" s="207" t="n">
         <v>1435280.798812628</v>
@@ -35299,7 +35299,7 @@
         <v>1448679.168235343</v>
       </c>
       <c r="AN176" s="207" t="n">
-        <v>1458495.409587527</v>
+        <v>1458495.409587526</v>
       </c>
       <c r="AO176" s="208" t="n">
         <v>1470806.519645696</v>
@@ -35320,7 +35320,7 @@
         <v>284029.782855784</v>
       </c>
       <c r="AU176" s="207" t="n">
-        <v>1641593.6984478</v>
+        <v>1641593.698447799</v>
       </c>
       <c r="AV176" s="207" t="n">
         <v>1668764.900469312</v>
@@ -35340,7 +35340,7 @@
         </is>
       </c>
       <c r="BB176" s="221" t="n">
-        <v>1419220.379298875</v>
+        <v>1419220.379298874</v>
       </c>
       <c r="BC176" s="222" t="n">
         <v>1435280.798812628</v>
@@ -35349,7 +35349,7 @@
         <v>1448679.168235343</v>
       </c>
       <c r="BE176" s="222" t="n">
-        <v>1458495.409587527</v>
+        <v>1458495.409587526</v>
       </c>
       <c r="BF176" s="214" t="n">
         <v>1470806.519645696</v>
@@ -35370,7 +35370,7 @@
         <v>284029.782855784</v>
       </c>
       <c r="BL176" s="222" t="n">
-        <v>1641593.6984478</v>
+        <v>1641593.698447799</v>
       </c>
       <c r="BM176" s="222" t="n">
         <v>1668764.900469312</v>
@@ -35379,7 +35379,7 @@
         <v>1695104.119977999</v>
       </c>
       <c r="BO176" s="222" t="n">
-        <v>1721390.552400128</v>
+        <v>1721390.552400127</v>
       </c>
       <c r="BP176" s="214" t="n">
         <v>1754836.30250148</v>
@@ -35390,7 +35390,7 @@
         </is>
       </c>
       <c r="BS176" s="221" t="n">
-        <v>1415379.050044507</v>
+        <v>1415379.050044506</v>
       </c>
       <c r="BT176" s="222" t="n">
         <v>1429707.124045061</v>
@@ -35399,7 +35399,7 @@
         <v>1441322.416354639</v>
       </c>
       <c r="BV176" s="222" t="n">
-        <v>1449303.18403771</v>
+        <v>1449303.184037709</v>
       </c>
       <c r="BW176" s="214" t="n">
         <v>1459680.857487838</v>
@@ -35414,13 +35414,13 @@
         <v>249983.1842321427</v>
       </c>
       <c r="CA176" s="222" t="n">
-        <v>267900.6531995422</v>
+        <v>267900.6531995421</v>
       </c>
       <c r="CB176" s="214" t="n">
         <v>290498.6552000805</v>
       </c>
       <c r="CC176" s="222" t="n">
-        <v>1638486.346796772</v>
+        <v>1638486.346796771</v>
       </c>
       <c r="CD176" s="222" t="n">
         <v>1665333.024353659</v>
@@ -35429,7 +35429,7 @@
         <v>1691305.600586782</v>
       </c>
       <c r="CF176" s="222" t="n">
-        <v>1717203.837237252</v>
+        <v>1717203.837237251</v>
       </c>
       <c r="CG176" s="214" t="n">
         <v>1750179.512687918</v>
@@ -38455,7 +38455,7 @@
         <v>1132051.225420706</v>
       </c>
       <c r="AN190" s="179" t="n">
-        <v>1140493.683591618</v>
+        <v>1140493.683591617</v>
       </c>
       <c r="AO190" s="195" t="n">
         <v>1151005.129087162</v>
@@ -38473,19 +38473,19 @@
         <v>183296.7559888872</v>
       </c>
       <c r="AT190" s="195" t="n">
-        <v>196929.6822474545</v>
+        <v>196929.6822474544</v>
       </c>
       <c r="AU190" s="190" t="n">
-        <v>1264286.590611396</v>
+        <v>1264286.590611395</v>
       </c>
       <c r="AV190" s="190" t="n">
-        <v>1285223.451381556</v>
+        <v>1285223.451381555</v>
       </c>
       <c r="AW190" s="190" t="n">
-        <v>1304795.66503686</v>
+        <v>1304795.665036861</v>
       </c>
       <c r="AX190" s="190" t="n">
-        <v>1323790.439580505</v>
+        <v>1323790.439580504</v>
       </c>
       <c r="AY190" s="196" t="n">
         <v>1347934.811334617</v>
@@ -38505,7 +38505,7 @@
         <v>1132051.225420706</v>
       </c>
       <c r="BE190" s="190" t="n">
-        <v>1140493.683591618</v>
+        <v>1140493.683591617</v>
       </c>
       <c r="BF190" s="198" t="n">
         <v>1151005.129087162</v>
@@ -38523,7 +38523,7 @@
         <v>183296.7559888872</v>
       </c>
       <c r="BK190" s="198" t="n">
-        <v>196929.6822474545</v>
+        <v>196929.6822474544</v>
       </c>
       <c r="BL190" s="199" t="n">
         <v>1264286.590611396</v>
@@ -38535,7 +38535,7 @@
         <v>1304795.665036861</v>
       </c>
       <c r="BO190" s="200" t="n">
-        <v>1323790.439580505</v>
+        <v>1323790.439580504</v>
       </c>
       <c r="BP190" s="201" t="n">
         <v>1347934.811334617</v>
@@ -38555,7 +38555,7 @@
         <v>1126388.412234446</v>
       </c>
       <c r="BV190" s="190" t="n">
-        <v>1133424.642644258</v>
+        <v>1133424.642644257</v>
       </c>
       <c r="BW190" s="198" t="n">
         <v>1142459.222383301</v>
@@ -38585,7 +38585,7 @@
         <v>1302416.798949552</v>
       </c>
       <c r="CF190" s="200" t="n">
-        <v>1321175.291252331</v>
+        <v>1321175.29125233</v>
       </c>
       <c r="CG190" s="201" t="n">
         <v>1345055.256761284</v>
@@ -38618,25 +38618,25 @@
         <v>29501926</v>
       </c>
       <c r="CW190" s="91" t="n">
-        <v>1964.87507178444</v>
+        <v>1964.875071784435</v>
       </c>
       <c r="CX190" s="92" t="n">
-        <v>2163.155319482304</v>
+        <v>2163.1553194823</v>
       </c>
       <c r="CY190" s="92" t="n">
-        <v>2378.866087308496</v>
+        <v>2378.866087308491</v>
       </c>
       <c r="CZ190" s="92" t="n">
-        <v>2615.148328173792</v>
+        <v>2615.148328173786</v>
       </c>
       <c r="DA190" s="93" t="n">
-        <v>2879.55457333282</v>
+        <v>2879.554573332814</v>
       </c>
       <c r="DC190" s="393" t="n">
         <v>0.009848161142173377</v>
       </c>
       <c r="DD190" s="394" t="n">
-        <v>0.01024095992487895</v>
+        <v>0.01024095992487894</v>
       </c>
       <c r="DE190" s="394" t="n">
         <v>0.01065955492972585</v>
@@ -38645,7 +38645,7 @@
         <v>0.01099740955274481</v>
       </c>
       <c r="DG190" s="395" t="n">
-        <v>0.01119286179102339</v>
+        <v>0.0111928617910234</v>
       </c>
     </row>
     <row r="191">
@@ -38755,7 +38755,7 @@
         </is>
       </c>
       <c r="AK191" s="194" t="n">
-        <v>251762.092882014</v>
+        <v>251762.092882013</v>
       </c>
       <c r="AL191" s="179" t="n">
         <v>253583.010683622</v>
@@ -38770,34 +38770,34 @@
         <v>256322.276880835</v>
       </c>
       <c r="AP191" s="194" t="n">
-        <v>31830.6981975012</v>
+        <v>31830.69819750122</v>
       </c>
       <c r="AQ191" s="179" t="n">
-        <v>32382.6751571124</v>
+        <v>32382.67515711238</v>
       </c>
       <c r="AR191" s="179" t="n">
-        <v>33517.01056342499</v>
+        <v>33517.01056342496</v>
       </c>
       <c r="AS191" s="179" t="n">
-        <v>35440.16241287872</v>
+        <v>35440.16241287873</v>
       </c>
       <c r="AT191" s="195" t="n">
-        <v>38024.3097182769</v>
+        <v>38024.30971827687</v>
       </c>
       <c r="AU191" s="190" t="n">
-        <v>283592.7910795147</v>
+        <v>283592.7910795146</v>
       </c>
       <c r="AV191" s="190" t="n">
-        <v>285965.685840734</v>
+        <v>285965.6858407339</v>
       </c>
       <c r="AW191" s="190" t="n">
         <v>288420.5176779932</v>
       </c>
       <c r="AX191" s="190" t="n">
-        <v>290894.570852753</v>
+        <v>290894.5708527529</v>
       </c>
       <c r="AY191" s="196" t="n">
-        <v>294346.5865991116</v>
+        <v>294346.5865991114</v>
       </c>
       <c r="BA191" s="101" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         </is>
       </c>
       <c r="BB191" s="197" t="n">
-        <v>251762.092882014</v>
+        <v>251762.092882013</v>
       </c>
       <c r="BC191" s="190" t="n">
         <v>253583.010683622</v>
@@ -38820,28 +38820,28 @@
         <v>256322.276880835</v>
       </c>
       <c r="BG191" s="197" t="n">
-        <v>31830.6981975012</v>
+        <v>31830.69819750122</v>
       </c>
       <c r="BH191" s="190" t="n">
-        <v>32382.6751571124</v>
+        <v>32382.67515711238</v>
       </c>
       <c r="BI191" s="190" t="n">
-        <v>33517.01056342499</v>
+        <v>33517.01056342496</v>
       </c>
       <c r="BJ191" s="190" t="n">
-        <v>35440.16241287872</v>
+        <v>35440.16241287873</v>
       </c>
       <c r="BK191" s="198" t="n">
-        <v>38024.3097182769</v>
+        <v>38024.30971827687</v>
       </c>
       <c r="BL191" s="197" t="n">
-        <v>283592.7910795152</v>
+        <v>283592.7910795143</v>
       </c>
       <c r="BM191" s="190" t="n">
         <v>285965.6858407344</v>
       </c>
       <c r="BN191" s="190" t="n">
-        <v>288420.517677993</v>
+        <v>288420.5176779929</v>
       </c>
       <c r="BO191" s="190" t="n">
         <v>290894.5708527527</v>
@@ -38855,7 +38855,7 @@
         </is>
       </c>
       <c r="BS191" s="197" t="n">
-        <v>251098.485750888</v>
+        <v>251098.485750887</v>
       </c>
       <c r="BT191" s="190" t="n">
         <v>252627.885292914</v>
@@ -38870,28 +38870,28 @@
         <v>254456.119521797</v>
       </c>
       <c r="BX191" s="197" t="n">
-        <v>32146.42968012412</v>
+        <v>32146.42968012414</v>
       </c>
       <c r="BY191" s="190" t="n">
-        <v>32965.71456648616</v>
+        <v>32965.71456648615</v>
       </c>
       <c r="BZ191" s="190" t="n">
-        <v>34361.04780651606</v>
+        <v>34361.04780651603</v>
       </c>
       <c r="CA191" s="190" t="n">
         <v>36546.78659560293</v>
       </c>
       <c r="CB191" s="198" t="n">
-        <v>39399.4959806685</v>
+        <v>39399.49598066847</v>
       </c>
       <c r="CC191" s="197" t="n">
-        <v>283244.9154310121</v>
+        <v>283244.9154310112</v>
       </c>
       <c r="CD191" s="190" t="n">
-        <v>285593.5998594002</v>
+        <v>285593.5998594001</v>
       </c>
       <c r="CE191" s="190" t="n">
-        <v>288012.8098743621</v>
+        <v>288012.809874362</v>
       </c>
       <c r="CF191" s="190" t="n">
         <v>290447.8180271229</v>
@@ -38927,25 +38927,25 @@
         <v>24983100</v>
       </c>
       <c r="CW191" s="102" t="n">
-        <v>347.8756485031444</v>
+        <v>347.8756485031441</v>
       </c>
       <c r="CX191" s="103" t="n">
-        <v>372.0859813342885</v>
+        <v>372.0859813342883</v>
       </c>
       <c r="CY191" s="103" t="n">
-        <v>407.7078036314259</v>
+        <v>407.7078036314253</v>
       </c>
       <c r="CZ191" s="103" t="n">
-        <v>446.7528256294976</v>
+        <v>446.7528256294972</v>
       </c>
       <c r="DA191" s="104" t="n">
-        <v>490.9710966467709</v>
+        <v>490.9710966467706</v>
       </c>
       <c r="DC191" s="396" t="n">
-        <v>0.009375041997798535</v>
+        <v>0.009375041997798528</v>
       </c>
       <c r="DD191" s="397" t="n">
-        <v>0.009757353086475153</v>
+        <v>0.00975735308647516</v>
       </c>
       <c r="DE191" s="397" t="n">
         <v>0.01026840829275268</v>
@@ -38954,7 +38954,7 @@
         <v>0.01058323089476837</v>
       </c>
       <c r="DG191" s="398" t="n">
-        <v>0.01076943133564507</v>
+        <v>0.01076943133564508</v>
       </c>
     </row>
     <row r="192">
@@ -39088,19 +39088,19 @@
         <v>13131.37395224124</v>
       </c>
       <c r="AS192" s="179" t="n">
-        <v>14239.36090163693</v>
+        <v>14239.36090163694</v>
       </c>
       <c r="AT192" s="195" t="n">
         <v>15645.96943166314</v>
       </c>
       <c r="AU192" s="190" t="n">
-        <v>68520.79892571838</v>
+        <v>68520.79892571835</v>
       </c>
       <c r="AV192" s="190" t="n">
-        <v>69762.95644698229</v>
+        <v>69762.95644698225</v>
       </c>
       <c r="AW192" s="190" t="n">
-        <v>71104.91150434417</v>
+        <v>71104.9115043442</v>
       </c>
       <c r="AX192" s="190" t="n">
         <v>72595.72034546072</v>
@@ -39138,7 +39138,7 @@
         <v>13131.37395224124</v>
       </c>
       <c r="BJ192" s="190" t="n">
-        <v>14239.36090163693</v>
+        <v>14239.36090163694</v>
       </c>
       <c r="BK192" s="198" t="n">
         <v>15645.96943166314</v>
@@ -39147,16 +39147,16 @@
         <v>68520.79892571813</v>
       </c>
       <c r="BM192" s="190" t="n">
-        <v>69762.95644698222</v>
+        <v>69762.95644698221</v>
       </c>
       <c r="BN192" s="190" t="n">
-        <v>71104.91150434423</v>
+        <v>71104.91150434424</v>
       </c>
       <c r="BO192" s="190" t="n">
         <v>72595.72034546094</v>
       </c>
       <c r="BP192" s="198" t="n">
-        <v>74541.05851927614</v>
+        <v>74541.05851927615</v>
       </c>
       <c r="BR192" s="111" t="inlineStr">
         <is>
@@ -39179,16 +39179,16 @@
         <v>58422.498776601</v>
       </c>
       <c r="BX192" s="197" t="n">
-        <v>11715.2177196184</v>
+        <v>11715.21771961839</v>
       </c>
       <c r="BY192" s="190" t="n">
         <v>12404.13892512474</v>
       </c>
       <c r="BZ192" s="190" t="n">
-        <v>13282.19313651668</v>
+        <v>13282.19313651669</v>
       </c>
       <c r="CA192" s="190" t="n">
-        <v>14452.7654678493</v>
+        <v>14452.76546784931</v>
       </c>
       <c r="CB192" s="198" t="n">
         <v>15925.64489480941</v>
@@ -39245,10 +39245,10 @@
         <v>157.7761316534094</v>
       </c>
       <c r="CZ192" s="103" t="n">
-        <v>174.2565804323907</v>
+        <v>174.2565804323906</v>
       </c>
       <c r="DA192" s="104" t="n">
-        <v>192.9148478659413</v>
+        <v>192.9148478659412</v>
       </c>
       <c r="DC192" s="396" t="n">
         <v>0.01079627364906017</v>
@@ -39388,7 +39388,7 @@
         <v>4584.024590086</v>
       </c>
       <c r="AP193" s="206" t="n">
-        <v>22158.11515268233</v>
+        <v>22158.11515268234</v>
       </c>
       <c r="AQ193" s="207" t="n">
         <v>24429.30328634562</v>
@@ -39397,25 +39397,25 @@
         <v>27032.12761083537</v>
       </c>
       <c r="AS193" s="207" t="n">
-        <v>29918.86350919777</v>
+        <v>29918.86350919776</v>
       </c>
       <c r="AT193" s="208" t="n">
         <v>33429.82145839032</v>
       </c>
       <c r="AU193" s="209" t="n">
-        <v>25193.517831171</v>
+        <v>25193.51783117101</v>
       </c>
       <c r="AV193" s="209" t="n">
-        <v>27812.80680003976</v>
+        <v>27812.80680003975</v>
       </c>
       <c r="AW193" s="209" t="n">
         <v>30783.02575880155</v>
       </c>
       <c r="AX193" s="209" t="n">
-        <v>34109.82162140912</v>
+        <v>34109.82162140911</v>
       </c>
       <c r="AY193" s="210" t="n">
-        <v>38013.84604847605</v>
+        <v>38013.84604847604</v>
       </c>
       <c r="BA193" s="111" t="inlineStr">
         <is>
@@ -39438,7 +39438,7 @@
         <v>4584.024590086</v>
       </c>
       <c r="BG193" s="211" t="n">
-        <v>22158.11515268233</v>
+        <v>22158.11515268234</v>
       </c>
       <c r="BH193" s="212" t="n">
         <v>24429.30328634562</v>
@@ -39447,7 +39447,7 @@
         <v>27032.12761083537</v>
       </c>
       <c r="BJ193" s="212" t="n">
-        <v>29918.86350919777</v>
+        <v>29918.86350919776</v>
       </c>
       <c r="BK193" s="213" t="n">
         <v>33429.82145839032</v>
@@ -39465,7 +39465,7 @@
         <v>34109.82162140877</v>
       </c>
       <c r="BP193" s="213" t="n">
-        <v>38013.84604847633</v>
+        <v>38013.84604847632</v>
       </c>
       <c r="BR193" s="111" t="inlineStr">
         <is>
@@ -39497,7 +39497,7 @@
         <v>26311.55657400407</v>
       </c>
       <c r="CA193" s="212" t="n">
-        <v>29150.45252801627</v>
+        <v>29150.45252801626</v>
       </c>
       <c r="CB193" s="213" t="n">
         <v>32577.4799466203</v>
@@ -39512,7 +39512,7 @@
         <v>29928.85639017706</v>
       </c>
       <c r="CF193" s="212" t="n">
-        <v>33159.26419276927</v>
+        <v>33159.26419276926</v>
       </c>
       <c r="CG193" s="213" t="n">
         <v>36920.4967527593</v>
@@ -39545,16 +39545,16 @@
         <v>837210</v>
       </c>
       <c r="CW193" s="132" t="n">
-        <v>663.9327169755792</v>
+        <v>663.9327169755794</v>
       </c>
       <c r="CX193" s="133" t="n">
-        <v>753.6182474419338</v>
+        <v>753.6182474419339</v>
       </c>
       <c r="CY193" s="133" t="n">
-        <v>854.1693686245004</v>
+        <v>854.1693686245003</v>
       </c>
       <c r="CZ193" s="133" t="n">
-        <v>950.5574286398273</v>
+        <v>950.5574286398277</v>
       </c>
       <c r="DA193" s="134" t="n">
         <v>1093.349295717359</v>
@@ -39566,13 +39566,13 @@
         <v>0.03031253335869558</v>
       </c>
       <c r="DE193" s="423" t="n">
-        <v>0.03101698224902301</v>
+        <v>0.031016982249023</v>
       </c>
       <c r="DF193" s="423" t="n">
-        <v>0.03114673314214131</v>
+        <v>0.03114673314214132</v>
       </c>
       <c r="DG193" s="424" t="n">
-        <v>0.03202818225054179</v>
+        <v>0.03202818225054181</v>
       </c>
     </row>
     <row r="194" ht="15.75" customHeight="1" thickBot="1">
@@ -39682,7 +39682,7 @@
         </is>
       </c>
       <c r="AK194" s="220" t="n">
-        <v>1419220.379298875</v>
+        <v>1419220.379298874</v>
       </c>
       <c r="AL194" s="209" t="n">
         <v>1435280.798812628</v>
@@ -39691,7 +39691,7 @@
         <v>1448679.168235343</v>
       </c>
       <c r="AN194" s="209" t="n">
-        <v>1458495.409587527</v>
+        <v>1458495.409587526</v>
       </c>
       <c r="AO194" s="210" t="n">
         <v>1470806.519645696</v>
@@ -39706,22 +39706,22 @@
         <v>246424.9517426564</v>
       </c>
       <c r="AS194" s="207" t="n">
-        <v>262895.1428126007</v>
+        <v>262895.1428126006</v>
       </c>
       <c r="AT194" s="208" t="n">
-        <v>284029.7828557849</v>
+        <v>284029.7828557848</v>
       </c>
       <c r="AU194" s="207" t="n">
-        <v>1641593.6984478</v>
+        <v>1641593.698447799</v>
       </c>
       <c r="AV194" s="207" t="n">
-        <v>1668764.900469312</v>
+        <v>1668764.900469311</v>
       </c>
       <c r="AW194" s="207" t="n">
-        <v>1695104.119977999</v>
+        <v>1695104.119978</v>
       </c>
       <c r="AX194" s="207" t="n">
-        <v>1721390.552400128</v>
+        <v>1721390.552400127</v>
       </c>
       <c r="AY194" s="208" t="n">
         <v>1754836.302501481</v>
@@ -39732,7 +39732,7 @@
         </is>
       </c>
       <c r="BB194" s="221" t="n">
-        <v>1419220.379298875</v>
+        <v>1419220.379298874</v>
       </c>
       <c r="BC194" s="222" t="n">
         <v>1435280.798812628</v>
@@ -39741,7 +39741,7 @@
         <v>1448679.168235343</v>
       </c>
       <c r="BE194" s="222" t="n">
-        <v>1458495.409587527</v>
+        <v>1458495.409587526</v>
       </c>
       <c r="BF194" s="214" t="n">
         <v>1470806.519645696</v>
@@ -39756,13 +39756,13 @@
         <v>246424.9517426564</v>
       </c>
       <c r="BJ194" s="222" t="n">
-        <v>262895.1428126007</v>
+        <v>262895.1428126006</v>
       </c>
       <c r="BK194" s="214" t="n">
-        <v>284029.7828557849</v>
+        <v>284029.7828557848</v>
       </c>
       <c r="BL194" s="222" t="n">
-        <v>1641593.6984478</v>
+        <v>1641593.698447799</v>
       </c>
       <c r="BM194" s="222" t="n">
         <v>1668764.900469312</v>
@@ -39771,7 +39771,7 @@
         <v>1695104.119977999</v>
       </c>
       <c r="BO194" s="222" t="n">
-        <v>1721390.552400128</v>
+        <v>1721390.552400127</v>
       </c>
       <c r="BP194" s="214" t="n">
         <v>1754836.302501481</v>
@@ -39782,7 +39782,7 @@
         </is>
       </c>
       <c r="BS194" s="221" t="n">
-        <v>1415379.050044507</v>
+        <v>1415379.050044506</v>
       </c>
       <c r="BT194" s="222" t="n">
         <v>1429707.124045061</v>
@@ -39791,7 +39791,7 @@
         <v>1441322.416354639</v>
       </c>
       <c r="BV194" s="222" t="n">
-        <v>1449303.18403771</v>
+        <v>1449303.184037709</v>
       </c>
       <c r="BW194" s="214" t="n">
         <v>1459680.857487838</v>
@@ -39803,16 +39803,16 @@
         <v>235625.9003085984</v>
       </c>
       <c r="BZ194" s="222" t="n">
-        <v>249983.1842321431</v>
+        <v>249983.184232143</v>
       </c>
       <c r="CA194" s="222" t="n">
         <v>267900.6531995418</v>
       </c>
       <c r="CB194" s="214" t="n">
-        <v>290498.6552000813</v>
+        <v>290498.6552000812</v>
       </c>
       <c r="CC194" s="222" t="n">
-        <v>1638486.346796772</v>
+        <v>1638486.346796771</v>
       </c>
       <c r="CD194" s="222" t="n">
         <v>1665333.024353659</v>
@@ -39821,7 +39821,7 @@
         <v>1691305.600586782</v>
       </c>
       <c r="CF194" s="222" t="n">
-        <v>1717203.837237252</v>
+        <v>1717203.837237251</v>
       </c>
       <c r="CG194" s="214" t="n">
         <v>1750179.512687919</v>
@@ -39854,19 +39854,19 @@
         <v>60466650</v>
       </c>
       <c r="CW194" s="132" t="n">
-        <v>3107.351651028078</v>
+        <v>3107.351651028073</v>
       </c>
       <c r="CX194" s="133" t="n">
-        <v>3431.876115652925</v>
+        <v>3431.87611565292</v>
       </c>
       <c r="CY194" s="133" t="n">
-        <v>3798.519391217832</v>
+        <v>3798.519391217827</v>
       </c>
       <c r="CZ194" s="133" t="n">
-        <v>4186.715162875507</v>
+        <v>4186.715162875502</v>
       </c>
       <c r="DA194" s="134" t="n">
-        <v>4656.789813562891</v>
+        <v>4656.789813562885</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" thickBot="1">
@@ -40648,7 +40648,7 @@
         <v>1.000000000000004</v>
       </c>
       <c r="CL198" s="397" t="n">
-        <v>1.000000000000001</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="CM198" s="398" t="n">
         <v>1</v>
@@ -40666,7 +40666,7 @@
         <v>1.000000000000606</v>
       </c>
       <c r="CR198" s="398" t="n">
-        <v>0.9999999999977438</v>
+        <v>0.9999999999977436</v>
       </c>
       <c r="CS198" s="465" t="n"/>
       <c r="CT198" s="396" t="n">
@@ -40679,7 +40679,7 @@
         <v>1.000000000000004</v>
       </c>
       <c r="CW198" s="397" t="n">
-        <v>1.000000000000001</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="CX198" s="398" t="n">
         <v>1</v>
@@ -40822,19 +40822,19 @@
         <v>0.00634</v>
       </c>
       <c r="AP199" s="233" t="n">
-        <v>2958.430622030667</v>
+        <v>2958.430622030665</v>
       </c>
       <c r="AQ199" s="190" t="n">
-        <v>4292.646327614397</v>
+        <v>4292.646327614395</v>
       </c>
       <c r="AR199" s="190" t="n">
-        <v>5662.813186259974</v>
+        <v>5662.813186259977</v>
       </c>
       <c r="AS199" s="190" t="n">
-        <v>7069.040947359897</v>
+        <v>7069.040947359893</v>
       </c>
       <c r="AT199" s="196" t="n">
-        <v>8545.906703861468</v>
+        <v>8545.906703861472</v>
       </c>
       <c r="AU199" s="190" t="n">
         <v>159657.3891568753</v>
@@ -40881,7 +40881,7 @@
         <v>5662.813186259977</v>
       </c>
       <c r="BJ199" s="190" t="n">
-        <v>7069.040947359898</v>
+        <v>7069.040947359893</v>
       </c>
       <c r="BK199" s="198" t="n">
         <v>8545.906703861468</v>
@@ -40925,16 +40925,16 @@
         <v>0.6466114449749487</v>
       </c>
       <c r="BY199" s="463" t="n">
-        <v>0.6803881747816335</v>
+        <v>0.6803881747816336</v>
       </c>
       <c r="BZ199" s="463" t="n">
-        <v>0.7041227667519322</v>
+        <v>0.7041227667519324</v>
       </c>
       <c r="CA199" s="463" t="n">
-        <v>0.7216460584379011</v>
+        <v>0.7216460584379013</v>
       </c>
       <c r="CB199" s="464" t="n">
-        <v>0.74335960479444</v>
+        <v>0.7433596047944403</v>
       </c>
       <c r="CC199" s="199" t="n">
         <v>101965.784394293</v>
@@ -40952,7 +40952,7 @@
         <v>150601.7080481383</v>
       </c>
       <c r="CI199" s="396" t="n">
-        <v>0.9999999999999792</v>
+        <v>0.9999999999999832</v>
       </c>
       <c r="CJ199" s="397" t="n">
         <v>0.9999999999999934</v>
@@ -40983,7 +40983,7 @@
       </c>
       <c r="CS199" s="465" t="n"/>
       <c r="CT199" s="396" t="n">
-        <v>0.9999999999999792</v>
+        <v>0.9999999999999832</v>
       </c>
       <c r="CU199" s="397" t="n">
         <v>0.9999999999999934</v>
@@ -40992,7 +40992,7 @@
         <v>1.000000000000013</v>
       </c>
       <c r="CW199" s="397" t="n">
-        <v>1.000000000000001</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="CX199" s="398" t="n">
         <v>0.9999999999999859</v>
@@ -41135,34 +41135,34 @@
         <v>0.00634</v>
       </c>
       <c r="AP200" s="233" t="n">
-        <v>663.6071311260645</v>
+        <v>663.6071311260641</v>
       </c>
       <c r="AQ200" s="190" t="n">
-        <v>955.1253907080516</v>
+        <v>955.1253907080513</v>
       </c>
       <c r="AR200" s="190" t="n">
         <v>1251.74504672249</v>
       </c>
       <c r="AS200" s="190" t="n">
-        <v>1553.377008353701</v>
+        <v>1553.3770083537</v>
       </c>
       <c r="AT200" s="196" t="n">
         <v>1866.157359038367</v>
       </c>
       <c r="AU200" s="190" t="n">
-        <v>32494.30532862726</v>
+        <v>32494.30532862729</v>
       </c>
       <c r="AV200" s="190" t="n">
-        <v>33337.80054782045</v>
+        <v>33337.80054782044</v>
       </c>
       <c r="AW200" s="190" t="n">
-        <v>34768.75561014748</v>
+        <v>34768.75561014745</v>
       </c>
       <c r="AX200" s="190" t="n">
-        <v>36993.53942123242</v>
+        <v>36993.53942123243</v>
       </c>
       <c r="AY200" s="196" t="n">
-        <v>39890.46707731527</v>
+        <v>39890.46707731523</v>
       </c>
       <c r="BA200" s="101" t="inlineStr">
         <is>
@@ -41185,13 +41185,13 @@
         <v>0.00634</v>
       </c>
       <c r="BG200" s="197" t="n">
-        <v>663.6071311260655</v>
+        <v>663.6071311260633</v>
       </c>
       <c r="BH200" s="190" t="n">
         <v>955.1253907080529</v>
       </c>
       <c r="BI200" s="190" t="n">
-        <v>1251.74504672249</v>
+        <v>1251.745046722489</v>
       </c>
       <c r="BJ200" s="190" t="n">
         <v>1553.377008353699</v>
@@ -41200,19 +41200,19 @@
         <v>1866.15735903837</v>
       </c>
       <c r="BL200" s="197" t="n">
-        <v>32494.30532862726</v>
+        <v>32494.30532862729</v>
       </c>
       <c r="BM200" s="190" t="n">
-        <v>33337.80054782045</v>
+        <v>33337.80054782044</v>
       </c>
       <c r="BN200" s="190" t="n">
-        <v>34768.75561014748</v>
+        <v>34768.75561014745</v>
       </c>
       <c r="BO200" s="190" t="n">
-        <v>36993.53942123242</v>
+        <v>36993.53942123243</v>
       </c>
       <c r="BP200" s="198" t="n">
-        <v>39890.46707731527</v>
+        <v>39890.46707731524</v>
       </c>
       <c r="BR200" s="101" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         </is>
       </c>
       <c r="BS200" s="335" t="n">
-        <v>19760.61072108875</v>
+        <v>19760.61072108874</v>
       </c>
       <c r="BT200" s="336" t="n">
         <v>21206.57507523217</v>
@@ -41235,28 +41235,28 @@
         <v>27292.71916327555</v>
       </c>
       <c r="BX200" s="462" t="n">
-        <v>0.61670004845085</v>
+        <v>0.6167000484508495</v>
       </c>
       <c r="BY200" s="463" t="n">
-        <v>0.6509786380063289</v>
+        <v>0.6509786380063293</v>
       </c>
       <c r="BZ200" s="463" t="n">
-        <v>0.6763319833413172</v>
+        <v>0.6763319833413178</v>
       </c>
       <c r="CA200" s="463" t="n">
-        <v>0.6929421555046226</v>
+        <v>0.6929421555046225</v>
       </c>
       <c r="CB200" s="464" t="n">
-        <v>0.7142533081465158</v>
+        <v>0.7142533081465164</v>
       </c>
       <c r="CC200" s="197" t="n">
-        <v>19824.70474125439</v>
+        <v>19824.70474125438</v>
       </c>
       <c r="CD200" s="190" t="n">
         <v>21459.97596939656</v>
       </c>
       <c r="CE200" s="190" t="n">
-        <v>23239.47561266682</v>
+        <v>23239.47561266683</v>
       </c>
       <c r="CF200" s="190" t="n">
         <v>25324.80908032454</v>
@@ -41448,13 +41448,13 @@
         <v>0.00634</v>
       </c>
       <c r="AP201" s="233" t="n">
-        <v>160.338669486181</v>
+        <v>160.3386694861809</v>
       </c>
       <c r="AQ201" s="190" t="n">
-        <v>233.0082745329209</v>
+        <v>233.0082745329207</v>
       </c>
       <c r="AR201" s="190" t="n">
-        <v>308.5953159288537</v>
+        <v>308.5953159288538</v>
       </c>
       <c r="AS201" s="190" t="n">
         <v>387.6611466447603</v>
@@ -41469,13 +41469,13 @@
         <v>12547.15549251914</v>
       </c>
       <c r="AW201" s="190" t="n">
-        <v>13439.96926817009</v>
+        <v>13439.9692681701</v>
       </c>
       <c r="AX201" s="190" t="n">
-        <v>14627.02204828169</v>
+        <v>14627.0220482817</v>
       </c>
       <c r="AY201" s="196" t="n">
-        <v>16118.55974267535</v>
+        <v>16118.55974267536</v>
       </c>
       <c r="BA201" s="111" t="inlineStr">
         <is>
@@ -41504,13 +41504,13 @@
         <v>233.0082745329206</v>
       </c>
       <c r="BI201" s="190" t="n">
-        <v>308.5953159288539</v>
+        <v>308.595315928854</v>
       </c>
       <c r="BJ201" s="190" t="n">
         <v>387.6611466447615</v>
       </c>
       <c r="BK201" s="198" t="n">
-        <v>472.5903110122107</v>
+        <v>472.5903110122108</v>
       </c>
       <c r="BL201" s="197" t="n">
         <v>11845.88593338331</v>
@@ -41519,10 +41519,10 @@
         <v>12547.15549251914</v>
       </c>
       <c r="BN201" s="190" t="n">
-        <v>13439.96926817009</v>
+        <v>13439.9692681701</v>
       </c>
       <c r="BO201" s="190" t="n">
-        <v>14627.02204828169</v>
+        <v>14627.0220482817</v>
       </c>
       <c r="BP201" s="198" t="n">
         <v>16118.55974267535</v>
@@ -41533,7 +41533,7 @@
         </is>
       </c>
       <c r="BS201" s="335" t="n">
-        <v>7709.422594120959</v>
+        <v>7709.422594120958</v>
       </c>
       <c r="BT201" s="336" t="n">
         <v>8517.104467793557</v>
@@ -41548,19 +41548,19 @@
         <v>12045.55205274821</v>
       </c>
       <c r="BX201" s="462" t="n">
-        <v>0.6559448055656167</v>
+        <v>0.6559448055656169</v>
       </c>
       <c r="BY201" s="463" t="n">
-        <v>0.6880968190885129</v>
+        <v>0.6880968190885131</v>
       </c>
       <c r="BZ201" s="463" t="n">
-        <v>0.7144401067455742</v>
+        <v>0.7144401067455739</v>
       </c>
       <c r="CA201" s="463" t="n">
-        <v>0.7384979676447369</v>
+        <v>0.7384979676447364</v>
       </c>
       <c r="CB201" s="464" t="n">
-        <v>0.7670945895259741</v>
+        <v>0.7670945895259742</v>
       </c>
       <c r="CC201" s="197" t="n">
         <v>7684.536209253957</v>
@@ -41596,7 +41596,7 @@
         <v>1.000000000014788</v>
       </c>
       <c r="CO201" s="423" t="n">
-        <v>0.9999999999853941</v>
+        <v>0.9999999999853939</v>
       </c>
       <c r="CP201" s="423" t="n">
         <v>1.000000000006299</v>
@@ -41760,31 +41760,31 @@
         <v>0.00634</v>
       </c>
       <c r="AP202" s="220" t="n">
-        <v>58.95283172494015</v>
+        <v>58.95283172494016</v>
       </c>
       <c r="AQ202" s="209" t="n">
-        <v>92.8947747121328</v>
+        <v>92.89477471213277</v>
       </c>
       <c r="AR202" s="209" t="n">
         <v>133.5983317931987</v>
       </c>
       <c r="AS202" s="209" t="n">
-        <v>182.1464474583247</v>
+        <v>182.1464474583246</v>
       </c>
       <c r="AT202" s="210" t="n">
-        <v>241.0077839473382</v>
+        <v>241.0077839473381</v>
       </c>
       <c r="AU202" s="209" t="n">
-        <v>22217.06798440727</v>
+        <v>22217.06798440728</v>
       </c>
       <c r="AV202" s="209" t="n">
-        <v>24522.19806105776</v>
+        <v>24522.19806105775</v>
       </c>
       <c r="AW202" s="209" t="n">
         <v>27165.72594262857</v>
       </c>
       <c r="AX202" s="209" t="n">
-        <v>30101.0099566561</v>
+        <v>30101.00995665609</v>
       </c>
       <c r="AY202" s="210" t="n">
         <v>33670.82924233766</v>
@@ -41810,16 +41810,16 @@
         <v>0.00634</v>
       </c>
       <c r="BG202" s="211" t="n">
-        <v>58.95283172494093</v>
+        <v>58.95283172494094</v>
       </c>
       <c r="BH202" s="212" t="n">
-        <v>92.89477471213235</v>
+        <v>92.89477471213233</v>
       </c>
       <c r="BI202" s="212" t="n">
         <v>133.598331793198</v>
       </c>
       <c r="BJ202" s="212" t="n">
-        <v>182.1464474583229</v>
+        <v>182.1464474583228</v>
       </c>
       <c r="BK202" s="213" t="n">
         <v>241.0077839473399</v>
@@ -41828,7 +41828,7 @@
         <v>22217.06798440728</v>
       </c>
       <c r="BM202" s="212" t="n">
-        <v>24522.19806105776</v>
+        <v>24522.19806105775</v>
       </c>
       <c r="BN202" s="212" t="n">
         <v>27165.72594262857</v>
@@ -41848,7 +41848,7 @@
         <v>15709.70744138703</v>
       </c>
       <c r="BT202" s="272" t="n">
-        <v>17732.88691759676</v>
+        <v>17732.88691759677</v>
       </c>
       <c r="BU202" s="272" t="n">
         <v>19920.31722773356</v>
@@ -41857,19 +41857,19 @@
         <v>22371.86578071988</v>
       </c>
       <c r="BW202" s="273" t="n">
-        <v>25652.86382685494</v>
+        <v>25652.86382685493</v>
       </c>
       <c r="BX202" s="466" t="n">
-        <v>0.7000174703485901</v>
+        <v>0.70001747034859</v>
       </c>
       <c r="BY202" s="467" t="n">
-        <v>0.7171947087884049</v>
+        <v>0.7171947087884051</v>
       </c>
       <c r="BZ202" s="467" t="n">
-        <v>0.7283718889102292</v>
+        <v>0.7283718889102293</v>
       </c>
       <c r="CA202" s="467" t="n">
-        <v>0.7395256918955588</v>
+        <v>0.7395256918955592</v>
       </c>
       <c r="CB202" s="468" t="n">
         <v>0.7595570753068652</v>
@@ -41884,7 +41884,7 @@
         <v>19164.5981619757</v>
       </c>
       <c r="CF202" s="212" t="n">
-        <v>21557.50857484987</v>
+        <v>21557.50857484988</v>
       </c>
       <c r="CG202" s="213" t="n">
         <v>24744.45538912297</v>
@@ -41931,7 +41931,7 @@
         <v>7356.815408947481</v>
       </c>
       <c r="K203" s="215" t="n">
-        <v>9192.319349132102</v>
+        <v>9192.3193491321</v>
       </c>
       <c r="L203" s="216" t="n">
         <v>11125.79579552732</v>
@@ -41981,7 +41981,7 @@
         <v>7356.815408947481</v>
       </c>
       <c r="AB203" s="218" t="n">
-        <v>9192.319349132102</v>
+        <v>9192.3193491321</v>
       </c>
       <c r="AC203" s="219" t="n">
         <v>11125.79579552732</v>
@@ -42022,16 +42022,16 @@
         <v>0.02536</v>
       </c>
       <c r="AP203" s="206" t="n">
-        <v>3841.329254367852</v>
+        <v>3841.32925436785</v>
       </c>
       <c r="AQ203" s="207" t="n">
-        <v>5573.674767567501</v>
+        <v>5573.6747675675</v>
       </c>
       <c r="AR203" s="207" t="n">
-        <v>7356.751880704516</v>
+        <v>7356.75188070452</v>
       </c>
       <c r="AS203" s="207" t="n">
-        <v>9192.225549816681</v>
+        <v>9192.225549816678</v>
       </c>
       <c r="AT203" s="208" t="n">
         <v>11125.66215785939</v>
@@ -42049,7 +42049,7 @@
         <v>272087.3683624173</v>
       </c>
       <c r="AY203" s="208" t="n">
-        <v>295155.4450136442</v>
+        <v>295155.4450136441</v>
       </c>
       <c r="BA203" s="155" t="inlineStr">
         <is>
@@ -42072,7 +42072,7 @@
         <v>0.02536</v>
       </c>
       <c r="BG203" s="221" t="n">
-        <v>3841.329254367853</v>
+        <v>3841.32925436785</v>
       </c>
       <c r="BH203" s="222" t="n">
         <v>5573.674767567501</v>
@@ -42081,7 +42081,7 @@
         <v>7356.751880704518</v>
       </c>
       <c r="BJ203" s="222" t="n">
-        <v>9192.225549816681</v>
+        <v>9192.225549816678</v>
       </c>
       <c r="BK203" s="214" t="n">
         <v>11125.66215785939</v>
@@ -42099,7 +42099,7 @@
         <v>272087.3683624173</v>
       </c>
       <c r="BP203" s="214" t="n">
-        <v>295155.4450136442</v>
+        <v>295155.4450136441</v>
       </c>
       <c r="BR203" s="155" t="inlineStr">
         <is>
@@ -42125,25 +42125,25 @@
         <v>0.6479510023973353</v>
       </c>
       <c r="BY203" s="467" t="n">
-        <v>0.6803922139863258</v>
+        <v>0.680392213986326</v>
       </c>
       <c r="BZ203" s="467" t="n">
-        <v>0.7034033128177946</v>
+        <v>0.7034033128177949</v>
       </c>
       <c r="CA203" s="467" t="n">
-        <v>0.7205849213567084</v>
+        <v>0.7205849213567086</v>
       </c>
       <c r="CB203" s="468" t="n">
-        <v>0.7425296329365555</v>
+        <v>0.7425296329365557</v>
       </c>
       <c r="CC203" s="212" t="n">
         <v>144562.5965727899</v>
       </c>
       <c r="CD203" s="212" t="n">
-        <v>160318.0279834885</v>
+        <v>160318.0279834886</v>
       </c>
       <c r="CE203" s="212" t="n">
-        <v>175838.9999376305</v>
+        <v>175838.9999376306</v>
       </c>
       <c r="CF203" s="212" t="n">
         <v>193045.1711172027</v>
@@ -42931,13 +42931,13 @@
         <v>1126388.412234446</v>
       </c>
       <c r="AN208" s="190" t="n">
-        <v>1133424.642644258</v>
+        <v>1133424.642644257</v>
       </c>
       <c r="AO208" s="196" t="n">
         <v>1142459.222383301</v>
       </c>
       <c r="AP208" s="473" t="n">
-        <v>0.876057406842331</v>
+        <v>0.8760574068423309</v>
       </c>
       <c r="AQ208" s="463" t="n">
         <v>0.8721171981272499</v>
@@ -42952,19 +42952,19 @@
         <v>0.8539026660699781</v>
       </c>
       <c r="AU208" s="463" t="n">
-        <v>0.8737174068423307</v>
+        <v>0.8737174068423312</v>
       </c>
       <c r="AV208" s="463" t="n">
-        <v>0.8687771981272497</v>
+        <v>0.8687771981272501</v>
       </c>
       <c r="AW208" s="463" t="n">
-        <v>0.8632680521686326</v>
+        <v>0.8632680521686322</v>
       </c>
       <c r="AX208" s="463" t="n">
-        <v>0.8561964256241555</v>
+        <v>0.8561964256241552</v>
       </c>
       <c r="AY208" s="474" t="n">
-        <v>0.8475626660699781</v>
+        <v>0.8475626660699779</v>
       </c>
       <c r="BA208" s="83" t="inlineStr">
         <is>
@@ -42981,7 +42981,7 @@
         <v>1126388.412234446</v>
       </c>
       <c r="BE208" s="190" t="n">
-        <v>1133424.642644258</v>
+        <v>1133424.642644257</v>
       </c>
       <c r="BF208" s="198" t="n">
         <v>1142459.222383301</v>
@@ -42996,7 +42996,7 @@
         <v>0.8676080521686322</v>
       </c>
       <c r="BJ208" s="463" t="n">
-        <v>0.8615364256241554</v>
+        <v>0.8615364256241553</v>
       </c>
       <c r="BK208" s="464" t="n">
         <v>0.8539026660699781</v>
@@ -43011,7 +43011,7 @@
         <v>0.8632680521686322</v>
       </c>
       <c r="BO208" s="476" t="n">
-        <v>0.8561964256241553</v>
+        <v>0.8561964256241552</v>
       </c>
       <c r="BP208" s="477" t="n">
         <v>0.8475626660699784</v>
@@ -43046,7 +43046,7 @@
         <v>0.8648448124616638</v>
       </c>
       <c r="CA208" s="463" t="n">
-        <v>0.8578911898737479</v>
+        <v>0.8578911898737478</v>
       </c>
       <c r="CB208" s="464" t="n">
         <v>0.8493771662096562</v>
@@ -43177,7 +43177,7 @@
         </is>
       </c>
       <c r="AK209" s="233" t="n">
-        <v>251098.4857508879</v>
+        <v>251098.4857508869</v>
       </c>
       <c r="AL209" s="190" t="n">
         <v>252627.885292914</v>
@@ -43192,34 +43192,34 @@
         <v>254456.1195217966</v>
       </c>
       <c r="AP209" s="473" t="n">
-        <v>0.8877591419854661</v>
+        <v>0.8877591419854659</v>
       </c>
       <c r="AQ209" s="463" t="n">
-        <v>0.8867602766328138</v>
+        <v>0.8867602766328139</v>
       </c>
       <c r="AR209" s="463" t="n">
-        <v>0.8837911711924564</v>
+        <v>0.8837911711924566</v>
       </c>
       <c r="AS209" s="463" t="n">
         <v>0.8781683607604417</v>
       </c>
       <c r="AT209" s="474" t="n">
-        <v>0.8708179015846222</v>
+        <v>0.8708179015846226</v>
       </c>
       <c r="AU209" s="463" t="n">
-        <v>0.8854191419854677</v>
+        <v>0.8854191419854646</v>
       </c>
       <c r="AV209" s="463" t="n">
-        <v>0.8834202766328153</v>
+        <v>0.8834202766328154</v>
       </c>
       <c r="AW209" s="463" t="n">
         <v>0.8794511711924559</v>
       </c>
       <c r="AX209" s="463" t="n">
-        <v>0.8728283607604408</v>
+        <v>0.8728283607604411</v>
       </c>
       <c r="AY209" s="474" t="n">
-        <v>0.8644779015846236</v>
+        <v>0.8644779015846239</v>
       </c>
       <c r="BA209" s="101" t="inlineStr">
         <is>
@@ -43227,7 +43227,7 @@
         </is>
       </c>
       <c r="BB209" s="197" t="n">
-        <v>251098.485750888</v>
+        <v>251098.485750887</v>
       </c>
       <c r="BC209" s="190" t="n">
         <v>252627.885292914</v>
@@ -43242,13 +43242,13 @@
         <v>254456.119521797</v>
       </c>
       <c r="BG209" s="462" t="n">
-        <v>0.8877591419854662</v>
+        <v>0.8877591419854657</v>
       </c>
       <c r="BH209" s="463" t="n">
         <v>0.886760276632814</v>
       </c>
       <c r="BI209" s="463" t="n">
-        <v>0.8837911711924564</v>
+        <v>0.8837911711924565</v>
       </c>
       <c r="BJ209" s="463" t="n">
         <v>0.8781683607604417</v>
@@ -43257,13 +43257,13 @@
         <v>0.8708179015846226</v>
       </c>
       <c r="BL209" s="462" t="n">
-        <v>0.8854191419854666</v>
+        <v>0.885419141985466</v>
       </c>
       <c r="BM209" s="463" t="n">
         <v>0.8834202766328141</v>
       </c>
       <c r="BN209" s="463" t="n">
-        <v>0.8794511711924581</v>
+        <v>0.8794511711924583</v>
       </c>
       <c r="BO209" s="463" t="n">
         <v>0.8728283607604407</v>
@@ -43292,19 +43292,19 @@
         <v>0</v>
       </c>
       <c r="BX209" s="462" t="n">
-        <v>0.8865065957805206</v>
+        <v>0.88650659578052</v>
       </c>
       <c r="BY209" s="463" t="n">
-        <v>0.8845712418530547</v>
+        <v>0.8845712418530548</v>
       </c>
       <c r="BZ209" s="463" t="n">
-        <v>0.8806961127128159</v>
+        <v>0.880696112712816</v>
       </c>
       <c r="CA209" s="463" t="n">
         <v>0.8741709032491679</v>
       </c>
       <c r="CB209" s="464" t="n">
-        <v>0.8659222628320405</v>
+        <v>0.8659222628320408</v>
       </c>
       <c r="CC209" s="482" t="n">
         <v>0</v>
@@ -43447,13 +43447,13 @@
         <v>58422.49877660078</v>
       </c>
       <c r="AP210" s="473" t="n">
-        <v>0.8294598509196438</v>
+        <v>0.8294598509196437</v>
       </c>
       <c r="AQ210" s="463" t="n">
         <v>0.8234858749522092</v>
       </c>
       <c r="AR210" s="463" t="n">
-        <v>0.8153239533750216</v>
+        <v>0.8153239533750214</v>
       </c>
       <c r="AS210" s="463" t="n">
         <v>0.8038539898236949</v>
@@ -43462,13 +43462,13 @@
         <v>0.7901026663363379</v>
       </c>
       <c r="AU210" s="463" t="n">
-        <v>0.82711985091964</v>
+        <v>0.8271198509196404</v>
       </c>
       <c r="AV210" s="463" t="n">
-        <v>0.820145874952208</v>
+        <v>0.8201458749522086</v>
       </c>
       <c r="AW210" s="463" t="n">
-        <v>0.8109839533750224</v>
+        <v>0.810983953375022</v>
       </c>
       <c r="AX210" s="463" t="n">
         <v>0.7985139898236979</v>
@@ -43500,31 +43500,31 @@
         <v>0.829459850919643</v>
       </c>
       <c r="BH210" s="463" t="n">
-        <v>0.8234858749522089</v>
+        <v>0.823485874952209</v>
       </c>
       <c r="BI210" s="463" t="n">
-        <v>0.8153239533750217</v>
+        <v>0.8153239533750216</v>
       </c>
       <c r="BJ210" s="463" t="n">
         <v>0.8038539898236955</v>
       </c>
       <c r="BK210" s="464" t="n">
-        <v>0.790102666336337</v>
+        <v>0.7901026663363369</v>
       </c>
       <c r="BL210" s="462" t="n">
         <v>0.8271198509196457</v>
       </c>
       <c r="BM210" s="463" t="n">
-        <v>0.8201458749522077</v>
+        <v>0.8201458749522079</v>
       </c>
       <c r="BN210" s="463" t="n">
-        <v>0.8109839533750197</v>
+        <v>0.8109839533750195</v>
       </c>
       <c r="BO210" s="463" t="n">
         <v>0.7985139898236923</v>
       </c>
       <c r="BP210" s="464" t="n">
-        <v>0.7837626663363398</v>
+        <v>0.7837626663363396</v>
       </c>
       <c r="BR210" s="111" t="inlineStr">
         <is>
@@ -43714,10 +43714,10 @@
         <v>0.1228666088825536</v>
       </c>
       <c r="AT211" s="491" t="n">
-        <v>0.1205882873372004</v>
+        <v>0.1205882873372003</v>
       </c>
       <c r="AU211" s="490" t="n">
-        <v>0.118143479077043</v>
+        <v>0.1181434790770429</v>
       </c>
       <c r="AV211" s="490" t="n">
         <v>0.1183127169666732</v>
@@ -43726,7 +43726,7 @@
         <v>0.1175095601230342</v>
       </c>
       <c r="AX211" s="490" t="n">
-        <v>0.1175266088825435</v>
+        <v>0.1175266088825436</v>
       </c>
       <c r="AY211" s="491" t="n">
         <v>0.1142482873372075</v>
@@ -43752,7 +43752,7 @@
         <v>4343.016806139</v>
       </c>
       <c r="BG211" s="466" t="n">
-        <v>0.1204834790770414</v>
+        <v>0.1204834790770413</v>
       </c>
       <c r="BH211" s="467" t="n">
         <v>0.1216527169666738</v>
@@ -43761,10 +43761,10 @@
         <v>0.1218495601230349</v>
       </c>
       <c r="BJ211" s="467" t="n">
-        <v>0.1228666088825447</v>
+        <v>0.1228666088825448</v>
       </c>
       <c r="BK211" s="468" t="n">
-        <v>0.1205882873372066</v>
+        <v>0.1205882873372067</v>
       </c>
       <c r="BL211" s="467" t="n">
         <v>0.118143479077039</v>
@@ -43776,7 +43776,7 @@
         <v>0.1175095601230414</v>
       </c>
       <c r="BO211" s="467" t="n">
-        <v>0.1175266088825542</v>
+        <v>0.1175266088825543</v>
       </c>
       <c r="BP211" s="468" t="n">
         <v>0.1142482873372156</v>
@@ -43811,7 +43811,7 @@
         <v>0.120863282212154</v>
       </c>
       <c r="CA211" s="467" t="n">
-        <v>0.1208956761358765</v>
+        <v>0.1208956761358766</v>
       </c>
       <c r="CB211" s="468" t="n">
         <v>0.1176315918830214</v>
@@ -43875,16 +43875,16 @@
         <v>0.8621930108418661</v>
       </c>
       <c r="N212" s="495" t="n">
-        <v>0.856739395836739</v>
+        <v>0.8567393958367389</v>
       </c>
       <c r="O212" s="495" t="n">
         <v>0.850278097729836</v>
       </c>
       <c r="P212" s="495" t="n">
-        <v>0.8419288112097916</v>
+        <v>0.8419288112097917</v>
       </c>
       <c r="Q212" s="496" t="n">
-        <v>0.8317945034486746</v>
+        <v>0.8317945034486744</v>
       </c>
       <c r="S212" s="143" t="inlineStr">
         <is>
@@ -43925,16 +43925,16 @@
         <v>0.8621930108418661</v>
       </c>
       <c r="AE212" s="498" t="n">
-        <v>0.856739395836739</v>
+        <v>0.8567393958367389</v>
       </c>
       <c r="AF212" s="498" t="n">
         <v>0.850278097729836</v>
       </c>
       <c r="AG212" s="498" t="n">
-        <v>0.8419288112097916</v>
+        <v>0.8419288112097917</v>
       </c>
       <c r="AH212" s="499" t="n">
-        <v>0.8317945034486746</v>
+        <v>0.8317945034486744</v>
       </c>
       <c r="AJ212" s="150" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         </is>
       </c>
       <c r="AK212" s="206" t="n">
-        <v>1415379.050044507</v>
+        <v>1415379.050044506</v>
       </c>
       <c r="AL212" s="207" t="n">
         <v>1429707.12404506</v>
@@ -43951,40 +43951,40 @@
         <v>1441322.416354639</v>
       </c>
       <c r="AN212" s="207" t="n">
-        <v>1449303.18403771</v>
+        <v>1449303.184037709</v>
       </c>
       <c r="AO212" s="208" t="n">
         <v>1459680.857487837</v>
       </c>
       <c r="AP212" s="500" t="n">
-        <v>0.8645381501164455</v>
+        <v>0.8645381501164453</v>
       </c>
       <c r="AQ212" s="501" t="n">
-        <v>0.8600856827759139</v>
+        <v>0.8600856827759141</v>
       </c>
       <c r="AR212" s="501" t="n">
-        <v>0.8546254776692687</v>
+        <v>0.8546254776692684</v>
       </c>
       <c r="AS212" s="501" t="n">
-        <v>0.8472774569106079</v>
+        <v>0.8472774569106077</v>
       </c>
       <c r="AT212" s="502" t="n">
-        <v>0.8381445708349512</v>
+        <v>0.838144570834951</v>
       </c>
       <c r="AU212" s="501" t="n">
-        <v>0.8621981501164454</v>
+        <v>0.8621981501164453</v>
       </c>
       <c r="AV212" s="501" t="n">
-        <v>0.8567456827759139</v>
+        <v>0.8567456827759141</v>
       </c>
       <c r="AW212" s="501" t="n">
-        <v>0.8502854776692688</v>
+        <v>0.8502854776692685</v>
       </c>
       <c r="AX212" s="501" t="n">
         <v>0.8419374569106077</v>
       </c>
       <c r="AY212" s="502" t="n">
-        <v>0.8318045708349512</v>
+        <v>0.831804570834951</v>
       </c>
       <c r="BA212" s="155" t="inlineStr">
         <is>
@@ -43992,7 +43992,7 @@
         </is>
       </c>
       <c r="BB212" s="221" t="n">
-        <v>1415379.050044507</v>
+        <v>1415379.050044506</v>
       </c>
       <c r="BC212" s="222" t="n">
         <v>1429707.124045061</v>
@@ -44001,13 +44001,13 @@
         <v>1441322.416354639</v>
       </c>
       <c r="BE212" s="222" t="n">
-        <v>1449303.18403771</v>
+        <v>1449303.184037709</v>
       </c>
       <c r="BF212" s="214" t="n">
         <v>1459680.857487838</v>
       </c>
       <c r="BG212" s="503" t="n">
-        <v>0.8645381501164454</v>
+        <v>0.8645381501164452</v>
       </c>
       <c r="BH212" s="504" t="n">
         <v>0.8600856827759139</v>
@@ -44016,13 +44016,13 @@
         <v>0.8546254776692686</v>
       </c>
       <c r="BJ212" s="504" t="n">
-        <v>0.847277456910608</v>
+        <v>0.8472774569106081</v>
       </c>
       <c r="BK212" s="505" t="n">
         <v>0.838144570834951</v>
       </c>
       <c r="BL212" s="504" t="n">
-        <v>0.8621981501164453</v>
+        <v>0.8621981501164452</v>
       </c>
       <c r="BM212" s="504" t="n">
         <v>0.8567456827759141</v>
@@ -44031,7 +44031,7 @@
         <v>0.8502854776692689</v>
       </c>
       <c r="BO212" s="504" t="n">
-        <v>0.8419374569106078</v>
+        <v>0.841937456910608</v>
       </c>
       <c r="BP212" s="505" t="n">
         <v>0.8318045708349517</v>
@@ -44057,7 +44057,7 @@
         <v>0</v>
       </c>
       <c r="BX212" s="503" t="n">
-        <v>0.8638332890668036</v>
+        <v>0.8638332890668035</v>
       </c>
       <c r="BY212" s="504" t="n">
         <v>0.8585112425786137</v>
@@ -44066,10 +44066,10 @@
         <v>0.8521951419392133</v>
       </c>
       <c r="CA212" s="504" t="n">
-        <v>0.8439901848632263</v>
+        <v>0.8439901848632265</v>
       </c>
       <c r="CB212" s="505" t="n">
-        <v>0.8340177946924229</v>
+        <v>0.8340177946924231</v>
       </c>
       <c r="CC212" s="492" t="n">
         <v>0</v>
@@ -44731,22 +44731,22 @@
         </is>
       </c>
       <c r="AK219" s="506" t="n">
-        <v>153558041.268438</v>
+        <v>153558041.2684379</v>
       </c>
       <c r="AL219" s="368" t="n">
         <v>159778964.1900266</v>
       </c>
       <c r="AM219" s="368" t="n">
-        <v>166038998.9901037</v>
+        <v>166038998.9901038</v>
       </c>
       <c r="AN219" s="368" t="n">
-        <v>173883609.5679222</v>
+        <v>173883609.5679223</v>
       </c>
       <c r="AO219" s="380" t="n">
         <v>181212790.6116953</v>
       </c>
       <c r="AP219" s="381" t="n">
-        <v>138.6418887510878</v>
+        <v>138.6418887510877</v>
       </c>
       <c r="AQ219" s="372" t="n">
         <v>142.549634812293</v>
@@ -44755,7 +44755,7 @@
         <v>146.6709237723747</v>
       </c>
       <c r="AS219" s="372" t="n">
-        <v>152.4634568955539</v>
+        <v>152.4634568955541</v>
       </c>
       <c r="AT219" s="382" t="n">
         <v>157.4387342265028</v>
@@ -44766,22 +44766,22 @@
         </is>
       </c>
       <c r="BB219" s="391" t="n">
-        <v>153558041.268438</v>
+        <v>153558041.2684379</v>
       </c>
       <c r="BC219" s="375" t="n">
         <v>159778964.1900266</v>
       </c>
       <c r="BD219" s="375" t="n">
-        <v>166038998.9901037</v>
+        <v>166038998.9901038</v>
       </c>
       <c r="BE219" s="375" t="n">
-        <v>173883609.5679222</v>
+        <v>173883609.5679223</v>
       </c>
       <c r="BF219" s="392" t="n">
         <v>181212790.6116953</v>
       </c>
       <c r="BG219" s="386" t="n">
-        <v>138.6418887510878</v>
+        <v>138.6418887510877</v>
       </c>
       <c r="BH219" s="372" t="n">
         <v>142.549634812293</v>
@@ -44790,7 +44790,7 @@
         <v>146.6709237723747</v>
       </c>
       <c r="BJ219" s="372" t="n">
-        <v>152.4634568955539</v>
+        <v>152.4634568955541</v>
       </c>
       <c r="BK219" s="387" t="n">
         <v>157.4387342265028</v>
@@ -44801,13 +44801,13 @@
         </is>
       </c>
       <c r="BS219" s="391" t="n">
-        <v>153147878.8592605</v>
+        <v>153147878.8592604</v>
       </c>
       <c r="BT219" s="375" t="n">
         <v>159167049.0236468</v>
       </c>
       <c r="BU219" s="375" t="n">
-        <v>165208428.9489246</v>
+        <v>165208428.9489247</v>
       </c>
       <c r="BV219" s="375" t="n">
         <v>172805839.1481515</v>
@@ -44816,7 +44816,7 @@
         <v>179867333.8774216</v>
       </c>
       <c r="BX219" s="386" t="n">
-        <v>138.6418887510878</v>
+        <v>138.6418887510877</v>
       </c>
       <c r="BY219" s="372" t="n">
         <v>142.549634812293</v>
@@ -44825,7 +44825,7 @@
         <v>146.6709237723747</v>
       </c>
       <c r="CA219" s="372" t="n">
-        <v>152.4634568955539</v>
+        <v>152.4634568955541</v>
       </c>
       <c r="CB219" s="387" t="n">
         <v>157.4387342265028</v>
@@ -44840,13 +44840,13 @@
         <v>241872927.186839</v>
       </c>
       <c r="CL219" s="388" t="n">
-        <v>130.7920126950558</v>
+        <v>130.7920126950557</v>
       </c>
       <c r="CM219" s="390" t="n">
-        <v>721.1982665064118</v>
+        <v>721.1982665064115</v>
       </c>
       <c r="CN219" s="507" t="n">
-        <v>199.6089300018313</v>
+        <v>199.6089300018312</v>
       </c>
     </row>
     <row r="220">
@@ -44926,7 +44926,7 @@
         </is>
       </c>
       <c r="AK220" s="506" t="n">
-        <v>99621263.56557637</v>
+        <v>99621263.56557636</v>
       </c>
       <c r="AL220" s="368" t="n">
         <v>102867455.424678</v>
@@ -44941,10 +44941,10 @@
         <v>112154742.9937822</v>
       </c>
       <c r="AP220" s="381" t="n">
-        <v>395.696041549285</v>
+        <v>395.6960415492866</v>
       </c>
       <c r="AQ220" s="372" t="n">
-        <v>405.6559433826529</v>
+        <v>405.6559433826528</v>
       </c>
       <c r="AR220" s="372" t="n">
         <v>415.6208472109535</v>
@@ -44953,7 +44953,7 @@
         <v>427.1601692832023</v>
       </c>
       <c r="AT220" s="382" t="n">
-        <v>437.5536311497548</v>
+        <v>437.5536311497547</v>
       </c>
       <c r="BA220" s="101" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         </is>
       </c>
       <c r="BB220" s="391" t="n">
-        <v>99621263.56557637</v>
+        <v>99621263.56557636</v>
       </c>
       <c r="BC220" s="375" t="n">
         <v>102867455.424678</v>
@@ -44976,10 +44976,10 @@
         <v>112154742.9937822</v>
       </c>
       <c r="BG220" s="386" t="n">
-        <v>395.696041549285</v>
+        <v>395.6960415492866</v>
       </c>
       <c r="BH220" s="372" t="n">
-        <v>405.6559433826529</v>
+        <v>405.6559433826528</v>
       </c>
       <c r="BI220" s="372" t="n">
         <v>415.6208472109535</v>
@@ -44988,7 +44988,7 @@
         <v>427.1601692832023</v>
       </c>
       <c r="BK220" s="387" t="n">
-        <v>437.5536311497548</v>
+        <v>437.5536311497547</v>
       </c>
       <c r="BR220" s="101" t="inlineStr">
         <is>
@@ -44996,25 +44996,25 @@
         </is>
       </c>
       <c r="BS220" s="391" t="n">
-        <v>99358676.85064594</v>
+        <v>99358676.85064593</v>
       </c>
       <c r="BT220" s="375" t="n">
-        <v>102480003.1332617</v>
+        <v>102480003.1332616</v>
       </c>
       <c r="BU220" s="375" t="n">
         <v>105422960.2471893</v>
       </c>
       <c r="BV220" s="375" t="n">
-        <v>108456407.5674678</v>
+        <v>108456407.5674677</v>
       </c>
       <c r="BW220" s="392" t="n">
-        <v>111338199.0650383</v>
+        <v>111338199.0650382</v>
       </c>
       <c r="BX220" s="386" t="n">
-        <v>395.696041549285</v>
+        <v>395.6960415492866</v>
       </c>
       <c r="BY220" s="372" t="n">
-        <v>405.6559433826529</v>
+        <v>405.6559433826528</v>
       </c>
       <c r="BZ220" s="372" t="n">
         <v>415.6208472109535</v>
@@ -45023,10 +45023,10 @@
         <v>427.1601692832023</v>
       </c>
       <c r="CB220" s="387" t="n">
-        <v>437.5536311497548</v>
+        <v>437.5536311497547</v>
       </c>
       <c r="CI220" s="197" t="n">
-        <v>92468586.62020525</v>
+        <v>92468586.62020524</v>
       </c>
       <c r="CJ220" s="198" t="n">
         <v>50146632.66768061</v>
@@ -45121,13 +45121,13 @@
         </is>
       </c>
       <c r="AK221" s="506" t="n">
-        <v>24428704.35144114</v>
+        <v>24428704.35144113</v>
       </c>
       <c r="AL221" s="368" t="n">
-        <v>25266859.46546123</v>
+        <v>25266859.46546124</v>
       </c>
       <c r="AM221" s="368" t="n">
-        <v>26068955.30914956</v>
+        <v>26068955.30914957</v>
       </c>
       <c r="AN221" s="368" t="n">
         <v>26915839.6432833</v>
@@ -45136,19 +45136,19 @@
         <v>27898487.10720398</v>
       </c>
       <c r="AP221" s="381" t="n">
-        <v>429.8160672674754</v>
+        <v>429.816067267475</v>
       </c>
       <c r="AQ221" s="372" t="n">
-        <v>439.8151990365076</v>
+        <v>439.8151990365079</v>
       </c>
       <c r="AR221" s="372" t="n">
-        <v>449.669908201141</v>
+        <v>449.6699082011413</v>
       </c>
       <c r="AS221" s="372" t="n">
-        <v>461.232330114655</v>
+        <v>461.2323301146551</v>
       </c>
       <c r="AT221" s="382" t="n">
-        <v>473.6980203171419</v>
+        <v>473.6980203171418</v>
       </c>
       <c r="BA221" s="111" t="inlineStr">
         <is>
@@ -45156,13 +45156,13 @@
         </is>
       </c>
       <c r="BB221" s="391" t="n">
-        <v>24428704.35144114</v>
+        <v>24428704.35144113</v>
       </c>
       <c r="BC221" s="375" t="n">
-        <v>25266859.46546123</v>
+        <v>25266859.46546124</v>
       </c>
       <c r="BD221" s="375" t="n">
-        <v>26068955.30914956</v>
+        <v>26068955.30914957</v>
       </c>
       <c r="BE221" s="375" t="n">
         <v>26915839.6432833</v>
@@ -45171,19 +45171,19 @@
         <v>27898487.10720398</v>
       </c>
       <c r="BG221" s="386" t="n">
-        <v>429.8160672674754</v>
+        <v>429.816067267475</v>
       </c>
       <c r="BH221" s="372" t="n">
-        <v>439.8151990365076</v>
+        <v>439.8151990365079</v>
       </c>
       <c r="BI221" s="372" t="n">
-        <v>449.669908201141</v>
+        <v>449.6699082011413</v>
       </c>
       <c r="BJ221" s="372" t="n">
-        <v>461.232330114655</v>
+        <v>461.2323301146551</v>
       </c>
       <c r="BK221" s="387" t="n">
-        <v>473.6980203171419</v>
+        <v>473.6980203171418</v>
       </c>
       <c r="BR221" s="111" t="inlineStr">
         <is>
@@ -45191,43 +45191,43 @@
         </is>
       </c>
       <c r="BS221" s="391" t="n">
-        <v>24359788.21509177</v>
+        <v>24359788.21509175</v>
       </c>
       <c r="BT221" s="375" t="n">
-        <v>25164378.88482035</v>
+        <v>25164378.88482036</v>
       </c>
       <c r="BU221" s="375" t="n">
-        <v>25930189.28176446</v>
+        <v>25930189.28176447</v>
       </c>
       <c r="BV221" s="375" t="n">
         <v>26737037.78932131</v>
       </c>
       <c r="BW221" s="392" t="n">
-        <v>27674622.01245654</v>
+        <v>27674622.01245653</v>
       </c>
       <c r="BX221" s="386" t="n">
-        <v>429.8160672674754</v>
+        <v>429.816067267475</v>
       </c>
       <c r="BY221" s="372" t="n">
-        <v>439.8151990365076</v>
+        <v>439.8151990365079</v>
       </c>
       <c r="BZ221" s="372" t="n">
-        <v>449.669908201141</v>
+        <v>449.6699082011413</v>
       </c>
       <c r="CA221" s="372" t="n">
-        <v>461.232330114655</v>
+        <v>461.2323301146551</v>
       </c>
       <c r="CB221" s="387" t="n">
-        <v>473.6980203171419</v>
+        <v>473.6980203171418</v>
       </c>
       <c r="CI221" s="197" t="n">
         <v>22520192.04029759</v>
       </c>
       <c r="CJ221" s="198" t="n">
-        <v>23188084.77820081</v>
+        <v>23188084.77820082</v>
       </c>
       <c r="CK221" s="346" t="n">
-        <v>45708276.8184984</v>
+        <v>45708276.81849842</v>
       </c>
       <c r="CL221" s="386" t="n">
         <v>408.0188433579301</v>
@@ -45236,7 +45236,7 @@
         <v>2158.838541867686</v>
       </c>
       <c r="CN221" s="508" t="n">
-        <v>693.2323776218761</v>
+        <v>693.2323776218764</v>
       </c>
     </row>
     <row r="222" ht="15.75" customHeight="1" thickBot="1">
@@ -45316,10 +45316,10 @@
         </is>
       </c>
       <c r="AK222" s="435" t="n">
-        <v>24369432.40270781</v>
+        <v>24369432.4027078</v>
       </c>
       <c r="AL222" s="408" t="n">
-        <v>28456663.682109</v>
+        <v>28456663.68210901</v>
       </c>
       <c r="AM222" s="408" t="n">
         <v>33847051.45428762</v>
@@ -45328,19 +45328,19 @@
         <v>40344383.15839814</v>
       </c>
       <c r="AO222" s="409" t="n">
-        <v>46075816.37371123</v>
+        <v>46075816.37371124</v>
       </c>
       <c r="AP222" s="410" t="n">
-        <v>8028.401824709043</v>
+        <v>8028.401824709041</v>
       </c>
       <c r="AQ222" s="411" t="n">
-        <v>8410.413515735036</v>
+        <v>8410.413515735037</v>
       </c>
       <c r="AR222" s="411" t="n">
         <v>9023.71915180951</v>
       </c>
       <c r="AS222" s="411" t="n">
-        <v>9626.529800154429</v>
+        <v>9626.529800154427</v>
       </c>
       <c r="AT222" s="412" t="n">
         <v>10051.38944353848</v>
@@ -45351,10 +45351,10 @@
         </is>
       </c>
       <c r="BB222" s="419" t="n">
-        <v>24369432.40270781</v>
+        <v>24369432.4027078</v>
       </c>
       <c r="BC222" s="420" t="n">
-        <v>28456663.682109</v>
+        <v>28456663.68210901</v>
       </c>
       <c r="BD222" s="420" t="n">
         <v>33847051.45428762</v>
@@ -45363,19 +45363,19 @@
         <v>40344383.15839814</v>
       </c>
       <c r="BF222" s="421" t="n">
-        <v>46075816.37371123</v>
+        <v>46075816.37371124</v>
       </c>
       <c r="BG222" s="416" t="n">
-        <v>8028.401824709043</v>
+        <v>8028.401824709041</v>
       </c>
       <c r="BH222" s="417" t="n">
-        <v>8410.413515735036</v>
+        <v>8410.413515735037</v>
       </c>
       <c r="BI222" s="417" t="n">
         <v>9023.71915180951</v>
       </c>
       <c r="BJ222" s="417" t="n">
-        <v>9626.529800154429</v>
+        <v>9626.529800154427</v>
       </c>
       <c r="BK222" s="418" t="n">
         <v>10051.38944353848</v>
@@ -45386,37 +45386,37 @@
         </is>
       </c>
       <c r="BS222" s="419" t="n">
-        <v>23896135.38091505</v>
+        <v>23896135.38091504</v>
       </c>
       <c r="BT222" s="420" t="n">
-        <v>27675380.21333003</v>
+        <v>27675380.21333004</v>
       </c>
       <c r="BU222" s="420" t="n">
         <v>32641497.62903732</v>
       </c>
       <c r="BV222" s="420" t="n">
-        <v>38590944.95395145</v>
+        <v>38590944.95395144</v>
       </c>
       <c r="BW222" s="421" t="n">
         <v>43653353.27833575</v>
       </c>
       <c r="BX222" s="416" t="n">
-        <v>8028.401824709043</v>
+        <v>8028.401824709041</v>
       </c>
       <c r="BY222" s="417" t="n">
-        <v>8410.413515735036</v>
+        <v>8410.413515735037</v>
       </c>
       <c r="BZ222" s="417" t="n">
         <v>9023.71915180951</v>
       </c>
       <c r="CA222" s="417" t="n">
-        <v>9626.529800154429</v>
+        <v>9626.529800154427</v>
       </c>
       <c r="CB222" s="418" t="n">
         <v>10051.38944353848</v>
       </c>
       <c r="CI222" s="211" t="n">
-        <v>17230897.74462212</v>
+        <v>17230897.74462213</v>
       </c>
       <c r="CJ222" s="213" t="n">
         <v>211983483.7044855</v>
@@ -45425,7 +45425,7 @@
         <v>229214381.4491076</v>
       </c>
       <c r="CL222" s="416" t="n">
-        <v>6864.899499849451</v>
+        <v>6864.899499849453</v>
       </c>
       <c r="CM222" s="418" t="n">
         <v>11988.65986339133</v>
@@ -45441,10 +45441,10 @@
         </is>
       </c>
       <c r="C223" s="425" t="n">
-        <v>301977441.5881631</v>
+        <v>301977441.588163</v>
       </c>
       <c r="D223" s="425" t="n">
-        <v>316369942.7622761</v>
+        <v>316369942.762276</v>
       </c>
       <c r="E223" s="425" t="n">
         <v>331898217.337541</v>
@@ -45459,13 +45459,13 @@
         <v>212.7769907992159</v>
       </c>
       <c r="I223" s="427" t="n">
-        <v>220.4237268582841</v>
+        <v>220.423726858284</v>
       </c>
       <c r="J223" s="427" t="n">
         <v>229.10401737997</v>
       </c>
       <c r="K223" s="427" t="n">
-        <v>240.154187953093</v>
+        <v>240.1541879530931</v>
       </c>
       <c r="L223" s="428" t="n">
         <v>249.7553771891122</v>
@@ -45476,10 +45476,10 @@
         </is>
       </c>
       <c r="T223" s="429" t="n">
-        <v>301977441.5881631</v>
+        <v>301977441.588163</v>
       </c>
       <c r="U223" s="430" t="n">
-        <v>316369942.7622761</v>
+        <v>316369942.762276</v>
       </c>
       <c r="V223" s="430" t="n">
         <v>331898217.337541</v>
@@ -45494,13 +45494,13 @@
         <v>212.7769907992159</v>
       </c>
       <c r="Z223" s="433" t="n">
-        <v>220.4237268582841</v>
+        <v>220.423726858284</v>
       </c>
       <c r="AA223" s="433" t="n">
         <v>229.10401737997</v>
       </c>
       <c r="AB223" s="433" t="n">
-        <v>240.154187953093</v>
+        <v>240.1541879530931</v>
       </c>
       <c r="AC223" s="434" t="n">
         <v>249.7553771891122</v>
@@ -45511,10 +45511,10 @@
         </is>
       </c>
       <c r="AK223" s="435" t="n">
-        <v>301977441.5881633</v>
+        <v>301977441.5881631</v>
       </c>
       <c r="AL223" s="408" t="n">
-        <v>316369942.7622749</v>
+        <v>316369942.7622748</v>
       </c>
       <c r="AM223" s="408" t="n">
         <v>331898217.337541</v>
@@ -45523,19 +45523,19 @@
         <v>350263780.7229205</v>
       </c>
       <c r="AO223" s="409" t="n">
-        <v>367341837.0863927</v>
+        <v>367341837.0863926</v>
       </c>
       <c r="AP223" s="436" t="n">
-        <v>212.7769907992348</v>
+        <v>212.7769907992349</v>
       </c>
       <c r="AQ223" s="437" t="n">
-        <v>220.4237268581868</v>
+        <v>220.4237268581867</v>
       </c>
       <c r="AR223" s="437" t="n">
         <v>229.1040173800739</v>
       </c>
       <c r="AS223" s="437" t="n">
-        <v>240.1541879531713</v>
+        <v>240.1541879531715</v>
       </c>
       <c r="AT223" s="438" t="n">
         <v>249.7553771891642</v>
@@ -45546,10 +45546,10 @@
         </is>
       </c>
       <c r="BB223" s="439" t="n">
-        <v>301977441.5881633</v>
+        <v>301977441.5881631</v>
       </c>
       <c r="BC223" s="440" t="n">
-        <v>316369942.7622749</v>
+        <v>316369942.7622748</v>
       </c>
       <c r="BD223" s="440" t="n">
         <v>331898217.337541</v>
@@ -45558,19 +45558,19 @@
         <v>350263780.7229205</v>
       </c>
       <c r="BF223" s="441" t="n">
-        <v>367341837.0863927</v>
+        <v>367341837.0863926</v>
       </c>
       <c r="BG223" s="442" t="n">
-        <v>212.7769907992348</v>
+        <v>212.7769907992349</v>
       </c>
       <c r="BH223" s="443" t="n">
-        <v>220.4237268581868</v>
+        <v>220.4237268581867</v>
       </c>
       <c r="BI223" s="443" t="n">
         <v>229.1040173800739</v>
       </c>
       <c r="BJ223" s="443" t="n">
-        <v>240.1541879531713</v>
+        <v>240.1541879531715</v>
       </c>
       <c r="BK223" s="444" t="n">
         <v>249.7553771891642</v>
@@ -45581,13 +45581,13 @@
         </is>
       </c>
       <c r="BS223" s="439" t="n">
-        <v>300762479.3059133</v>
+        <v>300762479.3059132</v>
       </c>
       <c r="BT223" s="440" t="n">
         <v>314486811.2550589</v>
       </c>
       <c r="BU223" s="440" t="n">
-        <v>329203076.1069157</v>
+        <v>329203076.1069158</v>
       </c>
       <c r="BV223" s="440" t="n">
         <v>346590229.458892</v>
@@ -45596,22 +45596,22 @@
         <v>362533508.2332522</v>
       </c>
       <c r="BX223" s="442" t="n">
-        <v>212.4960654861012</v>
+        <v>212.4960654861013</v>
       </c>
       <c r="BY223" s="443" t="n">
-        <v>219.9658978863332</v>
+        <v>219.9658978863331</v>
       </c>
       <c r="BZ223" s="443" t="n">
-        <v>228.4034941602649</v>
+        <v>228.403494160265</v>
       </c>
       <c r="CA223" s="443" t="n">
-        <v>239.1426675081906</v>
+        <v>239.1426675081907</v>
       </c>
       <c r="CB223" s="444" t="n">
-        <v>248.3649123529545</v>
+        <v>248.3649123529544</v>
       </c>
       <c r="CI223" s="349" t="n">
-        <v>272232002.8271314</v>
+        <v>272232002.8271313</v>
       </c>
       <c r="CJ223" s="350" t="n">
         <v>387178801.9151995</v>
@@ -47629,22 +47629,22 @@
         </is>
       </c>
       <c r="AK237" s="506" t="n">
-        <v>153558041.268438</v>
+        <v>153558041.2684379</v>
       </c>
       <c r="AL237" s="368" t="n">
         <v>159778964.1900266</v>
       </c>
       <c r="AM237" s="368" t="n">
-        <v>166038998.9901037</v>
+        <v>166038998.9901038</v>
       </c>
       <c r="AN237" s="368" t="n">
-        <v>173883609.5679222</v>
+        <v>173883609.5679223</v>
       </c>
       <c r="AO237" s="380" t="n">
         <v>181212790.6116953</v>
       </c>
       <c r="AP237" s="381" t="n">
-        <v>138.6418887510878</v>
+        <v>138.6418887510877</v>
       </c>
       <c r="AQ237" s="372" t="n">
         <v>142.549634812293</v>
@@ -47653,7 +47653,7 @@
         <v>146.6709237723747</v>
       </c>
       <c r="AS237" s="372" t="n">
-        <v>152.4634568955539</v>
+        <v>152.4634568955541</v>
       </c>
       <c r="AT237" s="382" t="n">
         <v>157.4387342265028</v>
@@ -47664,22 +47664,22 @@
         </is>
       </c>
       <c r="BB237" s="391" t="n">
-        <v>153558041.268438</v>
+        <v>153558041.2684379</v>
       </c>
       <c r="BC237" s="375" t="n">
         <v>159778964.1900266</v>
       </c>
       <c r="BD237" s="375" t="n">
-        <v>166038998.9901037</v>
+        <v>166038998.9901038</v>
       </c>
       <c r="BE237" s="375" t="n">
-        <v>173883609.5679222</v>
+        <v>173883609.5679223</v>
       </c>
       <c r="BF237" s="392" t="n">
         <v>181212790.6116953</v>
       </c>
       <c r="BG237" s="386" t="n">
-        <v>138.6418887510878</v>
+        <v>138.6418887510877</v>
       </c>
       <c r="BH237" s="372" t="n">
         <v>142.549634812293</v>
@@ -47688,7 +47688,7 @@
         <v>146.6709237723747</v>
       </c>
       <c r="BJ237" s="372" t="n">
-        <v>152.4634568955539</v>
+        <v>152.4634568955541</v>
       </c>
       <c r="BK237" s="387" t="n">
         <v>157.4387342265028</v>
@@ -47699,13 +47699,13 @@
         </is>
       </c>
       <c r="BS237" s="391" t="n">
-        <v>153147878.8592605</v>
+        <v>153147878.8592604</v>
       </c>
       <c r="BT237" s="375" t="n">
         <v>159167049.0236468</v>
       </c>
       <c r="BU237" s="375" t="n">
-        <v>165208428.9489246</v>
+        <v>165208428.9489247</v>
       </c>
       <c r="BV237" s="375" t="n">
         <v>172805839.1481515</v>
@@ -47714,7 +47714,7 @@
         <v>179867333.8774216</v>
       </c>
       <c r="BX237" s="386" t="n">
-        <v>138.6418887510878</v>
+        <v>138.6418887510877</v>
       </c>
       <c r="BY237" s="372" t="n">
         <v>142.549634812293</v>
@@ -47723,7 +47723,7 @@
         <v>146.6709237723747</v>
       </c>
       <c r="CA237" s="372" t="n">
-        <v>152.4634568955539</v>
+        <v>152.4634568955541</v>
       </c>
       <c r="CB237" s="387" t="n">
         <v>157.4387342265028</v>
@@ -47738,13 +47738,13 @@
         <v>241872927.186839</v>
       </c>
       <c r="CL237" s="388" t="n">
-        <v>130.7920126950558</v>
+        <v>130.7920126950557</v>
       </c>
       <c r="CM237" s="390" t="n">
-        <v>721.1982665064118</v>
+        <v>721.1982665064115</v>
       </c>
       <c r="CN237" s="507" t="n">
-        <v>199.6089300018313</v>
+        <v>199.6089300018312</v>
       </c>
     </row>
     <row r="238">
@@ -47824,7 +47824,7 @@
         </is>
       </c>
       <c r="AK238" s="506" t="n">
-        <v>99621263.56557637</v>
+        <v>99621263.56557636</v>
       </c>
       <c r="AL238" s="368" t="n">
         <v>102867455.424678</v>
@@ -47839,10 +47839,10 @@
         <v>112154742.9937822</v>
       </c>
       <c r="AP238" s="381" t="n">
-        <v>395.696041549285</v>
+        <v>395.6960415492866</v>
       </c>
       <c r="AQ238" s="372" t="n">
-        <v>405.6559433826529</v>
+        <v>405.6559433826528</v>
       </c>
       <c r="AR238" s="372" t="n">
         <v>415.6208472109535</v>
@@ -47851,7 +47851,7 @@
         <v>427.1601692832023</v>
       </c>
       <c r="AT238" s="382" t="n">
-        <v>437.5536311497548</v>
+        <v>437.5536311497547</v>
       </c>
       <c r="BA238" s="101" t="inlineStr">
         <is>
@@ -47859,7 +47859,7 @@
         </is>
       </c>
       <c r="BB238" s="391" t="n">
-        <v>99621263.56557637</v>
+        <v>99621263.56557636</v>
       </c>
       <c r="BC238" s="375" t="n">
         <v>102867455.424678</v>
@@ -47874,10 +47874,10 @@
         <v>112154742.9937822</v>
       </c>
       <c r="BG238" s="386" t="n">
-        <v>395.696041549285</v>
+        <v>395.6960415492866</v>
       </c>
       <c r="BH238" s="372" t="n">
-        <v>405.6559433826529</v>
+        <v>405.6559433826528</v>
       </c>
       <c r="BI238" s="372" t="n">
         <v>415.6208472109535</v>
@@ -47886,7 +47886,7 @@
         <v>427.1601692832023</v>
       </c>
       <c r="BK238" s="387" t="n">
-        <v>437.5536311497548</v>
+        <v>437.5536311497547</v>
       </c>
       <c r="BR238" s="101" t="inlineStr">
         <is>
@@ -47894,25 +47894,25 @@
         </is>
       </c>
       <c r="BS238" s="391" t="n">
-        <v>99358676.85064594</v>
+        <v>99358676.85064593</v>
       </c>
       <c r="BT238" s="375" t="n">
-        <v>102480003.1332617</v>
+        <v>102480003.1332616</v>
       </c>
       <c r="BU238" s="375" t="n">
         <v>105422960.2471893</v>
       </c>
       <c r="BV238" s="375" t="n">
-        <v>108456407.5674678</v>
+        <v>108456407.5674677</v>
       </c>
       <c r="BW238" s="392" t="n">
-        <v>111338199.0650383</v>
+        <v>111338199.0650382</v>
       </c>
       <c r="BX238" s="386" t="n">
-        <v>395.696041549285</v>
+        <v>395.6960415492866</v>
       </c>
       <c r="BY238" s="372" t="n">
-        <v>405.6559433826529</v>
+        <v>405.6559433826528</v>
       </c>
       <c r="BZ238" s="372" t="n">
         <v>415.6208472109535</v>
@@ -47921,10 +47921,10 @@
         <v>427.1601692832023</v>
       </c>
       <c r="CB238" s="387" t="n">
-        <v>437.5536311497548</v>
+        <v>437.5536311497547</v>
       </c>
       <c r="CI238" s="197" t="n">
-        <v>92468586.62020525</v>
+        <v>92468586.62020524</v>
       </c>
       <c r="CJ238" s="198" t="n">
         <v>50146632.66768061</v>
@@ -48019,13 +48019,13 @@
         </is>
       </c>
       <c r="AK239" s="506" t="n">
-        <v>24428704.35144114</v>
+        <v>24428704.35144113</v>
       </c>
       <c r="AL239" s="368" t="n">
-        <v>25266859.46546123</v>
+        <v>25266859.46546124</v>
       </c>
       <c r="AM239" s="368" t="n">
-        <v>26068955.30914956</v>
+        <v>26068955.30914957</v>
       </c>
       <c r="AN239" s="368" t="n">
         <v>26915839.6432833</v>
@@ -48034,19 +48034,19 @@
         <v>27898487.10720398</v>
       </c>
       <c r="AP239" s="381" t="n">
-        <v>429.8160672674754</v>
+        <v>429.816067267475</v>
       </c>
       <c r="AQ239" s="372" t="n">
-        <v>439.8151990365076</v>
+        <v>439.8151990365079</v>
       </c>
       <c r="AR239" s="372" t="n">
-        <v>449.669908201141</v>
+        <v>449.6699082011413</v>
       </c>
       <c r="AS239" s="372" t="n">
-        <v>461.232330114655</v>
+        <v>461.2323301146551</v>
       </c>
       <c r="AT239" s="382" t="n">
-        <v>473.6980203171419</v>
+        <v>473.6980203171418</v>
       </c>
       <c r="BA239" s="111" t="inlineStr">
         <is>
@@ -48054,13 +48054,13 @@
         </is>
       </c>
       <c r="BB239" s="391" t="n">
-        <v>24428704.35144114</v>
+        <v>24428704.35144113</v>
       </c>
       <c r="BC239" s="375" t="n">
-        <v>25266859.46546123</v>
+        <v>25266859.46546124</v>
       </c>
       <c r="BD239" s="375" t="n">
-        <v>26068955.30914956</v>
+        <v>26068955.30914957</v>
       </c>
       <c r="BE239" s="375" t="n">
         <v>26915839.6432833</v>
@@ -48069,19 +48069,19 @@
         <v>27898487.10720398</v>
       </c>
       <c r="BG239" s="386" t="n">
-        <v>429.8160672674754</v>
+        <v>429.816067267475</v>
       </c>
       <c r="BH239" s="372" t="n">
-        <v>439.8151990365076</v>
+        <v>439.8151990365079</v>
       </c>
       <c r="BI239" s="372" t="n">
-        <v>449.669908201141</v>
+        <v>449.6699082011413</v>
       </c>
       <c r="BJ239" s="372" t="n">
-        <v>461.232330114655</v>
+        <v>461.2323301146551</v>
       </c>
       <c r="BK239" s="387" t="n">
-        <v>473.6980203171419</v>
+        <v>473.6980203171418</v>
       </c>
       <c r="BR239" s="111" t="inlineStr">
         <is>
@@ -48089,43 +48089,43 @@
         </is>
       </c>
       <c r="BS239" s="391" t="n">
-        <v>24359788.21509177</v>
+        <v>24359788.21509175</v>
       </c>
       <c r="BT239" s="375" t="n">
-        <v>25164378.88482035</v>
+        <v>25164378.88482036</v>
       </c>
       <c r="BU239" s="375" t="n">
-        <v>25930189.28176446</v>
+        <v>25930189.28176447</v>
       </c>
       <c r="BV239" s="375" t="n">
         <v>26737037.78932131</v>
       </c>
       <c r="BW239" s="392" t="n">
-        <v>27674622.01245654</v>
+        <v>27674622.01245653</v>
       </c>
       <c r="BX239" s="386" t="n">
-        <v>429.8160672674754</v>
+        <v>429.816067267475</v>
       </c>
       <c r="BY239" s="372" t="n">
-        <v>439.8151990365076</v>
+        <v>439.8151990365079</v>
       </c>
       <c r="BZ239" s="372" t="n">
-        <v>449.669908201141</v>
+        <v>449.6699082011413</v>
       </c>
       <c r="CA239" s="372" t="n">
-        <v>461.232330114655</v>
+        <v>461.2323301146551</v>
       </c>
       <c r="CB239" s="387" t="n">
-        <v>473.6980203171419</v>
+        <v>473.6980203171418</v>
       </c>
       <c r="CI239" s="197" t="n">
         <v>22520192.04029759</v>
       </c>
       <c r="CJ239" s="198" t="n">
-        <v>23188084.77820081</v>
+        <v>23188084.77820082</v>
       </c>
       <c r="CK239" s="346" t="n">
-        <v>45708276.8184984</v>
+        <v>45708276.81849842</v>
       </c>
       <c r="CL239" s="386" t="n">
         <v>408.0188433579301</v>
@@ -48134,7 +48134,7 @@
         <v>2158.838541867686</v>
       </c>
       <c r="CN239" s="508" t="n">
-        <v>693.2323776218761</v>
+        <v>693.2323776218764</v>
       </c>
     </row>
     <row r="240" ht="15.75" customHeight="1" thickBot="1">
@@ -48214,10 +48214,10 @@
         </is>
       </c>
       <c r="AK240" s="435" t="n">
-        <v>24369432.40270781</v>
+        <v>24369432.4027078</v>
       </c>
       <c r="AL240" s="408" t="n">
-        <v>28456663.682109</v>
+        <v>28456663.68210901</v>
       </c>
       <c r="AM240" s="408" t="n">
         <v>33847051.45428762</v>
@@ -48226,19 +48226,19 @@
         <v>40344383.15839814</v>
       </c>
       <c r="AO240" s="409" t="n">
-        <v>46075816.37371123</v>
+        <v>46075816.37371124</v>
       </c>
       <c r="AP240" s="410" t="n">
-        <v>8028.401824709043</v>
+        <v>8028.401824709041</v>
       </c>
       <c r="AQ240" s="411" t="n">
-        <v>8410.413515735036</v>
+        <v>8410.413515735037</v>
       </c>
       <c r="AR240" s="411" t="n">
         <v>9023.71915180951</v>
       </c>
       <c r="AS240" s="411" t="n">
-        <v>9626.529800154429</v>
+        <v>9626.529800154427</v>
       </c>
       <c r="AT240" s="412" t="n">
         <v>10051.38944353848</v>
@@ -48249,10 +48249,10 @@
         </is>
       </c>
       <c r="BB240" s="419" t="n">
-        <v>24369432.40270781</v>
+        <v>24369432.4027078</v>
       </c>
       <c r="BC240" s="420" t="n">
-        <v>28456663.682109</v>
+        <v>28456663.68210901</v>
       </c>
       <c r="BD240" s="420" t="n">
         <v>33847051.45428762</v>
@@ -48261,19 +48261,19 @@
         <v>40344383.15839814</v>
       </c>
       <c r="BF240" s="421" t="n">
-        <v>46075816.37371123</v>
+        <v>46075816.37371124</v>
       </c>
       <c r="BG240" s="416" t="n">
-        <v>8028.401824709043</v>
+        <v>8028.401824709041</v>
       </c>
       <c r="BH240" s="417" t="n">
-        <v>8410.413515735036</v>
+        <v>8410.413515735037</v>
       </c>
       <c r="BI240" s="417" t="n">
         <v>9023.71915180951</v>
       </c>
       <c r="BJ240" s="417" t="n">
-        <v>9626.529800154429</v>
+        <v>9626.529800154427</v>
       </c>
       <c r="BK240" s="418" t="n">
         <v>10051.38944353848</v>
@@ -48284,37 +48284,37 @@
         </is>
       </c>
       <c r="BS240" s="419" t="n">
-        <v>23896135.38091505</v>
+        <v>23896135.38091504</v>
       </c>
       <c r="BT240" s="420" t="n">
-        <v>27675380.21333003</v>
+        <v>27675380.21333004</v>
       </c>
       <c r="BU240" s="420" t="n">
         <v>32641497.62903732</v>
       </c>
       <c r="BV240" s="420" t="n">
-        <v>38590944.95395145</v>
+        <v>38590944.95395144</v>
       </c>
       <c r="BW240" s="421" t="n">
         <v>43653353.27833575</v>
       </c>
       <c r="BX240" s="416" t="n">
-        <v>8028.401824709043</v>
+        <v>8028.401824709041</v>
       </c>
       <c r="BY240" s="417" t="n">
-        <v>8410.413515735036</v>
+        <v>8410.413515735037</v>
       </c>
       <c r="BZ240" s="417" t="n">
         <v>9023.71915180951</v>
       </c>
       <c r="CA240" s="417" t="n">
-        <v>9626.529800154429</v>
+        <v>9626.529800154427</v>
       </c>
       <c r="CB240" s="418" t="n">
         <v>10051.38944353848</v>
       </c>
       <c r="CI240" s="211" t="n">
-        <v>17230897.74462212</v>
+        <v>17230897.74462213</v>
       </c>
       <c r="CJ240" s="213" t="n">
         <v>211983483.7044855</v>
@@ -48323,7 +48323,7 @@
         <v>229214381.4491076</v>
       </c>
       <c r="CL240" s="416" t="n">
-        <v>6864.899499849451</v>
+        <v>6864.899499849453</v>
       </c>
       <c r="CM240" s="418" t="n">
         <v>11988.65986339133</v>
@@ -48339,10 +48339,10 @@
         </is>
       </c>
       <c r="C241" s="425" t="n">
-        <v>301977441.5881631</v>
+        <v>301977441.588163</v>
       </c>
       <c r="D241" s="425" t="n">
-        <v>316369942.7622761</v>
+        <v>316369942.762276</v>
       </c>
       <c r="E241" s="425" t="n">
         <v>331898217.337541</v>
@@ -48357,13 +48357,13 @@
         <v>212.7769907992159</v>
       </c>
       <c r="I241" s="427" t="n">
-        <v>220.4237268582841</v>
+        <v>220.423726858284</v>
       </c>
       <c r="J241" s="427" t="n">
         <v>229.10401737997</v>
       </c>
       <c r="K241" s="427" t="n">
-        <v>240.154187953093</v>
+        <v>240.1541879530931</v>
       </c>
       <c r="L241" s="428" t="n">
         <v>249.7553771891122</v>
@@ -48374,10 +48374,10 @@
         </is>
       </c>
       <c r="T241" s="429" t="n">
-        <v>301977441.5881631</v>
+        <v>301977441.588163</v>
       </c>
       <c r="U241" s="430" t="n">
-        <v>316369942.7622761</v>
+        <v>316369942.762276</v>
       </c>
       <c r="V241" s="430" t="n">
         <v>331898217.337541</v>
@@ -48392,13 +48392,13 @@
         <v>212.7769907992159</v>
       </c>
       <c r="Z241" s="433" t="n">
-        <v>220.4237268582841</v>
+        <v>220.423726858284</v>
       </c>
       <c r="AA241" s="433" t="n">
         <v>229.10401737997</v>
       </c>
       <c r="AB241" s="433" t="n">
-        <v>240.154187953093</v>
+        <v>240.1541879530931</v>
       </c>
       <c r="AC241" s="434" t="n">
         <v>249.7553771891122</v>
@@ -48409,10 +48409,10 @@
         </is>
       </c>
       <c r="AK241" s="435" t="n">
-        <v>301977441.5881633</v>
+        <v>301977441.5881631</v>
       </c>
       <c r="AL241" s="408" t="n">
-        <v>316369942.7622749</v>
+        <v>316369942.7622748</v>
       </c>
       <c r="AM241" s="408" t="n">
         <v>331898217.337541</v>
@@ -48421,19 +48421,19 @@
         <v>350263780.7229205</v>
       </c>
       <c r="AO241" s="409" t="n">
-        <v>367341837.0863927</v>
+        <v>367341837.0863926</v>
       </c>
       <c r="AP241" s="436" t="n">
-        <v>212.7769907992348</v>
+        <v>212.7769907992349</v>
       </c>
       <c r="AQ241" s="437" t="n">
-        <v>220.4237268581868</v>
+        <v>220.4237268581867</v>
       </c>
       <c r="AR241" s="437" t="n">
         <v>229.1040173800739</v>
       </c>
       <c r="AS241" s="437" t="n">
-        <v>240.1541879531713</v>
+        <v>240.1541879531715</v>
       </c>
       <c r="AT241" s="438" t="n">
         <v>249.7553771891642</v>
@@ -48444,10 +48444,10 @@
         </is>
       </c>
       <c r="BB241" s="439" t="n">
-        <v>301977441.5881633</v>
+        <v>301977441.5881631</v>
       </c>
       <c r="BC241" s="440" t="n">
-        <v>316369942.7622749</v>
+        <v>316369942.7622748</v>
       </c>
       <c r="BD241" s="440" t="n">
         <v>331898217.337541</v>
@@ -48456,19 +48456,19 @@
         <v>350263780.7229205</v>
       </c>
       <c r="BF241" s="441" t="n">
-        <v>367341837.0863927</v>
+        <v>367341837.0863926</v>
       </c>
       <c r="BG241" s="442" t="n">
-        <v>212.7769907992348</v>
+        <v>212.7769907992349</v>
       </c>
       <c r="BH241" s="443" t="n">
-        <v>220.4237268581868</v>
+        <v>220.4237268581867</v>
       </c>
       <c r="BI241" s="443" t="n">
         <v>229.1040173800739</v>
       </c>
       <c r="BJ241" s="443" t="n">
-        <v>240.1541879531713</v>
+        <v>240.1541879531715</v>
       </c>
       <c r="BK241" s="444" t="n">
         <v>249.7553771891642</v>
@@ -48479,13 +48479,13 @@
         </is>
       </c>
       <c r="BS241" s="439" t="n">
-        <v>300762479.3059133</v>
+        <v>300762479.3059132</v>
       </c>
       <c r="BT241" s="440" t="n">
         <v>314486811.2550589</v>
       </c>
       <c r="BU241" s="440" t="n">
-        <v>329203076.1069157</v>
+        <v>329203076.1069158</v>
       </c>
       <c r="BV241" s="440" t="n">
         <v>346590229.458892</v>
@@ -48494,22 +48494,22 @@
         <v>362533508.2332522</v>
       </c>
       <c r="BX241" s="442" t="n">
-        <v>212.4960654861012</v>
+        <v>212.4960654861013</v>
       </c>
       <c r="BY241" s="443" t="n">
-        <v>219.9658978863332</v>
+        <v>219.9658978863331</v>
       </c>
       <c r="BZ241" s="443" t="n">
-        <v>228.4034941602649</v>
+        <v>228.403494160265</v>
       </c>
       <c r="CA241" s="443" t="n">
-        <v>239.1426675081906</v>
+        <v>239.1426675081907</v>
       </c>
       <c r="CB241" s="444" t="n">
-        <v>248.3649123529545</v>
+        <v>248.3649123529544</v>
       </c>
       <c r="CI241" s="349" t="n">
-        <v>272232002.8271314</v>
+        <v>272232002.8271313</v>
       </c>
       <c r="CJ241" s="350" t="n">
         <v>387178801.9151995</v>
@@ -49039,7 +49039,7 @@
         <v>126617344.1039844</v>
       </c>
       <c r="AL246" s="368" t="n">
-        <v>141248374.0261256</v>
+        <v>141248374.0261258</v>
       </c>
       <c r="AM246" s="368" t="n">
         <v>156336436.1669482</v>
@@ -49048,22 +49048,22 @@
         <v>172797502.0263112</v>
       </c>
       <c r="AO246" s="380" t="n">
-        <v>194794539.8105858</v>
+        <v>194794539.8105859</v>
       </c>
       <c r="AP246" s="381" t="n">
-        <v>808.0292638054046</v>
+        <v>808.0292638054043</v>
       </c>
       <c r="AQ246" s="372" t="n">
-        <v>859.3947033651493</v>
+        <v>859.3947033651503</v>
       </c>
       <c r="AR246" s="372" t="n">
-        <v>905.0157360453046</v>
+        <v>905.0157360453048</v>
       </c>
       <c r="AS246" s="372" t="n">
         <v>942.7199139126483</v>
       </c>
       <c r="AT246" s="382" t="n">
-        <v>989.1578434875789</v>
+        <v>989.1578434875794</v>
       </c>
       <c r="BA246" s="83" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>126617344.1039844</v>
       </c>
       <c r="BC246" s="375" t="n">
-        <v>141248374.0261256</v>
+        <v>141248374.0261258</v>
       </c>
       <c r="BD246" s="375" t="n">
         <v>156336436.1669482</v>
@@ -49083,22 +49083,22 @@
         <v>172797502.0263112</v>
       </c>
       <c r="BF246" s="392" t="n">
-        <v>194794539.8105858</v>
+        <v>194794539.8105859</v>
       </c>
       <c r="BG246" s="386" t="n">
-        <v>808.0292638054046</v>
+        <v>808.0292638054043</v>
       </c>
       <c r="BH246" s="372" t="n">
-        <v>859.3947033651493</v>
+        <v>859.3947033651503</v>
       </c>
       <c r="BI246" s="372" t="n">
-        <v>905.0157360453046</v>
+        <v>905.0157360453048</v>
       </c>
       <c r="BJ246" s="372" t="n">
         <v>942.7199139126483</v>
       </c>
       <c r="BK246" s="387" t="n">
-        <v>989.1578434875789</v>
+        <v>989.1578434875794</v>
       </c>
       <c r="BR246" s="83" t="inlineStr">
         <is>
@@ -49109,7 +49109,7 @@
         <v>127420166.0637996</v>
       </c>
       <c r="BT246" s="375" t="n">
-        <v>143078447.3193781</v>
+        <v>143078447.3193782</v>
       </c>
       <c r="BU246" s="375" t="n">
         <v>159308459.9678396</v>
@@ -49118,22 +49118,22 @@
         <v>176996275.2928466</v>
       </c>
       <c r="BW246" s="392" t="n">
-        <v>200399456.4644607</v>
+        <v>200399456.4644608</v>
       </c>
       <c r="BX246" s="386" t="n">
-        <v>808.0292638054046</v>
+        <v>808.0292638054043</v>
       </c>
       <c r="BY246" s="372" t="n">
-        <v>859.3947033651493</v>
+        <v>859.3947033651503</v>
       </c>
       <c r="BZ246" s="372" t="n">
-        <v>905.0157360453046</v>
+        <v>905.0157360453048</v>
       </c>
       <c r="CA246" s="372" t="n">
         <v>942.7199139126483</v>
       </c>
       <c r="CB246" s="387" t="n">
-        <v>989.1578434875789</v>
+        <v>989.1578434875794</v>
       </c>
       <c r="CI246" s="225" t="n"/>
       <c r="CJ246" s="225" t="n"/>
@@ -49215,16 +49215,16 @@
         </is>
       </c>
       <c r="AK247" s="506" t="n">
-        <v>49640360.26519077</v>
+        <v>49640360.26519076</v>
       </c>
       <c r="AL247" s="368" t="n">
         <v>53602589.25996547</v>
       </c>
       <c r="AM247" s="368" t="n">
-        <v>58365089.44804497</v>
+        <v>58365089.448045</v>
       </c>
       <c r="AN247" s="368" t="n">
-        <v>64356552.90965887</v>
+        <v>64356552.90965885</v>
       </c>
       <c r="AO247" s="380" t="n">
         <v>72697882.80520257</v>
@@ -49236,7 +49236,7 @@
         <v>1655.286013274079</v>
       </c>
       <c r="AR247" s="372" t="n">
-        <v>1741.357253135669</v>
+        <v>1741.35725313567</v>
       </c>
       <c r="AS247" s="372" t="n">
         <v>1815.921500581826</v>
@@ -49250,16 +49250,16 @@
         </is>
       </c>
       <c r="BB247" s="391" t="n">
-        <v>49640360.26519077</v>
+        <v>49640360.26519076</v>
       </c>
       <c r="BC247" s="375" t="n">
         <v>53602589.25996547</v>
       </c>
       <c r="BD247" s="375" t="n">
-        <v>58365089.44804497</v>
+        <v>58365089.448045</v>
       </c>
       <c r="BE247" s="375" t="n">
-        <v>64356552.90965887</v>
+        <v>64356552.90965885</v>
       </c>
       <c r="BF247" s="392" t="n">
         <v>72697882.80520257</v>
@@ -49271,7 +49271,7 @@
         <v>1655.286013274079</v>
       </c>
       <c r="BI247" s="372" t="n">
-        <v>1741.357253135669</v>
+        <v>1741.35725313567</v>
       </c>
       <c r="BJ247" s="372" t="n">
         <v>1815.921500581826</v>
@@ -49285,16 +49285,16 @@
         </is>
       </c>
       <c r="BS247" s="391" t="n">
-        <v>50132747.34533641</v>
+        <v>50132747.3453364</v>
       </c>
       <c r="BT247" s="375" t="n">
         <v>54567686.23948944</v>
       </c>
       <c r="BU247" s="375" t="n">
-        <v>59834859.82321823</v>
+        <v>59834859.82321826</v>
       </c>
       <c r="BV247" s="375" t="n">
-        <v>66366095.55613156</v>
+        <v>66366095.55613153</v>
       </c>
       <c r="BW247" s="392" t="n">
         <v>75327072.67030132</v>
@@ -49306,7 +49306,7 @@
         <v>1655.286013274079</v>
       </c>
       <c r="BZ247" s="372" t="n">
-        <v>1741.357253135669</v>
+        <v>1741.35725313567</v>
       </c>
       <c r="CA247" s="372" t="n">
         <v>1815.921500581826</v>
@@ -49394,31 +49394,31 @@
         </is>
       </c>
       <c r="AK248" s="506" t="n">
-        <v>27454849.66467315</v>
+        <v>27454849.66467313</v>
       </c>
       <c r="AL248" s="368" t="n">
-        <v>30609035.16874773</v>
+        <v>30609035.16874772</v>
       </c>
       <c r="AM248" s="368" t="n">
-        <v>34281145.60176639</v>
+        <v>34281145.60176638</v>
       </c>
       <c r="AN248" s="368" t="n">
-        <v>38563749.91945266</v>
+        <v>38563749.91945268</v>
       </c>
       <c r="AO248" s="380" t="n">
         <v>43774095.21109043</v>
       </c>
       <c r="AP248" s="381" t="n">
-        <v>2349.47059343092</v>
+        <v>2349.470593430919</v>
       </c>
       <c r="AQ248" s="372" t="n">
-        <v>2485.680463852201</v>
+        <v>2485.6804638522</v>
       </c>
       <c r="AR248" s="372" t="n">
-        <v>2610.628996359971</v>
+        <v>2610.62899635997</v>
       </c>
       <c r="AS248" s="372" t="n">
-        <v>2708.250053204232</v>
+        <v>2708.250053204233</v>
       </c>
       <c r="AT248" s="382" t="n">
         <v>2797.7873408409</v>
@@ -49429,31 +49429,31 @@
         </is>
       </c>
       <c r="BB248" s="391" t="n">
-        <v>27454849.66467315</v>
+        <v>27454849.66467313</v>
       </c>
       <c r="BC248" s="375" t="n">
-        <v>30609035.16874773</v>
+        <v>30609035.16874772</v>
       </c>
       <c r="BD248" s="375" t="n">
-        <v>34281145.60176639</v>
+        <v>34281145.60176638</v>
       </c>
       <c r="BE248" s="375" t="n">
-        <v>38563749.91945266</v>
+        <v>38563749.91945268</v>
       </c>
       <c r="BF248" s="392" t="n">
         <v>43774095.21109043</v>
       </c>
       <c r="BG248" s="386" t="n">
-        <v>2349.47059343092</v>
+        <v>2349.470593430919</v>
       </c>
       <c r="BH248" s="372" t="n">
-        <v>2485.680463852201</v>
+        <v>2485.6804638522</v>
       </c>
       <c r="BI248" s="372" t="n">
-        <v>2610.628996359971</v>
+        <v>2610.62899635997</v>
       </c>
       <c r="BJ248" s="372" t="n">
-        <v>2708.250053204232</v>
+        <v>2708.250053204233</v>
       </c>
       <c r="BK248" s="387" t="n">
         <v>2797.7873408409</v>
@@ -49464,31 +49464,31 @@
         </is>
       </c>
       <c r="BS248" s="391" t="n">
-        <v>27524559.52788395</v>
+        <v>27524559.52788394</v>
       </c>
       <c r="BT248" s="375" t="n">
         <v>30832725.79709065</v>
       </c>
       <c r="BU248" s="375" t="n">
-        <v>34674878.53744322</v>
+        <v>34674878.53744321</v>
       </c>
       <c r="BV248" s="375" t="n">
-        <v>39141702.84725134</v>
+        <v>39141702.84725136</v>
       </c>
       <c r="BW248" s="392" t="n">
         <v>44556567.68142488</v>
       </c>
       <c r="BX248" s="386" t="n">
-        <v>2349.47059343092</v>
+        <v>2349.470593430919</v>
       </c>
       <c r="BY248" s="372" t="n">
-        <v>2485.680463852201</v>
+        <v>2485.6804638522</v>
       </c>
       <c r="BZ248" s="372" t="n">
-        <v>2610.628996359971</v>
+        <v>2610.62899635997</v>
       </c>
       <c r="CA248" s="372" t="n">
-        <v>2708.250053204232</v>
+        <v>2708.250053204233</v>
       </c>
       <c r="CB248" s="387" t="n">
         <v>2797.7873408409</v>
@@ -49582,10 +49582,10 @@
         <v>353845923.7850232</v>
       </c>
       <c r="AN249" s="408" t="n">
-        <v>400144174.7224734</v>
+        <v>400144174.7224731</v>
       </c>
       <c r="AO249" s="409" t="n">
-        <v>458182076.6647987</v>
+        <v>458182076.6647986</v>
       </c>
       <c r="AP249" s="410" t="n">
         <v>12521.3294952067</v>
@@ -49597,7 +49597,7 @@
         <v>13089.82884659049</v>
       </c>
       <c r="AS249" s="411" t="n">
-        <v>13374.31064517061</v>
+        <v>13374.3106451706</v>
       </c>
       <c r="AT249" s="412" t="n">
         <v>13705.78892367393</v>
@@ -49617,10 +49617,10 @@
         <v>353845923.7850232</v>
       </c>
       <c r="BE249" s="420" t="n">
-        <v>400144174.7224734</v>
+        <v>400144174.7224731</v>
       </c>
       <c r="BF249" s="421" t="n">
-        <v>458182076.6647987</v>
+        <v>458182076.6647986</v>
       </c>
       <c r="BG249" s="416" t="n">
         <v>12521.3294952067</v>
@@ -49632,7 +49632,7 @@
         <v>13089.82884659049</v>
       </c>
       <c r="BJ249" s="417" t="n">
-        <v>13374.31064517061</v>
+        <v>13374.3106451706</v>
       </c>
       <c r="BK249" s="418" t="n">
         <v>13705.78892367393</v>
@@ -49649,10 +49649,10 @@
         <v>304550625.5079275</v>
       </c>
       <c r="BU249" s="420" t="n">
-        <v>344413772.2410912</v>
+        <v>344413772.2410913</v>
       </c>
       <c r="BV249" s="420" t="n">
-        <v>389867207.5569915</v>
+        <v>389867207.5569912</v>
       </c>
       <c r="BW249" s="421" t="n">
         <v>446500063.8135937</v>
@@ -49667,7 +49667,7 @@
         <v>13089.82884659049</v>
       </c>
       <c r="CA249" s="417" t="n">
-        <v>13374.31064517061</v>
+        <v>13374.3106451706</v>
       </c>
       <c r="CB249" s="418" t="n">
         <v>13705.78892367393</v>
@@ -49755,28 +49755,28 @@
         <v>481161614.8533119</v>
       </c>
       <c r="AL250" s="408" t="n">
-        <v>538476579.7954476</v>
+        <v>538476579.7954478</v>
       </c>
       <c r="AM250" s="408" t="n">
-        <v>602828595.0017827</v>
+        <v>602828595.0017828</v>
       </c>
       <c r="AN250" s="408" t="n">
-        <v>675861979.5778961</v>
+        <v>675861979.5778959</v>
       </c>
       <c r="AO250" s="409" t="n">
-        <v>769448594.4916774</v>
+        <v>769448594.4916775</v>
       </c>
       <c r="AP250" s="436" t="n">
         <v>2163.756050837531</v>
       </c>
       <c r="AQ250" s="437" t="n">
-        <v>2306.26657650218</v>
+        <v>2306.266576502181</v>
       </c>
       <c r="AR250" s="437" t="n">
         <v>2446.296897853601</v>
       </c>
       <c r="AS250" s="437" t="n">
-        <v>2570.842398787373</v>
+        <v>2570.842398787372</v>
       </c>
       <c r="AT250" s="438" t="n">
         <v>2709.041941852854</v>
@@ -49790,28 +49790,28 @@
         <v>481161614.8533119</v>
       </c>
       <c r="BC250" s="440" t="n">
-        <v>538476579.7954476</v>
+        <v>538476579.7954478</v>
       </c>
       <c r="BD250" s="440" t="n">
-        <v>602828595.0017827</v>
+        <v>602828595.0017828</v>
       </c>
       <c r="BE250" s="440" t="n">
-        <v>675861979.5778961</v>
+        <v>675861979.5778959</v>
       </c>
       <c r="BF250" s="441" t="n">
-        <v>769448594.4916774</v>
+        <v>769448594.4916775</v>
       </c>
       <c r="BG250" s="442" t="n">
         <v>2163.756050837531</v>
       </c>
       <c r="BH250" s="443" t="n">
-        <v>2306.26657650218</v>
+        <v>2306.266576502181</v>
       </c>
       <c r="BI250" s="443" t="n">
         <v>2446.296897853601</v>
       </c>
       <c r="BJ250" s="443" t="n">
-        <v>2570.842398787373</v>
+        <v>2570.842398787372</v>
       </c>
       <c r="BK250" s="444" t="n">
         <v>2709.041941852854</v>
@@ -49822,28 +49822,28 @@
         </is>
       </c>
       <c r="BS250" s="439" t="n">
-        <v>474951381.2752882</v>
+        <v>474951381.2752881</v>
       </c>
       <c r="BT250" s="440" t="n">
-        <v>533029484.8638856</v>
+        <v>533029484.8638858</v>
       </c>
       <c r="BU250" s="440" t="n">
-        <v>598231970.5695922</v>
+        <v>598231970.5695924</v>
       </c>
       <c r="BV250" s="440" t="n">
-        <v>672371281.2532209</v>
+        <v>672371281.2532207</v>
       </c>
       <c r="BW250" s="441" t="n">
         <v>766783160.6297807</v>
       </c>
       <c r="BX250" s="442" t="n">
-        <v>2128.802545631968</v>
+        <v>2128.802545631967</v>
       </c>
       <c r="BY250" s="443" t="n">
         <v>2262.185456546918</v>
       </c>
       <c r="BZ250" s="443" t="n">
-        <v>2393.088848784541</v>
+        <v>2393.088848784542</v>
       </c>
       <c r="CA250" s="443" t="n">
         <v>2509.778431754753</v>
@@ -51945,7 +51945,7 @@
         <v>126617344.1039844</v>
       </c>
       <c r="AL264" s="368" t="n">
-        <v>141248374.0261256</v>
+        <v>141248374.0261258</v>
       </c>
       <c r="AM264" s="368" t="n">
         <v>156336436.1669482</v>
@@ -51954,22 +51954,22 @@
         <v>172797502.0263112</v>
       </c>
       <c r="AO264" s="380" t="n">
-        <v>194794539.8105858</v>
+        <v>194794539.8105859</v>
       </c>
       <c r="AP264" s="381" t="n">
-        <v>808.0292638054067</v>
+        <v>808.0292638054065</v>
       </c>
       <c r="AQ264" s="372" t="n">
-        <v>859.3947033651516</v>
+        <v>859.3947033651526</v>
       </c>
       <c r="AR264" s="372" t="n">
-        <v>905.0157360453056</v>
+        <v>905.0157360453059</v>
       </c>
       <c r="AS264" s="372" t="n">
-        <v>942.7199139126471</v>
+        <v>942.7199139126475</v>
       </c>
       <c r="AT264" s="382" t="n">
-        <v>989.1578434875767</v>
+        <v>989.1578434875773</v>
       </c>
       <c r="BA264" s="83" t="inlineStr">
         <is>
@@ -51980,7 +51980,7 @@
         <v>126617344.1039844</v>
       </c>
       <c r="BC264" s="375" t="n">
-        <v>141248374.0261256</v>
+        <v>141248374.0261258</v>
       </c>
       <c r="BD264" s="375" t="n">
         <v>156336436.1669482</v>
@@ -51989,22 +51989,22 @@
         <v>172797502.0263112</v>
       </c>
       <c r="BF264" s="392" t="n">
-        <v>194794539.8105858</v>
+        <v>194794539.8105859</v>
       </c>
       <c r="BG264" s="386" t="n">
-        <v>808.0292638054067</v>
+        <v>808.0292638054065</v>
       </c>
       <c r="BH264" s="372" t="n">
-        <v>859.3947033651516</v>
+        <v>859.3947033651526</v>
       </c>
       <c r="BI264" s="372" t="n">
-        <v>905.0157360453056</v>
+        <v>905.0157360453059</v>
       </c>
       <c r="BJ264" s="372" t="n">
-        <v>942.7199139126471</v>
+        <v>942.7199139126475</v>
       </c>
       <c r="BK264" s="387" t="n">
-        <v>989.1578434875767</v>
+        <v>989.1578434875773</v>
       </c>
       <c r="BR264" s="83" t="inlineStr">
         <is>
@@ -52012,10 +52012,10 @@
         </is>
       </c>
       <c r="BS264" s="391" t="n">
-        <v>127420166.0637997</v>
+        <v>127420166.0637996</v>
       </c>
       <c r="BT264" s="375" t="n">
-        <v>143078447.3193781</v>
+        <v>143078447.3193783</v>
       </c>
       <c r="BU264" s="375" t="n">
         <v>159308459.9678396</v>
@@ -52024,25 +52024,25 @@
         <v>176996275.2928466</v>
       </c>
       <c r="BW264" s="392" t="n">
-        <v>200399456.4644607</v>
+        <v>200399456.4644608</v>
       </c>
       <c r="BX264" s="386" t="n">
-        <v>808.0292638054067</v>
+        <v>808.0292638054065</v>
       </c>
       <c r="BY264" s="372" t="n">
-        <v>859.3947033651516</v>
+        <v>859.3947033651526</v>
       </c>
       <c r="BZ264" s="372" t="n">
-        <v>905.0157360453056</v>
+        <v>905.0157360453059</v>
       </c>
       <c r="CA264" s="372" t="n">
-        <v>942.7199139126471</v>
+        <v>942.7199139126475</v>
       </c>
       <c r="CB264" s="387" t="n">
-        <v>989.1578434875767</v>
+        <v>989.1578434875773</v>
       </c>
       <c r="CI264" s="396" t="n">
-        <v>0.9999999999999994</v>
+        <v>1</v>
       </c>
       <c r="CJ264" s="397" t="n">
         <v>1.000000000000001</v>
@@ -52051,16 +52051,16 @@
         <v>1</v>
       </c>
       <c r="CL264" s="397" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999999994</v>
       </c>
       <c r="CM264" s="398" t="n">
         <v>1.000000000000002</v>
       </c>
       <c r="CN264" s="102" t="n">
-        <v>0.9999999999999932</v>
+        <v>0.9999999999999934</v>
       </c>
       <c r="CO264" s="103" t="n">
-        <v>1.000000000000016</v>
+        <v>1.000000000000015</v>
       </c>
       <c r="CP264" s="103" t="n">
         <v>1.000000000000011</v>
@@ -52069,10 +52069,10 @@
         <v>0.9999999999999876</v>
       </c>
       <c r="CR264" s="104" t="n">
-        <v>1.000000000000051</v>
+        <v>1.00000000000005</v>
       </c>
       <c r="CT264" s="396" t="n">
-        <v>0.9999999999999994</v>
+        <v>1</v>
       </c>
       <c r="CU264" s="397" t="n">
         <v>1.000000000000001</v>
@@ -52081,16 +52081,16 @@
         <v>1</v>
       </c>
       <c r="CW264" s="397" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.9999999999999994</v>
       </c>
       <c r="CX264" s="398" t="n">
         <v>1.000000000000002</v>
       </c>
       <c r="CY264" s="102" t="n">
-        <v>1.012460167073759</v>
+        <v>1.01246016707376</v>
       </c>
       <c r="CZ264" s="103" t="n">
-        <v>1.012992901858759</v>
+        <v>1.012992901858758</v>
       </c>
       <c r="DA264" s="103" t="n">
         <v>1.013514104921968</v>
@@ -52099,7 +52099,7 @@
         <v>1.013928837783292</v>
       </c>
       <c r="DC264" s="104" t="n">
-        <v>1.014213282022972</v>
+        <v>1.014213282022971</v>
       </c>
       <c r="DE264" s="511" t="n">
         <v>0</v>
@@ -52117,7 +52117,7 @@
         <v>0</v>
       </c>
       <c r="DK264" s="391" t="n">
-        <v>91214772.24990854</v>
+        <v>91214772.24990852</v>
       </c>
       <c r="DL264" s="375" t="n">
         <v>104988005.1745398</v>
@@ -52209,34 +52209,34 @@
         </is>
       </c>
       <c r="AK265" s="506" t="n">
-        <v>49640360.26519077</v>
+        <v>49640360.26519076</v>
       </c>
       <c r="AL265" s="368" t="n">
         <v>53602589.25996547</v>
       </c>
       <c r="AM265" s="368" t="n">
-        <v>58365089.44804497</v>
+        <v>58365089.448045</v>
       </c>
       <c r="AN265" s="368" t="n">
-        <v>64356552.90965887</v>
+        <v>64356552.90965885</v>
       </c>
       <c r="AO265" s="380" t="n">
         <v>72697882.80520257</v>
       </c>
       <c r="AP265" s="381" t="n">
-        <v>1559.512140047487</v>
+        <v>1559.512140047485</v>
       </c>
       <c r="AQ265" s="372" t="n">
-        <v>1655.286013274058</v>
+        <v>1655.286013274059</v>
       </c>
       <c r="AR265" s="372" t="n">
-        <v>1741.35725313567</v>
+        <v>1741.357253135672</v>
       </c>
       <c r="AS265" s="372" t="n">
-        <v>1815.921500581841</v>
+        <v>1815.92150058184</v>
       </c>
       <c r="AT265" s="382" t="n">
-        <v>1911.87909376457</v>
+        <v>1911.879093764572</v>
       </c>
       <c r="BA265" s="101" t="inlineStr">
         <is>
@@ -52244,34 +52244,34 @@
         </is>
       </c>
       <c r="BB265" s="391" t="n">
-        <v>49640360.26519077</v>
+        <v>49640360.26519076</v>
       </c>
       <c r="BC265" s="375" t="n">
         <v>53602589.25996547</v>
       </c>
       <c r="BD265" s="375" t="n">
-        <v>58365089.44804497</v>
+        <v>58365089.448045</v>
       </c>
       <c r="BE265" s="375" t="n">
-        <v>64356552.90965887</v>
+        <v>64356552.90965885</v>
       </c>
       <c r="BF265" s="392" t="n">
         <v>72697882.80520257</v>
       </c>
       <c r="BG265" s="386" t="n">
-        <v>1559.512140047487</v>
+        <v>1559.512140047485</v>
       </c>
       <c r="BH265" s="372" t="n">
-        <v>1655.286013274058</v>
+        <v>1655.286013274059</v>
       </c>
       <c r="BI265" s="372" t="n">
-        <v>1741.35725313567</v>
+        <v>1741.357253135672</v>
       </c>
       <c r="BJ265" s="372" t="n">
-        <v>1815.921500581841</v>
+        <v>1815.92150058184</v>
       </c>
       <c r="BK265" s="387" t="n">
-        <v>1911.87909376457</v>
+        <v>1911.879093764572</v>
       </c>
       <c r="BR265" s="101" t="inlineStr">
         <is>
@@ -52279,82 +52279,82 @@
         </is>
       </c>
       <c r="BS265" s="391" t="n">
-        <v>50132747.3453364</v>
+        <v>50132747.34533639</v>
       </c>
       <c r="BT265" s="375" t="n">
         <v>54567686.23948943</v>
       </c>
       <c r="BU265" s="375" t="n">
-        <v>59834859.82321823</v>
+        <v>59834859.82321826</v>
       </c>
       <c r="BV265" s="375" t="n">
-        <v>66366095.55613156</v>
+        <v>66366095.55613154</v>
       </c>
       <c r="BW265" s="392" t="n">
         <v>75327072.67030132</v>
       </c>
       <c r="BX265" s="386" t="n">
-        <v>1559.512140047487</v>
+        <v>1559.512140047485</v>
       </c>
       <c r="BY265" s="372" t="n">
-        <v>1655.286013274058</v>
+        <v>1655.286013274059</v>
       </c>
       <c r="BZ265" s="372" t="n">
-        <v>1741.35725313567</v>
+        <v>1741.357253135672</v>
       </c>
       <c r="CA265" s="372" t="n">
-        <v>1815.921500581841</v>
+        <v>1815.92150058184</v>
       </c>
       <c r="CB265" s="387" t="n">
-        <v>1911.87909376457</v>
+        <v>1911.879093764572</v>
       </c>
       <c r="CI265" s="396" t="n">
-        <v>0.999999999999995</v>
+        <v>0.9999999999999952</v>
       </c>
       <c r="CJ265" s="397" t="n">
-        <v>1.000000000000001</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="CK265" s="397" t="n">
         <v>1.000000000000005</v>
       </c>
       <c r="CL265" s="397" t="n">
-        <v>0.9999999999999984</v>
+        <v>0.9999999999999987</v>
       </c>
       <c r="CM265" s="398" t="n">
-        <v>1.000000000000005</v>
+        <v>1.000000000000006</v>
       </c>
       <c r="CN265" s="102" t="n">
-        <v>0.9999999999998899</v>
+        <v>0.99999999999989</v>
       </c>
       <c r="CO265" s="103" t="n">
         <v>1.00000000000004</v>
       </c>
       <c r="CP265" s="103" t="n">
-        <v>1.000000000000254</v>
+        <v>1.000000000000253</v>
       </c>
       <c r="CQ265" s="103" t="n">
-        <v>0.9999999999999171</v>
+        <v>0.9999999999999175</v>
       </c>
       <c r="CR265" s="104" t="n">
         <v>1.000000000000211</v>
       </c>
       <c r="CT265" s="396" t="n">
-        <v>0.999999999999995</v>
+        <v>0.9999999999999952</v>
       </c>
       <c r="CU265" s="397" t="n">
-        <v>1.000000000000001</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="CV265" s="397" t="n">
         <v>1.000000000000005</v>
       </c>
       <c r="CW265" s="397" t="n">
-        <v>0.9999999999999984</v>
+        <v>0.9999999999999987</v>
       </c>
       <c r="CX265" s="398" t="n">
-        <v>1.000000000000005</v>
+        <v>1.000000000000006</v>
       </c>
       <c r="CY265" s="102" t="n">
-        <v>1.010821595180417</v>
+        <v>1.010821595180418</v>
       </c>
       <c r="CZ265" s="103" t="n">
         <v>1.011287059486804</v>
@@ -52384,16 +52384,16 @@
         <v>0</v>
       </c>
       <c r="DK265" s="391" t="n">
-        <v>34750578.12387209</v>
+        <v>34750578.12387208</v>
       </c>
       <c r="DL265" s="375" t="n">
-        <v>39059424.72251657</v>
+        <v>39059424.72251656</v>
       </c>
       <c r="DM265" s="375" t="n">
-        <v>43435991.25100249</v>
+        <v>43435991.2510025</v>
       </c>
       <c r="DN265" s="375" t="n">
-        <v>48299721.45664502</v>
+        <v>48299721.456645</v>
       </c>
       <c r="DO265" s="392" t="n">
         <v>55445858.27453823</v>
@@ -52476,34 +52476,34 @@
         </is>
       </c>
       <c r="AK266" s="506" t="n">
-        <v>27454849.66467315</v>
+        <v>27454849.66467313</v>
       </c>
       <c r="AL266" s="368" t="n">
-        <v>30609035.16874773</v>
+        <v>30609035.16874772</v>
       </c>
       <c r="AM266" s="368" t="n">
-        <v>34281145.60176639</v>
+        <v>34281145.60176638</v>
       </c>
       <c r="AN266" s="368" t="n">
-        <v>38563749.91945266</v>
+        <v>38563749.91945268</v>
       </c>
       <c r="AO266" s="380" t="n">
         <v>43774095.21109043</v>
       </c>
       <c r="AP266" s="381" t="n">
-        <v>2349.470593430894</v>
+        <v>2349.470593430893</v>
       </c>
       <c r="AQ266" s="372" t="n">
         <v>2485.680463852157</v>
       </c>
       <c r="AR266" s="372" t="n">
-        <v>2610.628996359924</v>
+        <v>2610.628996359922</v>
       </c>
       <c r="AS266" s="372" t="n">
         <v>2708.250053204245</v>
       </c>
       <c r="AT266" s="382" t="n">
-        <v>2797.787340840875</v>
+        <v>2797.787340840874</v>
       </c>
       <c r="BA266" s="111" t="inlineStr">
         <is>
@@ -52511,34 +52511,34 @@
         </is>
       </c>
       <c r="BB266" s="391" t="n">
-        <v>27454849.66467315</v>
+        <v>27454849.66467313</v>
       </c>
       <c r="BC266" s="375" t="n">
-        <v>30609035.16874773</v>
+        <v>30609035.16874772</v>
       </c>
       <c r="BD266" s="375" t="n">
-        <v>34281145.60176639</v>
+        <v>34281145.60176638</v>
       </c>
       <c r="BE266" s="375" t="n">
-        <v>38563749.91945266</v>
+        <v>38563749.91945268</v>
       </c>
       <c r="BF266" s="392" t="n">
         <v>43774095.21109043</v>
       </c>
       <c r="BG266" s="386" t="n">
-        <v>2349.470593430894</v>
+        <v>2349.470593430893</v>
       </c>
       <c r="BH266" s="372" t="n">
         <v>2485.680463852157</v>
       </c>
       <c r="BI266" s="372" t="n">
-        <v>2610.628996359924</v>
+        <v>2610.628996359922</v>
       </c>
       <c r="BJ266" s="372" t="n">
         <v>2708.250053204245</v>
       </c>
       <c r="BK266" s="387" t="n">
-        <v>2797.787340840875</v>
+        <v>2797.787340840874</v>
       </c>
       <c r="BR266" s="111" t="inlineStr">
         <is>
@@ -52546,7 +52546,7 @@
         </is>
       </c>
       <c r="BS266" s="391" t="n">
-        <v>27524559.52788395</v>
+        <v>27524559.52788394</v>
       </c>
       <c r="BT266" s="375" t="n">
         <v>30832725.79709065</v>
@@ -52555,73 +52555,73 @@
         <v>34674878.53744321</v>
       </c>
       <c r="BV266" s="375" t="n">
-        <v>39141702.84725134</v>
+        <v>39141702.84725136</v>
       </c>
       <c r="BW266" s="392" t="n">
         <v>44556567.68142487</v>
       </c>
       <c r="BX266" s="386" t="n">
-        <v>2349.470593430894</v>
+        <v>2349.470593430893</v>
       </c>
       <c r="BY266" s="372" t="n">
         <v>2485.680463852157</v>
       </c>
       <c r="BZ266" s="372" t="n">
-        <v>2610.628996359924</v>
+        <v>2610.628996359922</v>
       </c>
       <c r="CA266" s="372" t="n">
         <v>2708.250053204245</v>
       </c>
       <c r="CB266" s="387" t="n">
-        <v>2797.787340840875</v>
+        <v>2797.787340840874</v>
       </c>
       <c r="CI266" s="396" t="n">
-        <v>0.999999999999992</v>
+        <v>0.9999999999999928</v>
       </c>
       <c r="CJ266" s="397" t="n">
         <v>1.000000000000001</v>
       </c>
       <c r="CK266" s="397" t="n">
-        <v>1.000000000000021</v>
+        <v>1.00000000000002</v>
       </c>
       <c r="CL266" s="397" t="n">
-        <v>0.9999999999999706</v>
+        <v>0.9999999999999705</v>
       </c>
       <c r="CM266" s="398" t="n">
-        <v>0.9999999999999596</v>
+        <v>0.9999999999999597</v>
       </c>
       <c r="CN266" s="102" t="n">
-        <v>0.999999999999994</v>
+        <v>0.9999999999999944</v>
       </c>
       <c r="CO266" s="103" t="n">
         <v>1.000000000000006</v>
       </c>
       <c r="CP266" s="103" t="n">
-        <v>1.000000000000113</v>
+        <v>1.000000000000114</v>
       </c>
       <c r="CQ266" s="103" t="n">
-        <v>0.9999999999997716</v>
+        <v>0.999999999999771</v>
       </c>
       <c r="CR266" s="104" t="n">
         <v>0.9999999999997509</v>
       </c>
       <c r="CT266" s="396" t="n">
-        <v>0.999999999999992</v>
+        <v>0.9999999999999928</v>
       </c>
       <c r="CU266" s="397" t="n">
         <v>1.000000000000001</v>
       </c>
       <c r="CV266" s="397" t="n">
-        <v>1.000000000000021</v>
+        <v>1.00000000000002</v>
       </c>
       <c r="CW266" s="397" t="n">
-        <v>0.9999999999999706</v>
+        <v>0.9999999999999705</v>
       </c>
       <c r="CX266" s="398" t="n">
-        <v>0.9999999999999596</v>
+        <v>0.9999999999999597</v>
       </c>
       <c r="CY266" s="102" t="n">
-        <v>1.011153716208352</v>
+        <v>1.011153716208353</v>
       </c>
       <c r="CZ266" s="103" t="n">
         <v>1.011529745696788</v>
@@ -52654,7 +52654,7 @@
         <v>18936636.2269968</v>
       </c>
       <c r="DL266" s="375" t="n">
-        <v>21655757.8344942</v>
+        <v>21655757.83449421</v>
       </c>
       <c r="DM266" s="375" t="n">
         <v>24654357.08209224</v>
@@ -52752,13 +52752,13 @@
         <v>353845923.7850232</v>
       </c>
       <c r="AN267" s="408" t="n">
-        <v>400144174.7224734</v>
+        <v>400144174.7224731</v>
       </c>
       <c r="AO267" s="409" t="n">
-        <v>458182076.6647987</v>
+        <v>458182076.6647986</v>
       </c>
       <c r="AP267" s="410" t="n">
-        <v>12521.32949520651</v>
+        <v>12521.3294952065</v>
       </c>
       <c r="AQ267" s="411" t="n">
         <v>12813.16039477739</v>
@@ -52767,7 +52767,7 @@
         <v>13089.82884659031</v>
       </c>
       <c r="AS267" s="411" t="n">
-        <v>13374.31064517072</v>
+        <v>13374.31064517071</v>
       </c>
       <c r="AT267" s="412" t="n">
         <v>13705.7889236738</v>
@@ -52787,13 +52787,13 @@
         <v>353845923.7850232</v>
       </c>
       <c r="BE267" s="420" t="n">
-        <v>400144174.7224734</v>
+        <v>400144174.7224731</v>
       </c>
       <c r="BF267" s="421" t="n">
-        <v>458182076.6647987</v>
+        <v>458182076.6647986</v>
       </c>
       <c r="BG267" s="416" t="n">
-        <v>12521.32949520651</v>
+        <v>12521.3294952065</v>
       </c>
       <c r="BH267" s="417" t="n">
         <v>12813.16039477739</v>
@@ -52802,7 +52802,7 @@
         <v>13089.82884659031</v>
       </c>
       <c r="BJ267" s="417" t="n">
-        <v>13374.31064517072</v>
+        <v>13374.31064517071</v>
       </c>
       <c r="BK267" s="418" t="n">
         <v>13705.7889236738</v>
@@ -52813,7 +52813,7 @@
         </is>
       </c>
       <c r="BS267" s="419" t="n">
-        <v>269873908.3382682</v>
+        <v>269873908.3382681</v>
       </c>
       <c r="BT267" s="420" t="n">
         <v>304550625.5079275</v>
@@ -52822,13 +52822,13 @@
         <v>344413772.2410913</v>
       </c>
       <c r="BV267" s="420" t="n">
-        <v>389867207.5569916</v>
+        <v>389867207.5569912</v>
       </c>
       <c r="BW267" s="421" t="n">
         <v>446500063.8135937</v>
       </c>
       <c r="BX267" s="416" t="n">
-        <v>12521.32949520651</v>
+        <v>12521.3294952065</v>
       </c>
       <c r="BY267" s="417" t="n">
         <v>12813.16039477739</v>
@@ -52837,16 +52837,16 @@
         <v>13089.82884659031</v>
       </c>
       <c r="CA267" s="417" t="n">
-        <v>13374.31064517072</v>
+        <v>13374.31064517071</v>
       </c>
       <c r="CB267" s="418" t="n">
         <v>13705.7889236738</v>
       </c>
       <c r="CI267" s="422" t="n">
-        <v>0.999999999999776</v>
+        <v>0.9999999999997758</v>
       </c>
       <c r="CJ267" s="423" t="n">
-        <v>1.000000000000282</v>
+        <v>1.000000000000281</v>
       </c>
       <c r="CK267" s="423" t="n">
         <v>0.999999999999782</v>
@@ -52861,22 +52861,22 @@
         <v>1.000000000000435</v>
       </c>
       <c r="CO267" s="133" t="n">
-        <v>0.9999999999995582</v>
+        <v>0.9999999999995581</v>
       </c>
       <c r="CP267" s="133" t="n">
         <v>1.000000000000194</v>
       </c>
       <c r="CQ267" s="133" t="n">
-        <v>0.9999999999997883</v>
+        <v>0.9999999999997891</v>
       </c>
       <c r="CR267" s="134" t="n">
-        <v>0.9999999999996196</v>
+        <v>0.9999999999996199</v>
       </c>
       <c r="CT267" s="422" t="n">
-        <v>0.999999999999776</v>
+        <v>0.9999999999997758</v>
       </c>
       <c r="CU267" s="423" t="n">
-        <v>1.000000000000282</v>
+        <v>1.000000000000281</v>
       </c>
       <c r="CV267" s="423" t="n">
         <v>0.999999999999782</v>
@@ -52894,13 +52894,13 @@
         <v>1.031706490389905</v>
       </c>
       <c r="DA267" s="133" t="n">
-        <v>1.032463657793182</v>
+        <v>1.032463657793181</v>
       </c>
       <c r="DB267" s="133" t="n">
-        <v>1.032608668003571</v>
+        <v>1.032608668003572</v>
       </c>
       <c r="DC267" s="134" t="n">
-        <v>1.03356150621562</v>
+        <v>1.033561506215621</v>
       </c>
       <c r="DE267" s="419" t="n">
         <v>0</v>
@@ -52918,19 +52918,19 @@
         <v>0</v>
       </c>
       <c r="DK267" s="419" t="n">
-        <v>163797061.6705368</v>
+        <v>163797061.6705367</v>
       </c>
       <c r="DL267" s="420" t="n">
         <v>188089957.4893983</v>
       </c>
       <c r="DM267" s="420" t="n">
-        <v>215978942.3423748</v>
+        <v>215978942.3423746</v>
       </c>
       <c r="DN267" s="420" t="n">
         <v>246346883.7616721</v>
       </c>
       <c r="DO267" s="421" t="n">
-        <v>286688358.6587306</v>
+        <v>286688358.6587304</v>
       </c>
     </row>
     <row r="268" ht="15.75" customHeight="1" thickBot="1">
@@ -53013,31 +53013,31 @@
         <v>481161614.8533119</v>
       </c>
       <c r="AL268" s="408" t="n">
-        <v>538476579.7954476</v>
+        <v>538476579.7954478</v>
       </c>
       <c r="AM268" s="408" t="n">
-        <v>602828595.0017827</v>
+        <v>602828595.0017828</v>
       </c>
       <c r="AN268" s="408" t="n">
-        <v>675861979.5778961</v>
+        <v>675861979.5778959</v>
       </c>
       <c r="AO268" s="409" t="n">
-        <v>769448594.4916774</v>
+        <v>769448594.4916775</v>
       </c>
       <c r="AP268" s="436" t="n">
-        <v>2163.756050837528</v>
+        <v>2163.756050837529</v>
       </c>
       <c r="AQ268" s="437" t="n">
-        <v>2306.266576502182</v>
+        <v>2306.266576502183</v>
       </c>
       <c r="AR268" s="437" t="n">
-        <v>2446.296897853597</v>
+        <v>2446.296897853598</v>
       </c>
       <c r="AS268" s="437" t="n">
         <v>2570.842398787376</v>
       </c>
       <c r="AT268" s="438" t="n">
-        <v>2709.041941852845</v>
+        <v>2709.041941852847</v>
       </c>
       <c r="BA268" s="155" t="inlineStr">
         <is>
@@ -53048,31 +53048,31 @@
         <v>481161614.8533119</v>
       </c>
       <c r="BC268" s="440" t="n">
-        <v>538476579.7954476</v>
+        <v>538476579.7954478</v>
       </c>
       <c r="BD268" s="440" t="n">
-        <v>602828595.0017827</v>
+        <v>602828595.0017828</v>
       </c>
       <c r="BE268" s="440" t="n">
-        <v>675861979.5778961</v>
+        <v>675861979.5778959</v>
       </c>
       <c r="BF268" s="441" t="n">
-        <v>769448594.4916774</v>
+        <v>769448594.4916775</v>
       </c>
       <c r="BG268" s="442" t="n">
-        <v>2163.756050837528</v>
+        <v>2163.756050837529</v>
       </c>
       <c r="BH268" s="443" t="n">
-        <v>2306.266576502182</v>
+        <v>2306.266576502183</v>
       </c>
       <c r="BI268" s="443" t="n">
-        <v>2446.296897853597</v>
+        <v>2446.296897853598</v>
       </c>
       <c r="BJ268" s="443" t="n">
         <v>2570.842398787376</v>
       </c>
       <c r="BK268" s="444" t="n">
-        <v>2709.041941852845</v>
+        <v>2709.041941852847</v>
       </c>
       <c r="BR268" s="155" t="inlineStr">
         <is>
@@ -53080,16 +53080,16 @@
         </is>
       </c>
       <c r="BS268" s="439" t="n">
-        <v>474951381.2752882</v>
+        <v>474951381.275288</v>
       </c>
       <c r="BT268" s="440" t="n">
-        <v>533029484.8638857</v>
+        <v>533029484.8638859</v>
       </c>
       <c r="BU268" s="440" t="n">
-        <v>598231970.5695922</v>
+        <v>598231970.5695924</v>
       </c>
       <c r="BV268" s="440" t="n">
-        <v>672371281.253221</v>
+        <v>672371281.2532208</v>
       </c>
       <c r="BW268" s="441" t="n">
         <v>766783160.6297807</v>
@@ -53098,16 +53098,16 @@
         <v>2128.802545631965</v>
       </c>
       <c r="BY268" s="443" t="n">
-        <v>2262.18545654692</v>
+        <v>2262.185456546921</v>
       </c>
       <c r="BZ268" s="443" t="n">
-        <v>2393.088848784537</v>
+        <v>2393.088848784538</v>
       </c>
       <c r="CA268" s="443" t="n">
-        <v>2509.778431754757</v>
+        <v>2509.778431754756</v>
       </c>
       <c r="CB268" s="444" t="n">
-        <v>2639.54117137533</v>
+        <v>2639.541171375331</v>
       </c>
       <c r="DE268" s="419" t="n">
         <v>0</v>
@@ -53125,19 +53125,19 @@
         <v>0</v>
       </c>
       <c r="DK268" s="439" t="n">
-        <v>308699048.2713143</v>
+        <v>308699048.2713141</v>
       </c>
       <c r="DL268" s="440" t="n">
         <v>353793145.2209489</v>
       </c>
       <c r="DM268" s="440" t="n">
-        <v>402085870.8963985</v>
+        <v>402085870.8963984</v>
       </c>
       <c r="DN268" s="440" t="n">
-        <v>454436840.5772561</v>
+        <v>454436840.577256</v>
       </c>
       <c r="DO268" s="441" t="n">
-        <v>525288975.6667447</v>
+        <v>525288975.6667445</v>
       </c>
     </row>
     <row r="269">
@@ -58406,34 +58406,34 @@
         <v>0</v>
       </c>
       <c r="BX294" s="197" t="n">
-        <v>1964.87507178444</v>
+        <v>1964.875071784435</v>
       </c>
       <c r="BY294" s="190" t="n">
-        <v>2163.155319482304</v>
+        <v>2163.1553194823</v>
       </c>
       <c r="BZ294" s="190" t="n">
-        <v>2378.866087308496</v>
+        <v>2378.866087308491</v>
       </c>
       <c r="CA294" s="190" t="n">
-        <v>2615.148328173792</v>
+        <v>2615.148328173786</v>
       </c>
       <c r="CB294" s="198" t="n">
-        <v>2879.55457333282</v>
+        <v>2879.554573332814</v>
       </c>
       <c r="CC294" s="199" t="n">
-        <v>1964.87507178444</v>
+        <v>1964.875071784435</v>
       </c>
       <c r="CD294" s="200" t="n">
-        <v>2163.155319482304</v>
+        <v>2163.1553194823</v>
       </c>
       <c r="CE294" s="200" t="n">
-        <v>2378.866087308496</v>
+        <v>2378.866087308491</v>
       </c>
       <c r="CF294" s="200" t="n">
-        <v>2615.148328173792</v>
+        <v>2615.148328173786</v>
       </c>
       <c r="CG294" s="201" t="n">
-        <v>2879.55457333282</v>
+        <v>2879.554573332814</v>
       </c>
       <c r="CI294" s="199" t="n">
         <v>0</v>
@@ -58463,19 +58463,19 @@
         <v>0</v>
       </c>
       <c r="CW294" s="199" t="n">
-        <v>1964.87507178444</v>
+        <v>1964.875071784435</v>
       </c>
       <c r="CX294" s="200" t="n">
-        <v>2163.155319482304</v>
+        <v>2163.1553194823</v>
       </c>
       <c r="CY294" s="200" t="n">
-        <v>2378.866087308496</v>
+        <v>2378.866087308491</v>
       </c>
       <c r="CZ294" s="200" t="n">
-        <v>2615.148328173792</v>
+        <v>2615.148328173786</v>
       </c>
       <c r="DA294" s="201" t="n">
-        <v>2879.55457333282</v>
+        <v>2879.554573332814</v>
       </c>
     </row>
     <row r="295">
@@ -58701,34 +58701,34 @@
         <v>0</v>
       </c>
       <c r="BX295" s="197" t="n">
-        <v>347.8756485031444</v>
+        <v>347.8756485031441</v>
       </c>
       <c r="BY295" s="190" t="n">
-        <v>372.0859813342885</v>
+        <v>372.0859813342883</v>
       </c>
       <c r="BZ295" s="190" t="n">
-        <v>407.7078036314259</v>
+        <v>407.7078036314253</v>
       </c>
       <c r="CA295" s="190" t="n">
-        <v>446.7528256294976</v>
+        <v>446.7528256294972</v>
       </c>
       <c r="CB295" s="198" t="n">
-        <v>490.9710966467709</v>
+        <v>490.9710966467706</v>
       </c>
       <c r="CC295" s="197" t="n">
-        <v>347.8756485031444</v>
+        <v>347.8756485031441</v>
       </c>
       <c r="CD295" s="190" t="n">
-        <v>372.0859813342885</v>
+        <v>372.0859813342883</v>
       </c>
       <c r="CE295" s="190" t="n">
-        <v>407.7078036314259</v>
+        <v>407.7078036314253</v>
       </c>
       <c r="CF295" s="190" t="n">
-        <v>446.7528256294976</v>
+        <v>446.7528256294972</v>
       </c>
       <c r="CG295" s="198" t="n">
-        <v>490.9710966467709</v>
+        <v>490.9710966467706</v>
       </c>
       <c r="CI295" s="197" t="n">
         <v>0</v>
@@ -58758,19 +58758,19 @@
         <v>0</v>
       </c>
       <c r="CW295" s="197" t="n">
-        <v>347.8756485031444</v>
+        <v>347.8756485031441</v>
       </c>
       <c r="CX295" s="190" t="n">
-        <v>372.0859813342885</v>
+        <v>372.0859813342883</v>
       </c>
       <c r="CY295" s="190" t="n">
-        <v>407.7078036314259</v>
+        <v>407.7078036314253</v>
       </c>
       <c r="CZ295" s="190" t="n">
-        <v>446.7528256294976</v>
+        <v>446.7528256294972</v>
       </c>
       <c r="DA295" s="198" t="n">
-        <v>490.9710966467709</v>
+        <v>490.9710966467706</v>
       </c>
     </row>
     <row r="296">
@@ -59005,10 +59005,10 @@
         <v>157.7761316534094</v>
       </c>
       <c r="CA296" s="190" t="n">
-        <v>174.2565804323907</v>
+        <v>174.2565804323906</v>
       </c>
       <c r="CB296" s="198" t="n">
-        <v>192.9148478659413</v>
+        <v>192.9148478659412</v>
       </c>
       <c r="CC296" s="197" t="n">
         <v>130.6682137649147</v>
@@ -59020,10 +59020,10 @@
         <v>157.7761316534094</v>
       </c>
       <c r="CF296" s="190" t="n">
-        <v>174.2565804323907</v>
+        <v>174.2565804323906</v>
       </c>
       <c r="CG296" s="198" t="n">
-        <v>192.9148478659413</v>
+        <v>192.9148478659412</v>
       </c>
       <c r="CI296" s="197" t="n">
         <v>0</v>
@@ -59062,10 +59062,10 @@
         <v>157.7761316534094</v>
       </c>
       <c r="CZ296" s="190" t="n">
-        <v>174.2565804323907</v>
+        <v>174.2565804323906</v>
       </c>
       <c r="DA296" s="198" t="n">
-        <v>192.9148478659413</v>
+        <v>192.9148478659412</v>
       </c>
     </row>
     <row r="297" ht="15.75" customHeight="1" thickBot="1">
@@ -59291,31 +59291,31 @@
         <v>0</v>
       </c>
       <c r="BX297" s="211" t="n">
-        <v>663.9327169755792</v>
+        <v>663.9327169755794</v>
       </c>
       <c r="BY297" s="212" t="n">
-        <v>753.6182474419338</v>
+        <v>753.6182474419339</v>
       </c>
       <c r="BZ297" s="212" t="n">
-        <v>854.1693686245004</v>
+        <v>854.1693686245003</v>
       </c>
       <c r="CA297" s="212" t="n">
-        <v>950.5574286398273</v>
+        <v>950.5574286398277</v>
       </c>
       <c r="CB297" s="213" t="n">
         <v>1093.349295717359</v>
       </c>
       <c r="CC297" s="212" t="n">
-        <v>663.9327169755792</v>
+        <v>663.9327169755794</v>
       </c>
       <c r="CD297" s="212" t="n">
-        <v>753.6182474419338</v>
+        <v>753.6182474419339</v>
       </c>
       <c r="CE297" s="212" t="n">
-        <v>854.1693686245004</v>
+        <v>854.1693686245003</v>
       </c>
       <c r="CF297" s="212" t="n">
-        <v>950.5574286398273</v>
+        <v>950.5574286398277</v>
       </c>
       <c r="CG297" s="213" t="n">
         <v>1093.349295717359</v>
@@ -59348,16 +59348,16 @@
         <v>0</v>
       </c>
       <c r="CW297" s="211" t="n">
-        <v>663.9327169755792</v>
+        <v>663.9327169755794</v>
       </c>
       <c r="CX297" s="212" t="n">
-        <v>753.6182474419338</v>
+        <v>753.6182474419339</v>
       </c>
       <c r="CY297" s="212" t="n">
-        <v>854.1693686245004</v>
+        <v>854.1693686245003</v>
       </c>
       <c r="CZ297" s="212" t="n">
-        <v>950.5574286398273</v>
+        <v>950.5574286398277</v>
       </c>
       <c r="DA297" s="213" t="n">
         <v>1093.349295717359</v>
@@ -59586,34 +59586,34 @@
         <v>0</v>
       </c>
       <c r="BX298" s="221" t="n">
-        <v>3107.351651028078</v>
+        <v>3107.351651028073</v>
       </c>
       <c r="BY298" s="222" t="n">
-        <v>3431.876115652925</v>
+        <v>3431.87611565292</v>
       </c>
       <c r="BZ298" s="222" t="n">
-        <v>3798.519391217832</v>
+        <v>3798.519391217827</v>
       </c>
       <c r="CA298" s="222" t="n">
-        <v>4186.715162875507</v>
+        <v>4186.715162875502</v>
       </c>
       <c r="CB298" s="214" t="n">
-        <v>4656.789813562891</v>
+        <v>4656.789813562885</v>
       </c>
       <c r="CC298" s="222" t="n">
-        <v>3107.351651028078</v>
+        <v>3107.351651028073</v>
       </c>
       <c r="CD298" s="222" t="n">
-        <v>3431.876115652925</v>
+        <v>3431.87611565292</v>
       </c>
       <c r="CE298" s="222" t="n">
-        <v>3798.519391217832</v>
+        <v>3798.519391217827</v>
       </c>
       <c r="CF298" s="222" t="n">
-        <v>4186.715162875507</v>
+        <v>4186.715162875502</v>
       </c>
       <c r="CG298" s="214" t="n">
-        <v>4656.789813562891</v>
+        <v>4656.789813562885</v>
       </c>
       <c r="CI298" s="349" t="n">
         <v>0</v>
@@ -59643,19 +59643,19 @@
         <v>0</v>
       </c>
       <c r="CW298" s="211" t="n">
-        <v>3107.351651028078</v>
+        <v>3107.351651028073</v>
       </c>
       <c r="CX298" s="212" t="n">
-        <v>3431.876115652925</v>
+        <v>3431.87611565292</v>
       </c>
       <c r="CY298" s="212" t="n">
-        <v>3798.519391217832</v>
+        <v>3798.519391217827</v>
       </c>
       <c r="CZ298" s="212" t="n">
-        <v>4186.715162875507</v>
+        <v>4186.715162875502</v>
       </c>
       <c r="DA298" s="213" t="n">
-        <v>4656.789813562891</v>
+        <v>4656.789813562885</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1" thickBot="1">
@@ -71183,49 +71183,49 @@
         </is>
       </c>
       <c r="BS368" s="391" t="n">
-        <v>1587676.557723576</v>
+        <v>1587676.557723572</v>
       </c>
       <c r="BT368" s="375" t="n">
-        <v>1859004.224119244</v>
+        <v>1859004.224119243</v>
       </c>
       <c r="BU368" s="375" t="n">
-        <v>2152911.242958715</v>
+        <v>2152911.242958711</v>
       </c>
       <c r="BV368" s="375" t="n">
-        <v>2465352.4068048</v>
+        <v>2465352.406804795</v>
       </c>
       <c r="BW368" s="392" t="n">
-        <v>2848333.991962681</v>
+        <v>2848333.991962677</v>
       </c>
       <c r="BX368" s="386" t="n">
-        <v>808.0292638054067</v>
+        <v>808.0292638054065</v>
       </c>
       <c r="BY368" s="372" t="n">
-        <v>859.3947033651516</v>
+        <v>859.3947033651526</v>
       </c>
       <c r="BZ368" s="372" t="n">
-        <v>905.0157360453056</v>
+        <v>905.0157360453057</v>
       </c>
       <c r="CA368" s="372" t="n">
-        <v>942.719913912647</v>
+        <v>942.7199139126474</v>
       </c>
       <c r="CB368" s="387" t="n">
-        <v>989.1578434875767</v>
+        <v>989.1578434875773</v>
       </c>
       <c r="CW368" s="511" t="n">
-        <v>1587676.557723576</v>
+        <v>1587676.557723572</v>
       </c>
       <c r="CX368" s="512" t="n">
-        <v>1859004.224119244</v>
+        <v>1859004.224119243</v>
       </c>
       <c r="CY368" s="512" t="n">
-        <v>2152911.242958715</v>
+        <v>2152911.242958711</v>
       </c>
       <c r="CZ368" s="512" t="n">
-        <v>2465352.4068048</v>
+        <v>2465352.406804795</v>
       </c>
       <c r="DA368" s="513" t="n">
-        <v>2848333.991962681</v>
+        <v>2848333.991962677</v>
       </c>
     </row>
     <row r="369">
@@ -71375,49 +71375,49 @@
         </is>
       </c>
       <c r="BS369" s="391" t="n">
-        <v>542516.2970675459</v>
+        <v>542516.2970675449</v>
       </c>
       <c r="BT369" s="375" t="n">
-        <v>615908.7206380002</v>
+        <v>615908.7206380001</v>
       </c>
       <c r="BU369" s="375" t="n">
-        <v>709964.9410135967</v>
+        <v>709964.9410135968</v>
       </c>
       <c r="BV369" s="375" t="n">
-        <v>811268.0615062946</v>
+        <v>811268.0615062936</v>
       </c>
       <c r="BW369" s="392" t="n">
-        <v>938677.3753216255</v>
+        <v>938677.3753216256</v>
       </c>
       <c r="BX369" s="386" t="n">
-        <v>1559.512140047487</v>
+        <v>1559.512140047485</v>
       </c>
       <c r="BY369" s="372" t="n">
-        <v>1655.286013274058</v>
+        <v>1655.286013274059</v>
       </c>
       <c r="BZ369" s="372" t="n">
-        <v>1741.35725313567</v>
+        <v>1741.357253135672</v>
       </c>
       <c r="CA369" s="372" t="n">
-        <v>1815.921500581841</v>
+        <v>1815.92150058184</v>
       </c>
       <c r="CB369" s="387" t="n">
-        <v>1911.87909376457</v>
+        <v>1911.879093764572</v>
       </c>
       <c r="CW369" s="391" t="n">
-        <v>542516.2970675459</v>
+        <v>542516.2970675449</v>
       </c>
       <c r="CX369" s="375" t="n">
-        <v>615908.7206380002</v>
+        <v>615908.7206380001</v>
       </c>
       <c r="CY369" s="375" t="n">
-        <v>709964.9410135967</v>
+        <v>709964.9410135968</v>
       </c>
       <c r="CZ369" s="375" t="n">
-        <v>811268.0615062946</v>
+        <v>811268.0615062936</v>
       </c>
       <c r="DA369" s="392" t="n">
-        <v>938677.3753216255</v>
+        <v>938677.3753216256</v>
       </c>
     </row>
     <row r="370">
@@ -71567,49 +71567,49 @@
         </is>
       </c>
       <c r="BS370" s="391" t="n">
-        <v>307001.125736809</v>
+        <v>307001.1257368088</v>
       </c>
       <c r="BT370" s="375" t="n">
-        <v>355493.487579452</v>
+        <v>355493.4875794519</v>
       </c>
       <c r="BU370" s="375" t="n">
-        <v>411894.9442278914</v>
+        <v>411894.9442278913</v>
       </c>
       <c r="BV370" s="375" t="n">
-        <v>471930.3932272118</v>
+        <v>471930.3932272116</v>
       </c>
       <c r="BW370" s="392" t="n">
-        <v>539734.7192195738</v>
+        <v>539734.7192195734</v>
       </c>
       <c r="BX370" s="386" t="n">
-        <v>2349.470593430894</v>
+        <v>2349.470593430893</v>
       </c>
       <c r="BY370" s="372" t="n">
         <v>2485.680463852157</v>
       </c>
       <c r="BZ370" s="372" t="n">
-        <v>2610.628996359924</v>
+        <v>2610.628996359922</v>
       </c>
       <c r="CA370" s="372" t="n">
         <v>2708.250053204245</v>
       </c>
       <c r="CB370" s="387" t="n">
-        <v>2797.787340840875</v>
+        <v>2797.787340840874</v>
       </c>
       <c r="CW370" s="391" t="n">
-        <v>307001.125736809</v>
+        <v>307001.1257368088</v>
       </c>
       <c r="CX370" s="375" t="n">
-        <v>355493.487579452</v>
+        <v>355493.4875794519</v>
       </c>
       <c r="CY370" s="375" t="n">
-        <v>411894.9442278914</v>
+        <v>411894.9442278913</v>
       </c>
       <c r="CZ370" s="375" t="n">
-        <v>471930.3932272118</v>
+        <v>471930.3932272116</v>
       </c>
       <c r="DA370" s="392" t="n">
-        <v>539734.7192195738</v>
+        <v>539734.7192195734</v>
       </c>
     </row>
     <row r="371" ht="15.75" customHeight="1" thickBot="1">
@@ -71759,22 +71759,22 @@
         </is>
       </c>
       <c r="BS371" s="419" t="n">
-        <v>8313320.311898914</v>
+        <v>8313320.311898915</v>
       </c>
       <c r="BT371" s="420" t="n">
-        <v>9656231.480904531</v>
+        <v>9656231.480904533</v>
       </c>
       <c r="BU371" s="420" t="n">
         <v>11180930.84129482</v>
       </c>
       <c r="BV371" s="420" t="n">
-        <v>12713050.33670375</v>
+        <v>12713050.33670374</v>
       </c>
       <c r="BW371" s="421" t="n">
-        <v>14985214.66694952</v>
+        <v>14985214.66694953</v>
       </c>
       <c r="BX371" s="416" t="n">
-        <v>12521.32949520651</v>
+        <v>12521.3294952065</v>
       </c>
       <c r="BY371" s="417" t="n">
         <v>12813.16039477739</v>
@@ -71783,25 +71783,25 @@
         <v>13089.82884659031</v>
       </c>
       <c r="CA371" s="417" t="n">
-        <v>13374.31064517072</v>
+        <v>13374.31064517071</v>
       </c>
       <c r="CB371" s="418" t="n">
         <v>13705.7889236738</v>
       </c>
       <c r="CW371" s="419" t="n">
-        <v>8313320.311898914</v>
+        <v>8313320.311898915</v>
       </c>
       <c r="CX371" s="420" t="n">
-        <v>9656231.480904531</v>
+        <v>9656231.480904533</v>
       </c>
       <c r="CY371" s="420" t="n">
         <v>11180930.84129482</v>
       </c>
       <c r="CZ371" s="420" t="n">
-        <v>12713050.33670375</v>
+        <v>12713050.33670374</v>
       </c>
       <c r="DA371" s="421" t="n">
-        <v>14985214.66694952</v>
+        <v>14985214.66694953</v>
       </c>
     </row>
     <row r="372" ht="15.75" customHeight="1" thickBot="1">
@@ -71951,7 +71951,7 @@
         </is>
       </c>
       <c r="BS372" s="439" t="n">
-        <v>10750514.29242685</v>
+        <v>10750514.29242684</v>
       </c>
       <c r="BT372" s="440" t="n">
         <v>12486637.91324123</v>
@@ -71960,28 +71960,28 @@
         <v>14455701.96949502</v>
       </c>
       <c r="BV372" s="440" t="n">
-        <v>16461601.19824205</v>
+        <v>16461601.19824204</v>
       </c>
       <c r="BW372" s="441" t="n">
         <v>19311960.7534534</v>
       </c>
       <c r="BX372" s="442" t="n">
-        <v>3459.703149101261</v>
+        <v>3459.703149101265</v>
       </c>
       <c r="BY372" s="443" t="n">
-        <v>3638.429096053079</v>
+        <v>3638.429096053085</v>
       </c>
       <c r="BZ372" s="443" t="n">
-        <v>3805.614893770602</v>
+        <v>3805.614893770606</v>
       </c>
       <c r="CA372" s="443" t="n">
-        <v>3931.86556950675</v>
+        <v>3931.865569506753</v>
       </c>
       <c r="CB372" s="444" t="n">
-        <v>4147.054414439611</v>
+        <v>4147.054414439617</v>
       </c>
       <c r="CW372" s="419" t="n">
-        <v>10750514.29242685</v>
+        <v>10750514.29242684</v>
       </c>
       <c r="CX372" s="420" t="n">
         <v>12486637.91324123</v>
@@ -71990,7 +71990,7 @@
         <v>14455701.96949502</v>
       </c>
       <c r="CZ372" s="420" t="n">
-        <v>16461601.19824205</v>
+        <v>16461601.19824204</v>
       </c>
       <c r="DA372" s="421" t="n">
         <v>19311960.7534534</v>
